--- a/data/Annotation tracker.xlsx
+++ b/data/Annotation tracker.xlsx
@@ -1,21 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10312"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harom/Library/CloudStorage/Box-Box/Lawrenson Lab/Endometriosis/Rstudio_analysis/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HaroM\Box\Lawrenson Lab\Endometriosis\Rstudio_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23CB2EB7-97DB-464E-8212-293212D9439A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61069038-2E24-417C-BD4D-3AC1CB775A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="4140" windowWidth="23280" windowHeight="18420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9465" yWindow="1950" windowWidth="28080" windowHeight="13800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clusters" sheetId="1" r:id="rId1"/>
     <sheet name="Epi_Data" sheetId="2" r:id="rId2"/>
     <sheet name="tissue_sample_meta" sheetId="3" r:id="rId3"/>
+    <sheet name="Major_groups" sheetId="4" r:id="rId4"/>
+    <sheet name="Patient_LA_Status_Tissue_Level" sheetId="5" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="Z_D9CDEFDA_B742_4707_B803_BE75C138FC2A_.wvu.FilterData" localSheetId="2" hidden="1">tissue_sample_meta!$P$1:$P$994</definedName>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="154">
   <si>
     <t>Cluster_Number</t>
   </si>
@@ -481,17 +483,33 @@
   </si>
   <si>
     <t>Posterior uterus</t>
+  </si>
+  <si>
+    <t>Major_groups</t>
+  </si>
+  <si>
+    <t>Immune cells</t>
+  </si>
+  <si>
+    <t>Patient_LA_Status_Tissue_Level</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -563,6 +581,13 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -669,98 +694,102 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="11" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="12" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -981,15 +1010,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" customWidth="1"/>
-    <col min="4" max="5" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" customWidth="1"/>
+    <col min="4" max="5" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1000,7 +1029,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1008,7 +1037,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1016,7 +1045,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1024,7 +1053,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1032,7 +1061,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1040,7 +1069,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1048,7 +1077,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1056,7 +1085,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1065,7 +1094,7 @@
       </c>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1074,7 +1103,7 @@
       </c>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1083,7 +1112,7 @@
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1092,7 +1121,7 @@
       </c>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1101,7 +1130,7 @@
       </c>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1111,7 +1140,7 @@
       <c r="H14" s="6"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1119,7 +1148,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1127,7 +1156,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1135,7 +1164,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1143,7 +1172,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1154,7 +1183,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1162,7 +1191,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1171,7 +1200,7 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1179,7 +1208,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1187,7 +1216,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -1195,7 +1224,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -1206,7 +1235,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -1215,7 +1244,7 @@
       </c>
       <c r="C26" s="7"/>
     </row>
-    <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -1223,7 +1252,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -1234,7 +1263,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -1245,7 +1274,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -1253,7 +1282,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -1261,7 +1290,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -1269,7 +1298,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -1277,7 +1306,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -1285,7 +1314,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -1293,7 +1322,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -1301,7 +1330,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -1309,7 +1338,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -1317,7 +1346,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -1325,7 +1354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -1333,7 +1362,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -1341,7 +1370,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -1349,7 +1378,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -1357,7 +1386,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -1365,7 +1394,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -1376,7 +1405,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -1384,7 +1413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -1395,7 +1424,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -1403,7 +1432,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -1411,7 +1440,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -1419,7 +1448,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -1427,7 +1456,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -1435,7 +1464,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -1443,7 +1472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -1451,7 +1480,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -1462,7 +1491,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -1470,7 +1499,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -1481,7 +1510,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -1489,7 +1518,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -1497,7 +1526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -1505,7 +1534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -1516,7 +1545,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>60</v>
       </c>
@@ -1524,7 +1553,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>61</v>
       </c>
@@ -1532,7 +1561,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -1543,7 +1572,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -1551,7 +1580,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -1562,7 +1591,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -1573,7 +1602,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -1581,7 +1610,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -1589,7 +1618,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>68</v>
       </c>
@@ -1597,7 +1626,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>69</v>
       </c>
@@ -1605,7 +1634,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>70</v>
       </c>
@@ -1613,7 +1642,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -1621,7 +1650,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>72</v>
       </c>
@@ -1629,7 +1658,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>73</v>
       </c>
@@ -1637,7 +1666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>74</v>
       </c>
@@ -1648,7 +1677,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -1656,7 +1685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -1664,7 +1693,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>77</v>
       </c>
@@ -1672,7 +1701,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>78</v>
       </c>
@@ -1680,7 +1709,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>79</v>
       </c>
@@ -1691,7 +1720,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>80</v>
       </c>
@@ -1699,7 +1728,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>81</v>
       </c>
@@ -1707,7 +1736,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>82</v>
       </c>
@@ -1715,7 +1744,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>83</v>
       </c>
@@ -1723,7 +1752,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>84</v>
       </c>
@@ -1731,7 +1760,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>85</v>
       </c>
@@ -1739,7 +1768,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>86</v>
       </c>
@@ -1747,7 +1776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>87</v>
       </c>
@@ -1755,7 +1784,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>88</v>
       </c>
@@ -1766,7 +1795,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>89</v>
       </c>
@@ -1774,7 +1803,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>90</v>
       </c>
@@ -1782,7 +1811,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>91</v>
       </c>
@@ -1790,7 +1819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>92</v>
       </c>
@@ -1798,7 +1827,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>93</v>
       </c>
@@ -1806,7 +1835,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>94</v>
       </c>
@@ -1814,7 +1843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>95</v>
       </c>
@@ -1822,7 +1851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>96</v>
       </c>
@@ -1830,7 +1859,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>97</v>
       </c>
@@ -1838,7 +1867,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>98</v>
       </c>
@@ -1846,7 +1875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>99</v>
       </c>
@@ -1854,7 +1883,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>100</v>
       </c>
@@ -1862,7 +1891,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>101</v>
       </c>
@@ -1873,7 +1902,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>102</v>
       </c>
@@ -1881,7 +1910,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>103</v>
       </c>
@@ -1892,7 +1921,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>104</v>
       </c>
@@ -1900,7 +1929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>105</v>
       </c>
@@ -1908,7 +1937,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>106</v>
       </c>
@@ -1916,7 +1945,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>107</v>
       </c>
@@ -1924,7 +1953,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>108</v>
       </c>
@@ -1932,7 +1961,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>109</v>
       </c>
@@ -1940,7 +1969,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>110</v>
       </c>
@@ -1948,7 +1977,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>111</v>
       </c>
@@ -1956,7 +1985,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>112</v>
       </c>
@@ -1964,7 +1993,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>113</v>
       </c>
@@ -1983,9 +2012,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
@@ -2002,7 +2031,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2019,7 +2048,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -2036,7 +2065,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -2053,7 +2082,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -2070,7 +2099,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -2087,7 +2116,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -2104,7 +2133,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -2121,7 +2150,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -2138,7 +2167,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -2155,7 +2184,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -2172,7 +2201,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -2189,7 +2218,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -2206,7 +2235,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -2223,7 +2252,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -2240,7 +2269,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -2257,7 +2286,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -2274,7 +2303,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -2291,7 +2320,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -2308,7 +2337,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2325,7 +2354,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -2342,7 +2371,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -2370,16 +2399,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P994"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="3" max="5" width="24.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
-    <col min="10" max="10" width="26.1640625" customWidth="1"/>
+    <col min="3" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>29</v>
       </c>
@@ -2411,7 +2440,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
@@ -2443,7 +2472,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>23</v>
       </c>
@@ -2475,7 +2504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>23</v>
       </c>
@@ -2507,7 +2536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>23</v>
       </c>
@@ -2540,7 +2569,7 @@
       </c>
       <c r="P5" s="9"/>
     </row>
-    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
@@ -2573,7 +2602,7 @@
       </c>
       <c r="P6" s="9"/>
     </row>
-    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
         <v>22</v>
       </c>
@@ -2606,7 +2635,7 @@
       </c>
       <c r="P7" s="9"/>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>20</v>
       </c>
@@ -2639,7 +2668,7 @@
       </c>
       <c r="P8" s="9"/>
     </row>
-    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>23</v>
       </c>
@@ -2672,7 +2701,7 @@
       </c>
       <c r="P9" s="9"/>
     </row>
-    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>23</v>
       </c>
@@ -2701,7 +2730,7 @@
       </c>
       <c r="P10" s="9"/>
     </row>
-    <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="24" t="s">
         <v>68</v>
       </c>
@@ -2734,7 +2763,7 @@
       </c>
       <c r="P11" s="9"/>
     </row>
-    <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
         <v>20</v>
       </c>
@@ -2767,7 +2796,7 @@
       </c>
       <c r="P12" s="9"/>
     </row>
-    <row r="13" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
         <v>23</v>
       </c>
@@ -2800,7 +2829,7 @@
       </c>
       <c r="P13" s="9"/>
     </row>
-    <row r="14" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
         <v>20</v>
       </c>
@@ -2833,7 +2862,7 @@
       </c>
       <c r="P14" s="9"/>
     </row>
-    <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>22</v>
       </c>
@@ -2866,7 +2895,7 @@
       </c>
       <c r="P15" s="9"/>
     </row>
-    <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
         <v>23</v>
       </c>
@@ -2899,7 +2928,7 @@
       </c>
       <c r="P16" s="9"/>
     </row>
-    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
         <v>22</v>
       </c>
@@ -2932,7 +2961,7 @@
       </c>
       <c r="P17" s="9"/>
     </row>
-    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
         <v>22</v>
       </c>
@@ -2961,7 +2990,7 @@
       </c>
       <c r="P18" s="9"/>
     </row>
-    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>22</v>
       </c>
@@ -2994,7 +3023,7 @@
       </c>
       <c r="P19" s="9"/>
     </row>
-    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="24" t="s">
         <v>22</v>
       </c>
@@ -3027,7 +3056,7 @@
       </c>
       <c r="P20" s="9"/>
     </row>
-    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="24" t="s">
         <v>22</v>
       </c>
@@ -3060,7 +3089,7 @@
       </c>
       <c r="P21" s="9"/>
     </row>
-    <row r="22" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="24" t="s">
         <v>23</v>
       </c>
@@ -3093,7 +3122,7 @@
       </c>
       <c r="P22" s="9"/>
     </row>
-    <row r="23" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
         <v>22</v>
       </c>
@@ -3120,7 +3149,7 @@
       </c>
       <c r="P23" s="9"/>
     </row>
-    <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="27" t="s">
         <v>22</v>
       </c>
@@ -3152,7 +3181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
         <v>23</v>
       </c>
@@ -3178,7 +3207,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>22</v>
       </c>
@@ -3204,7 +3233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>22</v>
       </c>
@@ -3230,7 +3259,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="20" t="s">
         <v>20</v>
       </c>
@@ -3258,7 +3287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="24" t="s">
         <v>20</v>
       </c>
@@ -3291,7 +3320,7 @@
       </c>
       <c r="P29" s="9"/>
     </row>
-    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="24" t="s">
         <v>23</v>
       </c>
@@ -3324,7 +3353,7 @@
       </c>
       <c r="P30" s="9"/>
     </row>
-    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
         <v>23</v>
       </c>
@@ -3353,7 +3382,7 @@
       </c>
       <c r="P31" s="9"/>
     </row>
-    <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="20" t="s">
         <v>23</v>
       </c>
@@ -3382,7 +3411,7 @@
       </c>
       <c r="P32" s="9"/>
     </row>
-    <row r="33" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
         <v>23</v>
       </c>
@@ -3411,7 +3440,7 @@
       </c>
       <c r="P33" s="9"/>
     </row>
-    <row r="34" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>22</v>
       </c>
@@ -3443,7 +3472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>23</v>
       </c>
@@ -3467,7 +3496,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
         <v>23</v>
       </c>
@@ -3495,7 +3524,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
         <v>23</v>
       </c>
@@ -3523,7 +3552,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="16" t="s">
         <v>20</v>
       </c>
@@ -3555,7 +3584,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="20" t="s">
         <v>23</v>
       </c>
@@ -3583,7 +3612,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="27" t="s">
         <v>23</v>
       </c>
@@ -3611,7 +3640,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="16" t="s">
         <v>23</v>
       </c>
@@ -3640,7 +3669,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="20" t="s">
         <v>23</v>
       </c>
@@ -3668,7 +3697,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="24" t="s">
         <v>23</v>
       </c>
@@ -3697,7 +3726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="27" t="s">
         <v>20</v>
       </c>
@@ -3729,7 +3758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="20" t="s">
         <v>20</v>
       </c>
@@ -3761,7 +3790,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="24" t="s">
         <v>22</v>
       </c>
@@ -3793,7 +3822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="24" t="s">
         <v>20</v>
       </c>
@@ -3825,7 +3854,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="24" t="s">
         <v>20</v>
       </c>
@@ -3857,7 +3886,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="24" t="s">
         <v>22</v>
       </c>
@@ -3889,7 +3918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="27" t="s">
         <v>22</v>
       </c>
@@ -3921,2845 +3950,4192 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J51" s="9"/>
     </row>
-    <row r="52" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J52" s="9"/>
     </row>
-    <row r="53" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J53" s="9"/>
     </row>
-    <row r="54" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J54" s="9"/>
     </row>
-    <row r="55" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J55" s="9"/>
     </row>
-    <row r="56" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J56" s="9"/>
     </row>
-    <row r="57" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J57" s="9"/>
     </row>
-    <row r="58" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J58" s="9"/>
     </row>
-    <row r="59" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J59" s="9"/>
     </row>
-    <row r="60" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J60" s="9"/>
     </row>
-    <row r="61" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J61" s="9"/>
     </row>
-    <row r="62" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J62" s="9"/>
     </row>
-    <row r="63" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J63" s="9"/>
     </row>
-    <row r="64" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J64" s="9"/>
     </row>
-    <row r="65" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="65" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J65" s="9"/>
     </row>
-    <row r="66" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="66" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J66" s="9"/>
     </row>
-    <row r="67" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="67" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J67" s="9"/>
     </row>
-    <row r="68" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="68" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J68" s="9"/>
     </row>
-    <row r="69" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J69" s="9"/>
     </row>
-    <row r="70" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="70" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J70" s="9"/>
     </row>
-    <row r="71" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="71" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J71" s="9"/>
     </row>
-    <row r="72" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="72" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J72" s="9"/>
     </row>
-    <row r="73" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="73" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J73" s="9"/>
     </row>
-    <row r="74" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="74" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J74" s="9"/>
     </row>
-    <row r="75" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="75" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J75" s="9"/>
     </row>
-    <row r="76" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J76" s="9"/>
     </row>
-    <row r="77" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J77" s="9"/>
     </row>
-    <row r="78" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J78" s="9"/>
     </row>
-    <row r="79" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J79" s="9"/>
     </row>
-    <row r="80" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J80" s="9"/>
     </row>
-    <row r="81" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="81" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J81" s="9"/>
     </row>
-    <row r="82" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="82" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J82" s="9"/>
     </row>
-    <row r="83" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="83" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J83" s="9"/>
     </row>
-    <row r="84" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="84" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J84" s="9"/>
     </row>
-    <row r="85" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="85" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J85" s="9"/>
     </row>
-    <row r="86" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="86" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J86" s="9"/>
     </row>
-    <row r="87" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="87" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J87" s="9"/>
     </row>
-    <row r="88" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="88" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J88" s="9"/>
     </row>
-    <row r="89" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="89" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J89" s="9"/>
     </row>
-    <row r="90" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="90" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J90" s="9"/>
     </row>
-    <row r="91" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="91" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J91" s="9"/>
     </row>
-    <row r="92" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="92" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J92" s="9"/>
     </row>
-    <row r="93" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="93" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J93" s="9"/>
     </row>
-    <row r="94" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="94" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J94" s="9"/>
     </row>
-    <row r="95" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="95" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J95" s="9"/>
     </row>
-    <row r="96" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="96" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J96" s="9"/>
     </row>
-    <row r="97" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="97" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J97" s="9"/>
     </row>
-    <row r="98" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="98" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J98" s="9"/>
     </row>
-    <row r="99" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="99" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J99" s="9"/>
     </row>
-    <row r="100" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="100" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J100" s="9"/>
     </row>
-    <row r="101" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="101" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J101" s="9"/>
     </row>
-    <row r="102" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="102" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J102" s="9"/>
     </row>
-    <row r="103" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="103" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J103" s="9"/>
     </row>
-    <row r="104" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="104" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J104" s="9"/>
     </row>
-    <row r="105" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="105" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J105" s="9"/>
     </row>
-    <row r="106" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="106" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J106" s="9"/>
     </row>
-    <row r="107" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="107" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J107" s="9"/>
     </row>
-    <row r="108" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="108" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J108" s="9"/>
     </row>
-    <row r="109" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="109" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J109" s="9"/>
     </row>
-    <row r="110" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="110" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J110" s="9"/>
     </row>
-    <row r="111" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="111" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J111" s="9"/>
     </row>
-    <row r="112" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="112" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J112" s="9"/>
     </row>
-    <row r="113" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="113" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J113" s="9"/>
     </row>
-    <row r="114" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="114" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J114" s="9"/>
     </row>
-    <row r="115" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="115" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J115" s="9"/>
     </row>
-    <row r="116" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="116" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J116" s="9"/>
     </row>
-    <row r="117" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="117" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J117" s="9"/>
     </row>
-    <row r="118" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="118" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J118" s="9"/>
     </row>
-    <row r="119" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="119" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J119" s="9"/>
     </row>
-    <row r="120" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="120" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J120" s="9"/>
     </row>
-    <row r="121" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="121" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J121" s="9"/>
     </row>
-    <row r="122" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="122" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J122" s="9"/>
     </row>
-    <row r="123" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="123" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J123" s="9"/>
     </row>
-    <row r="124" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="124" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J124" s="9"/>
     </row>
-    <row r="125" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="125" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J125" s="9"/>
     </row>
-    <row r="126" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="126" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J126" s="9"/>
     </row>
-    <row r="127" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="127" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J127" s="9"/>
     </row>
-    <row r="128" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="128" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J128" s="9"/>
     </row>
-    <row r="129" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="129" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J129" s="9"/>
     </row>
-    <row r="130" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="130" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J130" s="9"/>
     </row>
-    <row r="131" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="131" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J131" s="9"/>
     </row>
-    <row r="132" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="132" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J132" s="9"/>
     </row>
-    <row r="133" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="133" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J133" s="9"/>
     </row>
-    <row r="134" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="134" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J134" s="9"/>
     </row>
-    <row r="135" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="135" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J135" s="9"/>
     </row>
-    <row r="136" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="136" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J136" s="9"/>
     </row>
-    <row r="137" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="137" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J137" s="9"/>
     </row>
-    <row r="138" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="138" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J138" s="9"/>
     </row>
-    <row r="139" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="139" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J139" s="9"/>
     </row>
-    <row r="140" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="140" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J140" s="9"/>
     </row>
-    <row r="141" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="141" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J141" s="9"/>
     </row>
-    <row r="142" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="142" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J142" s="9"/>
     </row>
-    <row r="143" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="143" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J143" s="9"/>
     </row>
-    <row r="144" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="144" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J144" s="9"/>
     </row>
-    <row r="145" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="145" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J145" s="9"/>
     </row>
-    <row r="146" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="146" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J146" s="9"/>
     </row>
-    <row r="147" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="147" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J147" s="9"/>
     </row>
-    <row r="148" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="148" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J148" s="9"/>
     </row>
-    <row r="149" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="149" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J149" s="9"/>
     </row>
-    <row r="150" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="150" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J150" s="9"/>
     </row>
-    <row r="151" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="151" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J151" s="9"/>
     </row>
-    <row r="152" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="152" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J152" s="9"/>
     </row>
-    <row r="153" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="153" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J153" s="9"/>
     </row>
-    <row r="154" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="154" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J154" s="9"/>
     </row>
-    <row r="155" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="155" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J155" s="9"/>
     </row>
-    <row r="156" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="156" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J156" s="9"/>
     </row>
-    <row r="157" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="157" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J157" s="9"/>
     </row>
-    <row r="158" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="158" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J158" s="9"/>
     </row>
-    <row r="159" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="159" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J159" s="9"/>
     </row>
-    <row r="160" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="160" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J160" s="9"/>
     </row>
-    <row r="161" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="161" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J161" s="9"/>
     </row>
-    <row r="162" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="162" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J162" s="9"/>
     </row>
-    <row r="163" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="163" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J163" s="9"/>
     </row>
-    <row r="164" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="164" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J164" s="9"/>
     </row>
-    <row r="165" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="165" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J165" s="9"/>
     </row>
-    <row r="166" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="166" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J166" s="9"/>
     </row>
-    <row r="167" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="167" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J167" s="9"/>
     </row>
-    <row r="168" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="168" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J168" s="9"/>
     </row>
-    <row r="169" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="169" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J169" s="9"/>
     </row>
-    <row r="170" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="170" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J170" s="9"/>
     </row>
-    <row r="171" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="171" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J171" s="9"/>
     </row>
-    <row r="172" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="172" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J172" s="9"/>
     </row>
-    <row r="173" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="173" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J173" s="9"/>
     </row>
-    <row r="174" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="174" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J174" s="9"/>
     </row>
-    <row r="175" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="175" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J175" s="9"/>
     </row>
-    <row r="176" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="176" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J176" s="9"/>
     </row>
-    <row r="177" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="177" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J177" s="9"/>
     </row>
-    <row r="178" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="178" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J178" s="9"/>
     </row>
-    <row r="179" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="179" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J179" s="9"/>
     </row>
-    <row r="180" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="180" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J180" s="9"/>
     </row>
-    <row r="181" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="181" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J181" s="9"/>
     </row>
-    <row r="182" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="182" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J182" s="9"/>
     </row>
-    <row r="183" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="183" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J183" s="9"/>
     </row>
-    <row r="184" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="184" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J184" s="9"/>
     </row>
-    <row r="185" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="185" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J185" s="9"/>
     </row>
-    <row r="186" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="186" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J186" s="9"/>
     </row>
-    <row r="187" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="187" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J187" s="9"/>
     </row>
-    <row r="188" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="188" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J188" s="9"/>
     </row>
-    <row r="189" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="189" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J189" s="9"/>
     </row>
-    <row r="190" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="190" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J190" s="9"/>
     </row>
-    <row r="191" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="191" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J191" s="9"/>
     </row>
-    <row r="192" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="192" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J192" s="9"/>
     </row>
-    <row r="193" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="193" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J193" s="9"/>
     </row>
-    <row r="194" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="194" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J194" s="9"/>
     </row>
-    <row r="195" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="195" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J195" s="9"/>
     </row>
-    <row r="196" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="196" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J196" s="9"/>
     </row>
-    <row r="197" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="197" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J197" s="9"/>
     </row>
-    <row r="198" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="198" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J198" s="9"/>
     </row>
-    <row r="199" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="199" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J199" s="9"/>
     </row>
-    <row r="200" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="200" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J200" s="9"/>
     </row>
-    <row r="201" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="201" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J201" s="9"/>
     </row>
-    <row r="202" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="202" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J202" s="9"/>
     </row>
-    <row r="203" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="203" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J203" s="9"/>
     </row>
-    <row r="204" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="204" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J204" s="9"/>
     </row>
-    <row r="205" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="205" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J205" s="9"/>
     </row>
-    <row r="206" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="206" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J206" s="9"/>
     </row>
-    <row r="207" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="207" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J207" s="9"/>
     </row>
-    <row r="208" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="208" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J208" s="9"/>
     </row>
-    <row r="209" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="209" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J209" s="9"/>
     </row>
-    <row r="210" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="210" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J210" s="9"/>
     </row>
-    <row r="211" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="211" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J211" s="9"/>
     </row>
-    <row r="212" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="212" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J212" s="9"/>
     </row>
-    <row r="213" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="213" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J213" s="9"/>
     </row>
-    <row r="214" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="214" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J214" s="9"/>
     </row>
-    <row r="215" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="215" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J215" s="9"/>
     </row>
-    <row r="216" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="216" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J216" s="9"/>
     </row>
-    <row r="217" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="217" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J217" s="9"/>
     </row>
-    <row r="218" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="218" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J218" s="9"/>
     </row>
-    <row r="219" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="219" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J219" s="9"/>
     </row>
-    <row r="220" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="220" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J220" s="9"/>
     </row>
-    <row r="221" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="221" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J221" s="9"/>
     </row>
-    <row r="222" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="222" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J222" s="9"/>
     </row>
-    <row r="223" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="223" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J223" s="9"/>
     </row>
-    <row r="224" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="224" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J224" s="9"/>
     </row>
-    <row r="225" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="225" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J225" s="9"/>
     </row>
-    <row r="226" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="226" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J226" s="9"/>
     </row>
-    <row r="227" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="227" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J227" s="9"/>
     </row>
-    <row r="228" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="228" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J228" s="9"/>
     </row>
-    <row r="229" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="229" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J229" s="9"/>
     </row>
-    <row r="230" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="230" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J230" s="9"/>
     </row>
-    <row r="231" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="231" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J231" s="9"/>
     </row>
-    <row r="232" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="232" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J232" s="9"/>
     </row>
-    <row r="233" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="233" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J233" s="9"/>
     </row>
-    <row r="234" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="234" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J234" s="9"/>
     </row>
-    <row r="235" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="235" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J235" s="9"/>
     </row>
-    <row r="236" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="236" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J236" s="9"/>
     </row>
-    <row r="237" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="237" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J237" s="9"/>
     </row>
-    <row r="238" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="238" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J238" s="9"/>
     </row>
-    <row r="239" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="239" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J239" s="9"/>
     </row>
-    <row r="240" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="240" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J240" s="9"/>
     </row>
-    <row r="241" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="241" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J241" s="9"/>
     </row>
-    <row r="242" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="242" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J242" s="9"/>
     </row>
-    <row r="243" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="243" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J243" s="9"/>
     </row>
-    <row r="244" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="244" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J244" s="9"/>
     </row>
-    <row r="245" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="245" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J245" s="9"/>
     </row>
-    <row r="246" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="246" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J246" s="9"/>
     </row>
-    <row r="247" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="247" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J247" s="9"/>
     </row>
-    <row r="248" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="248" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J248" s="9"/>
     </row>
-    <row r="249" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="249" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J249" s="9"/>
     </row>
-    <row r="250" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="250" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J250" s="9"/>
     </row>
-    <row r="251" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="251" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J251" s="9"/>
     </row>
-    <row r="252" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="252" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J252" s="9"/>
     </row>
-    <row r="253" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="253" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J253" s="9"/>
     </row>
-    <row r="254" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="254" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J254" s="9"/>
     </row>
-    <row r="255" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="255" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J255" s="9"/>
     </row>
-    <row r="256" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="256" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J256" s="9"/>
     </row>
-    <row r="257" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="257" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J257" s="9"/>
     </row>
-    <row r="258" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="258" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J258" s="9"/>
     </row>
-    <row r="259" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="259" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J259" s="9"/>
     </row>
-    <row r="260" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="260" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J260" s="9"/>
     </row>
-    <row r="261" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="261" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J261" s="9"/>
     </row>
-    <row r="262" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="262" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J262" s="9"/>
     </row>
-    <row r="263" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="263" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J263" s="9"/>
     </row>
-    <row r="264" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="264" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J264" s="9"/>
     </row>
-    <row r="265" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="265" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J265" s="9"/>
     </row>
-    <row r="266" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="266" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J266" s="9"/>
     </row>
-    <row r="267" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="267" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J267" s="9"/>
     </row>
-    <row r="268" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="268" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J268" s="9"/>
     </row>
-    <row r="269" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="269" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J269" s="9"/>
     </row>
-    <row r="270" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="270" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J270" s="9"/>
     </row>
-    <row r="271" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="271" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J271" s="9"/>
     </row>
-    <row r="272" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="272" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J272" s="9"/>
     </row>
-    <row r="273" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="273" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J273" s="9"/>
     </row>
-    <row r="274" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="274" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J274" s="9"/>
     </row>
-    <row r="275" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="275" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J275" s="9"/>
     </row>
-    <row r="276" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="276" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J276" s="9"/>
     </row>
-    <row r="277" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="277" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J277" s="9"/>
     </row>
-    <row r="278" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="278" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J278" s="9"/>
     </row>
-    <row r="279" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="279" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J279" s="9"/>
     </row>
-    <row r="280" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="280" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J280" s="9"/>
     </row>
-    <row r="281" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="281" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J281" s="9"/>
     </row>
-    <row r="282" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="282" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J282" s="9"/>
     </row>
-    <row r="283" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="283" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J283" s="9"/>
     </row>
-    <row r="284" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="284" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J284" s="9"/>
     </row>
-    <row r="285" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="285" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J285" s="9"/>
     </row>
-    <row r="286" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="286" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J286" s="9"/>
     </row>
-    <row r="287" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="287" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J287" s="9"/>
     </row>
-    <row r="288" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="288" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J288" s="9"/>
     </row>
-    <row r="289" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="289" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J289" s="9"/>
     </row>
-    <row r="290" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="290" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J290" s="9"/>
     </row>
-    <row r="291" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="291" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J291" s="9"/>
     </row>
-    <row r="292" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="292" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J292" s="9"/>
     </row>
-    <row r="293" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="293" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J293" s="9"/>
     </row>
-    <row r="294" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="294" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J294" s="9"/>
     </row>
-    <row r="295" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="295" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J295" s="9"/>
     </row>
-    <row r="296" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="296" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J296" s="9"/>
     </row>
-    <row r="297" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="297" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J297" s="9"/>
     </row>
-    <row r="298" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="298" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J298" s="9"/>
     </row>
-    <row r="299" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="299" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J299" s="9"/>
     </row>
-    <row r="300" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="300" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J300" s="9"/>
     </row>
-    <row r="301" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="301" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J301" s="9"/>
     </row>
-    <row r="302" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="302" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J302" s="9"/>
     </row>
-    <row r="303" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="303" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J303" s="9"/>
     </row>
-    <row r="304" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="304" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J304" s="9"/>
     </row>
-    <row r="305" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="305" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J305" s="9"/>
     </row>
-    <row r="306" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="306" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J306" s="9"/>
     </row>
-    <row r="307" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="307" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J307" s="9"/>
     </row>
-    <row r="308" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="308" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J308" s="9"/>
     </row>
-    <row r="309" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="309" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J309" s="9"/>
     </row>
-    <row r="310" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="310" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J310" s="9"/>
     </row>
-    <row r="311" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="311" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J311" s="9"/>
     </row>
-    <row r="312" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="312" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J312" s="9"/>
     </row>
-    <row r="313" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="313" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J313" s="9"/>
     </row>
-    <row r="314" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="314" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J314" s="9"/>
     </row>
-    <row r="315" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="315" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J315" s="9"/>
     </row>
-    <row r="316" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="316" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J316" s="9"/>
     </row>
-    <row r="317" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="317" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J317" s="9"/>
     </row>
-    <row r="318" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="318" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J318" s="9"/>
     </row>
-    <row r="319" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="319" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J319" s="9"/>
     </row>
-    <row r="320" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="320" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J320" s="9"/>
     </row>
-    <row r="321" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="321" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J321" s="9"/>
     </row>
-    <row r="322" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="322" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J322" s="9"/>
     </row>
-    <row r="323" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="323" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J323" s="9"/>
     </row>
-    <row r="324" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="324" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J324" s="9"/>
     </row>
-    <row r="325" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="325" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J325" s="9"/>
     </row>
-    <row r="326" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="326" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J326" s="9"/>
     </row>
-    <row r="327" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="327" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J327" s="9"/>
     </row>
-    <row r="328" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="328" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J328" s="9"/>
     </row>
-    <row r="329" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="329" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J329" s="9"/>
     </row>
-    <row r="330" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="330" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J330" s="9"/>
     </row>
-    <row r="331" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="331" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J331" s="9"/>
     </row>
-    <row r="332" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="332" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J332" s="9"/>
     </row>
-    <row r="333" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="333" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J333" s="9"/>
     </row>
-    <row r="334" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="334" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J334" s="9"/>
     </row>
-    <row r="335" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="335" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J335" s="9"/>
     </row>
-    <row r="336" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="336" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J336" s="9"/>
     </row>
-    <row r="337" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="337" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J337" s="9"/>
     </row>
-    <row r="338" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="338" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J338" s="9"/>
     </row>
-    <row r="339" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="339" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J339" s="9"/>
     </row>
-    <row r="340" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="340" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J340" s="9"/>
     </row>
-    <row r="341" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="341" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J341" s="9"/>
     </row>
-    <row r="342" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="342" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J342" s="9"/>
     </row>
-    <row r="343" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="343" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J343" s="9"/>
     </row>
-    <row r="344" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="344" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J344" s="9"/>
     </row>
-    <row r="345" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="345" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J345" s="9"/>
     </row>
-    <row r="346" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="346" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J346" s="9"/>
     </row>
-    <row r="347" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="347" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J347" s="9"/>
     </row>
-    <row r="348" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="348" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J348" s="9"/>
     </row>
-    <row r="349" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="349" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J349" s="9"/>
     </row>
-    <row r="350" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="350" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J350" s="9"/>
     </row>
-    <row r="351" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="351" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J351" s="9"/>
     </row>
-    <row r="352" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="352" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J352" s="9"/>
     </row>
-    <row r="353" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="353" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J353" s="9"/>
     </row>
-    <row r="354" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="354" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J354" s="9"/>
     </row>
-    <row r="355" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="355" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J355" s="9"/>
     </row>
-    <row r="356" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="356" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J356" s="9"/>
     </row>
-    <row r="357" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="357" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J357" s="9"/>
     </row>
-    <row r="358" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="358" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J358" s="9"/>
     </row>
-    <row r="359" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="359" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J359" s="9"/>
     </row>
-    <row r="360" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="360" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J360" s="9"/>
     </row>
-    <row r="361" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="361" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J361" s="9"/>
     </row>
-    <row r="362" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="362" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J362" s="9"/>
     </row>
-    <row r="363" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="363" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J363" s="9"/>
     </row>
-    <row r="364" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="364" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J364" s="9"/>
     </row>
-    <row r="365" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="365" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J365" s="9"/>
     </row>
-    <row r="366" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="366" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J366" s="9"/>
     </row>
-    <row r="367" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="367" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J367" s="9"/>
     </row>
-    <row r="368" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="368" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J368" s="9"/>
     </row>
-    <row r="369" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="369" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J369" s="9"/>
     </row>
-    <row r="370" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="370" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J370" s="9"/>
     </row>
-    <row r="371" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="371" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J371" s="9"/>
     </row>
-    <row r="372" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="372" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J372" s="9"/>
     </row>
-    <row r="373" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="373" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J373" s="9"/>
     </row>
-    <row r="374" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="374" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J374" s="9"/>
     </row>
-    <row r="375" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="375" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J375" s="9"/>
     </row>
-    <row r="376" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="376" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J376" s="9"/>
     </row>
-    <row r="377" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="377" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J377" s="9"/>
     </row>
-    <row r="378" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="378" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J378" s="9"/>
     </row>
-    <row r="379" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="379" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J379" s="9"/>
     </row>
-    <row r="380" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="380" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J380" s="9"/>
     </row>
-    <row r="381" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="381" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J381" s="9"/>
     </row>
-    <row r="382" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="382" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J382" s="9"/>
     </row>
-    <row r="383" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="383" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J383" s="9"/>
     </row>
-    <row r="384" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="384" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J384" s="9"/>
     </row>
-    <row r="385" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="385" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J385" s="9"/>
     </row>
-    <row r="386" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="386" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J386" s="9"/>
     </row>
-    <row r="387" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="387" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J387" s="9"/>
     </row>
-    <row r="388" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="388" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J388" s="9"/>
     </row>
-    <row r="389" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="389" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J389" s="9"/>
     </row>
-    <row r="390" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="390" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J390" s="9"/>
     </row>
-    <row r="391" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="391" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J391" s="9"/>
     </row>
-    <row r="392" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="392" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J392" s="9"/>
     </row>
-    <row r="393" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="393" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J393" s="9"/>
     </row>
-    <row r="394" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="394" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J394" s="9"/>
     </row>
-    <row r="395" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="395" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J395" s="9"/>
     </row>
-    <row r="396" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="396" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J396" s="9"/>
     </row>
-    <row r="397" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="397" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J397" s="9"/>
     </row>
-    <row r="398" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="398" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J398" s="9"/>
     </row>
-    <row r="399" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="399" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J399" s="9"/>
     </row>
-    <row r="400" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="400" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J400" s="9"/>
     </row>
-    <row r="401" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="401" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J401" s="9"/>
     </row>
-    <row r="402" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="402" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J402" s="9"/>
     </row>
-    <row r="403" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="403" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J403" s="9"/>
     </row>
-    <row r="404" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="404" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J404" s="9"/>
     </row>
-    <row r="405" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="405" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J405" s="9"/>
     </row>
-    <row r="406" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="406" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J406" s="9"/>
     </row>
-    <row r="407" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="407" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J407" s="9"/>
     </row>
-    <row r="408" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="408" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J408" s="9"/>
     </row>
-    <row r="409" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="409" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J409" s="9"/>
     </row>
-    <row r="410" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="410" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J410" s="9"/>
     </row>
-    <row r="411" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="411" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J411" s="9"/>
     </row>
-    <row r="412" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="412" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J412" s="9"/>
     </row>
-    <row r="413" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="413" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J413" s="9"/>
     </row>
-    <row r="414" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="414" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J414" s="9"/>
     </row>
-    <row r="415" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="415" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J415" s="9"/>
     </row>
-    <row r="416" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="416" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J416" s="9"/>
     </row>
-    <row r="417" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="417" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J417" s="9"/>
     </row>
-    <row r="418" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="418" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J418" s="9"/>
     </row>
-    <row r="419" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="419" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J419" s="9"/>
     </row>
-    <row r="420" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="420" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J420" s="9"/>
     </row>
-    <row r="421" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="421" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J421" s="9"/>
     </row>
-    <row r="422" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="422" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J422" s="9"/>
     </row>
-    <row r="423" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="423" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J423" s="9"/>
     </row>
-    <row r="424" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="424" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J424" s="9"/>
     </row>
-    <row r="425" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="425" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J425" s="9"/>
     </row>
-    <row r="426" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="426" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J426" s="9"/>
     </row>
-    <row r="427" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="427" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J427" s="9"/>
     </row>
-    <row r="428" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="428" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J428" s="9"/>
     </row>
-    <row r="429" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="429" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J429" s="9"/>
     </row>
-    <row r="430" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="430" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J430" s="9"/>
     </row>
-    <row r="431" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="431" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J431" s="9"/>
     </row>
-    <row r="432" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="432" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J432" s="9"/>
     </row>
-    <row r="433" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="433" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J433" s="9"/>
     </row>
-    <row r="434" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="434" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J434" s="9"/>
     </row>
-    <row r="435" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="435" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J435" s="9"/>
     </row>
-    <row r="436" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="436" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J436" s="9"/>
     </row>
-    <row r="437" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="437" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J437" s="9"/>
     </row>
-    <row r="438" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="438" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J438" s="9"/>
     </row>
-    <row r="439" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="439" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J439" s="9"/>
     </row>
-    <row r="440" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="440" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J440" s="9"/>
     </row>
-    <row r="441" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="441" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J441" s="9"/>
     </row>
-    <row r="442" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="442" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J442" s="9"/>
     </row>
-    <row r="443" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="443" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J443" s="9"/>
     </row>
-    <row r="444" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="444" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J444" s="9"/>
     </row>
-    <row r="445" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="445" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J445" s="9"/>
     </row>
-    <row r="446" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="446" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J446" s="9"/>
     </row>
-    <row r="447" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="447" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J447" s="9"/>
     </row>
-    <row r="448" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="448" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J448" s="9"/>
     </row>
-    <row r="449" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="449" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J449" s="9"/>
     </row>
-    <row r="450" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="450" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J450" s="9"/>
     </row>
-    <row r="451" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="451" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J451" s="9"/>
     </row>
-    <row r="452" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="452" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J452" s="9"/>
     </row>
-    <row r="453" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="453" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J453" s="9"/>
     </row>
-    <row r="454" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="454" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J454" s="9"/>
     </row>
-    <row r="455" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="455" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J455" s="9"/>
     </row>
-    <row r="456" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="456" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J456" s="9"/>
     </row>
-    <row r="457" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="457" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J457" s="9"/>
     </row>
-    <row r="458" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="458" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J458" s="9"/>
     </row>
-    <row r="459" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="459" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J459" s="9"/>
     </row>
-    <row r="460" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="460" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J460" s="9"/>
     </row>
-    <row r="461" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="461" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J461" s="9"/>
     </row>
-    <row r="462" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="462" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J462" s="9"/>
     </row>
-    <row r="463" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="463" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J463" s="9"/>
     </row>
-    <row r="464" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="464" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J464" s="9"/>
     </row>
-    <row r="465" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="465" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J465" s="9"/>
     </row>
-    <row r="466" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="466" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J466" s="9"/>
     </row>
-    <row r="467" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="467" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J467" s="9"/>
     </row>
-    <row r="468" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="468" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J468" s="9"/>
     </row>
-    <row r="469" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="469" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J469" s="9"/>
     </row>
-    <row r="470" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="470" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J470" s="9"/>
     </row>
-    <row r="471" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="471" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J471" s="9"/>
     </row>
-    <row r="472" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="472" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J472" s="9"/>
     </row>
-    <row r="473" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="473" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J473" s="9"/>
     </row>
-    <row r="474" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="474" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J474" s="9"/>
     </row>
-    <row r="475" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="475" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J475" s="9"/>
     </row>
-    <row r="476" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="476" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J476" s="9"/>
     </row>
-    <row r="477" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="477" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J477" s="9"/>
     </row>
-    <row r="478" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="478" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J478" s="9"/>
     </row>
-    <row r="479" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="479" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J479" s="9"/>
     </row>
-    <row r="480" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="480" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J480" s="9"/>
     </row>
-    <row r="481" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="481" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J481" s="9"/>
     </row>
-    <row r="482" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="482" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J482" s="9"/>
     </row>
-    <row r="483" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="483" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J483" s="9"/>
     </row>
-    <row r="484" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="484" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J484" s="9"/>
     </row>
-    <row r="485" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="485" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J485" s="9"/>
     </row>
-    <row r="486" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="486" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J486" s="9"/>
     </row>
-    <row r="487" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="487" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J487" s="9"/>
     </row>
-    <row r="488" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="488" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J488" s="9"/>
     </row>
-    <row r="489" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="489" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J489" s="9"/>
     </row>
-    <row r="490" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="490" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J490" s="9"/>
     </row>
-    <row r="491" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="491" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J491" s="9"/>
     </row>
-    <row r="492" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="492" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J492" s="9"/>
     </row>
-    <row r="493" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="493" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J493" s="9"/>
     </row>
-    <row r="494" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="494" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J494" s="9"/>
     </row>
-    <row r="495" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="495" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J495" s="9"/>
     </row>
-    <row r="496" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="496" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J496" s="9"/>
     </row>
-    <row r="497" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="497" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J497" s="9"/>
     </row>
-    <row r="498" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="498" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J498" s="9"/>
     </row>
-    <row r="499" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="499" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J499" s="9"/>
     </row>
-    <row r="500" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="500" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J500" s="9"/>
     </row>
-    <row r="501" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="501" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J501" s="9"/>
     </row>
-    <row r="502" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="502" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J502" s="9"/>
     </row>
-    <row r="503" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="503" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J503" s="9"/>
     </row>
-    <row r="504" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="504" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J504" s="9"/>
     </row>
-    <row r="505" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="505" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J505" s="9"/>
     </row>
-    <row r="506" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="506" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J506" s="9"/>
     </row>
-    <row r="507" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="507" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J507" s="9"/>
     </row>
-    <row r="508" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="508" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J508" s="9"/>
     </row>
-    <row r="509" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="509" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J509" s="9"/>
     </row>
-    <row r="510" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="510" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J510" s="9"/>
     </row>
-    <row r="511" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="511" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J511" s="9"/>
     </row>
-    <row r="512" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="512" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J512" s="9"/>
     </row>
-    <row r="513" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="513" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J513" s="9"/>
     </row>
-    <row r="514" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="514" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J514" s="9"/>
     </row>
-    <row r="515" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="515" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J515" s="9"/>
     </row>
-    <row r="516" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="516" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J516" s="9"/>
     </row>
-    <row r="517" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="517" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J517" s="9"/>
     </row>
-    <row r="518" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="518" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J518" s="9"/>
     </row>
-    <row r="519" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="519" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J519" s="9"/>
     </row>
-    <row r="520" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="520" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J520" s="9"/>
     </row>
-    <row r="521" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="521" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J521" s="9"/>
     </row>
-    <row r="522" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="522" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J522" s="9"/>
     </row>
-    <row r="523" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="523" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J523" s="9"/>
     </row>
-    <row r="524" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="524" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J524" s="9"/>
     </row>
-    <row r="525" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="525" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J525" s="9"/>
     </row>
-    <row r="526" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="526" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J526" s="9"/>
     </row>
-    <row r="527" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="527" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J527" s="9"/>
     </row>
-    <row r="528" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="528" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J528" s="9"/>
     </row>
-    <row r="529" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="529" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J529" s="9"/>
     </row>
-    <row r="530" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="530" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J530" s="9"/>
     </row>
-    <row r="531" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="531" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J531" s="9"/>
     </row>
-    <row r="532" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="532" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J532" s="9"/>
     </row>
-    <row r="533" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="533" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J533" s="9"/>
     </row>
-    <row r="534" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="534" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J534" s="9"/>
     </row>
-    <row r="535" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="535" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J535" s="9"/>
     </row>
-    <row r="536" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="536" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J536" s="9"/>
     </row>
-    <row r="537" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="537" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J537" s="9"/>
     </row>
-    <row r="538" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="538" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J538" s="9"/>
     </row>
-    <row r="539" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="539" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J539" s="9"/>
     </row>
-    <row r="540" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="540" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J540" s="9"/>
     </row>
-    <row r="541" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="541" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J541" s="9"/>
     </row>
-    <row r="542" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="542" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J542" s="9"/>
     </row>
-    <row r="543" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="543" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J543" s="9"/>
     </row>
-    <row r="544" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="544" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J544" s="9"/>
     </row>
-    <row r="545" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="545" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J545" s="9"/>
     </row>
-    <row r="546" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="546" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J546" s="9"/>
     </row>
-    <row r="547" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="547" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J547" s="9"/>
     </row>
-    <row r="548" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="548" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J548" s="9"/>
     </row>
-    <row r="549" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="549" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J549" s="9"/>
     </row>
-    <row r="550" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="550" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J550" s="9"/>
     </row>
-    <row r="551" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="551" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J551" s="9"/>
     </row>
-    <row r="552" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="552" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J552" s="9"/>
     </row>
-    <row r="553" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="553" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J553" s="9"/>
     </row>
-    <row r="554" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="554" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J554" s="9"/>
     </row>
-    <row r="555" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="555" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J555" s="9"/>
     </row>
-    <row r="556" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="556" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J556" s="9"/>
     </row>
-    <row r="557" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="557" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J557" s="9"/>
     </row>
-    <row r="558" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="558" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J558" s="9"/>
     </row>
-    <row r="559" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="559" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J559" s="9"/>
     </row>
-    <row r="560" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="560" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J560" s="9"/>
     </row>
-    <row r="561" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="561" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J561" s="9"/>
     </row>
-    <row r="562" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="562" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J562" s="9"/>
     </row>
-    <row r="563" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="563" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J563" s="9"/>
     </row>
-    <row r="564" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="564" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J564" s="9"/>
     </row>
-    <row r="565" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="565" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J565" s="9"/>
     </row>
-    <row r="566" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="566" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J566" s="9"/>
     </row>
-    <row r="567" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="567" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J567" s="9"/>
     </row>
-    <row r="568" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="568" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J568" s="9"/>
     </row>
-    <row r="569" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="569" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J569" s="9"/>
     </row>
-    <row r="570" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="570" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J570" s="9"/>
     </row>
-    <row r="571" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="571" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J571" s="9"/>
     </row>
-    <row r="572" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="572" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J572" s="9"/>
     </row>
-    <row r="573" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="573" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J573" s="9"/>
     </row>
-    <row r="574" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="574" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J574" s="9"/>
     </row>
-    <row r="575" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="575" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J575" s="9"/>
     </row>
-    <row r="576" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="576" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J576" s="9"/>
     </row>
-    <row r="577" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="577" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J577" s="9"/>
     </row>
-    <row r="578" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="578" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J578" s="9"/>
     </row>
-    <row r="579" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="579" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J579" s="9"/>
     </row>
-    <row r="580" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="580" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J580" s="9"/>
     </row>
-    <row r="581" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="581" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J581" s="9"/>
     </row>
-    <row r="582" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="582" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J582" s="9"/>
     </row>
-    <row r="583" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="583" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J583" s="9"/>
     </row>
-    <row r="584" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="584" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J584" s="9"/>
     </row>
-    <row r="585" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="585" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J585" s="9"/>
     </row>
-    <row r="586" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="586" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J586" s="9"/>
     </row>
-    <row r="587" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="587" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J587" s="9"/>
     </row>
-    <row r="588" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="588" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J588" s="9"/>
     </row>
-    <row r="589" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="589" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J589" s="9"/>
     </row>
-    <row r="590" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="590" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J590" s="9"/>
     </row>
-    <row r="591" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="591" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J591" s="9"/>
     </row>
-    <row r="592" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="592" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J592" s="9"/>
     </row>
-    <row r="593" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="593" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J593" s="9"/>
     </row>
-    <row r="594" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="594" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J594" s="9"/>
     </row>
-    <row r="595" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="595" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J595" s="9"/>
     </row>
-    <row r="596" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="596" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J596" s="9"/>
     </row>
-    <row r="597" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="597" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J597" s="9"/>
     </row>
-    <row r="598" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="598" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J598" s="9"/>
     </row>
-    <row r="599" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="599" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J599" s="9"/>
     </row>
-    <row r="600" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="600" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J600" s="9"/>
     </row>
-    <row r="601" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="601" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J601" s="9"/>
     </row>
-    <row r="602" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="602" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J602" s="9"/>
     </row>
-    <row r="603" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="603" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J603" s="9"/>
     </row>
-    <row r="604" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="604" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J604" s="9"/>
     </row>
-    <row r="605" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="605" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J605" s="9"/>
     </row>
-    <row r="606" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="606" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J606" s="9"/>
     </row>
-    <row r="607" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="607" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J607" s="9"/>
     </row>
-    <row r="608" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="608" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J608" s="9"/>
     </row>
-    <row r="609" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="609" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J609" s="9"/>
     </row>
-    <row r="610" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="610" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J610" s="9"/>
     </row>
-    <row r="611" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="611" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J611" s="9"/>
     </row>
-    <row r="612" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="612" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J612" s="9"/>
     </row>
-    <row r="613" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="613" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J613" s="9"/>
     </row>
-    <row r="614" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="614" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J614" s="9"/>
     </row>
-    <row r="615" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="615" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J615" s="9"/>
     </row>
-    <row r="616" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="616" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J616" s="9"/>
     </row>
-    <row r="617" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="617" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J617" s="9"/>
     </row>
-    <row r="618" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="618" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J618" s="9"/>
     </row>
-    <row r="619" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="619" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J619" s="9"/>
     </row>
-    <row r="620" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="620" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J620" s="9"/>
     </row>
-    <row r="621" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="621" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J621" s="9"/>
     </row>
-    <row r="622" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="622" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J622" s="9"/>
     </row>
-    <row r="623" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="623" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J623" s="9"/>
     </row>
-    <row r="624" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="624" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J624" s="9"/>
     </row>
-    <row r="625" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="625" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J625" s="9"/>
     </row>
-    <row r="626" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="626" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J626" s="9"/>
     </row>
-    <row r="627" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="627" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J627" s="9"/>
     </row>
-    <row r="628" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="628" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J628" s="9"/>
     </row>
-    <row r="629" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="629" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J629" s="9"/>
     </row>
-    <row r="630" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="630" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J630" s="9"/>
     </row>
-    <row r="631" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="631" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J631" s="9"/>
     </row>
-    <row r="632" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="632" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J632" s="9"/>
     </row>
-    <row r="633" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="633" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J633" s="9"/>
     </row>
-    <row r="634" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="634" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J634" s="9"/>
     </row>
-    <row r="635" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="635" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J635" s="9"/>
     </row>
-    <row r="636" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="636" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J636" s="9"/>
     </row>
-    <row r="637" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="637" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J637" s="9"/>
     </row>
-    <row r="638" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="638" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J638" s="9"/>
     </row>
-    <row r="639" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="639" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J639" s="9"/>
     </row>
-    <row r="640" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="640" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J640" s="9"/>
     </row>
-    <row r="641" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="641" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J641" s="9"/>
     </row>
-    <row r="642" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="642" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J642" s="9"/>
     </row>
-    <row r="643" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="643" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J643" s="9"/>
     </row>
-    <row r="644" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="644" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J644" s="9"/>
     </row>
-    <row r="645" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="645" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J645" s="9"/>
     </row>
-    <row r="646" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="646" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J646" s="9"/>
     </row>
-    <row r="647" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="647" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J647" s="9"/>
     </row>
-    <row r="648" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="648" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J648" s="9"/>
     </row>
-    <row r="649" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="649" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J649" s="9"/>
     </row>
-    <row r="650" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="650" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J650" s="9"/>
     </row>
-    <row r="651" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="651" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J651" s="9"/>
     </row>
-    <row r="652" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="652" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J652" s="9"/>
     </row>
-    <row r="653" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="653" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J653" s="9"/>
     </row>
-    <row r="654" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="654" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J654" s="9"/>
     </row>
-    <row r="655" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="655" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J655" s="9"/>
     </row>
-    <row r="656" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="656" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J656" s="9"/>
     </row>
-    <row r="657" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="657" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J657" s="9"/>
     </row>
-    <row r="658" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="658" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J658" s="9"/>
     </row>
-    <row r="659" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="659" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J659" s="9"/>
     </row>
-    <row r="660" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="660" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J660" s="9"/>
     </row>
-    <row r="661" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="661" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J661" s="9"/>
     </row>
-    <row r="662" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="662" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J662" s="9"/>
     </row>
-    <row r="663" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="663" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J663" s="9"/>
     </row>
-    <row r="664" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="664" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J664" s="9"/>
     </row>
-    <row r="665" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="665" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J665" s="9"/>
     </row>
-    <row r="666" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="666" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J666" s="9"/>
     </row>
-    <row r="667" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="667" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J667" s="9"/>
     </row>
-    <row r="668" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="668" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J668" s="9"/>
     </row>
-    <row r="669" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="669" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J669" s="9"/>
     </row>
-    <row r="670" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="670" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J670" s="9"/>
     </row>
-    <row r="671" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="671" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J671" s="9"/>
     </row>
-    <row r="672" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="672" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J672" s="9"/>
     </row>
-    <row r="673" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="673" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J673" s="9"/>
     </row>
-    <row r="674" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="674" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J674" s="9"/>
     </row>
-    <row r="675" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="675" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J675" s="9"/>
     </row>
-    <row r="676" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="676" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J676" s="9"/>
     </row>
-    <row r="677" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="677" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J677" s="9"/>
     </row>
-    <row r="678" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="678" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J678" s="9"/>
     </row>
-    <row r="679" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="679" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J679" s="9"/>
     </row>
-    <row r="680" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="680" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J680" s="9"/>
     </row>
-    <row r="681" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="681" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J681" s="9"/>
     </row>
-    <row r="682" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="682" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J682" s="9"/>
     </row>
-    <row r="683" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="683" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J683" s="9"/>
     </row>
-    <row r="684" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="684" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J684" s="9"/>
     </row>
-    <row r="685" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="685" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J685" s="9"/>
     </row>
-    <row r="686" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="686" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J686" s="9"/>
     </row>
-    <row r="687" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="687" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J687" s="9"/>
     </row>
-    <row r="688" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="688" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J688" s="9"/>
     </row>
-    <row r="689" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="689" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J689" s="9"/>
     </row>
-    <row r="690" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="690" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J690" s="9"/>
     </row>
-    <row r="691" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="691" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J691" s="9"/>
     </row>
-    <row r="692" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="692" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J692" s="9"/>
     </row>
-    <row r="693" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="693" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J693" s="9"/>
     </row>
-    <row r="694" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="694" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J694" s="9"/>
     </row>
-    <row r="695" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="695" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J695" s="9"/>
     </row>
-    <row r="696" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="696" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J696" s="9"/>
     </row>
-    <row r="697" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="697" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J697" s="9"/>
     </row>
-    <row r="698" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="698" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J698" s="9"/>
     </row>
-    <row r="699" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="699" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J699" s="9"/>
     </row>
-    <row r="700" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="700" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J700" s="9"/>
     </row>
-    <row r="701" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="701" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J701" s="9"/>
     </row>
-    <row r="702" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="702" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J702" s="9"/>
     </row>
-    <row r="703" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="703" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J703" s="9"/>
     </row>
-    <row r="704" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="704" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J704" s="9"/>
     </row>
-    <row r="705" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="705" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J705" s="9"/>
     </row>
-    <row r="706" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="706" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J706" s="9"/>
     </row>
-    <row r="707" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="707" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J707" s="9"/>
     </row>
-    <row r="708" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="708" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J708" s="9"/>
     </row>
-    <row r="709" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="709" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J709" s="9"/>
     </row>
-    <row r="710" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="710" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J710" s="9"/>
     </row>
-    <row r="711" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="711" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J711" s="9"/>
     </row>
-    <row r="712" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="712" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J712" s="9"/>
     </row>
-    <row r="713" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="713" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J713" s="9"/>
     </row>
-    <row r="714" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="714" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J714" s="9"/>
     </row>
-    <row r="715" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="715" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J715" s="9"/>
     </row>
-    <row r="716" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="716" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J716" s="9"/>
     </row>
-    <row r="717" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="717" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J717" s="9"/>
     </row>
-    <row r="718" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="718" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J718" s="9"/>
     </row>
-    <row r="719" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="719" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J719" s="9"/>
     </row>
-    <row r="720" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="720" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J720" s="9"/>
     </row>
-    <row r="721" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="721" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J721" s="9"/>
     </row>
-    <row r="722" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="722" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J722" s="9"/>
     </row>
-    <row r="723" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="723" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J723" s="9"/>
     </row>
-    <row r="724" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="724" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J724" s="9"/>
     </row>
-    <row r="725" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="725" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J725" s="9"/>
     </row>
-    <row r="726" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="726" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J726" s="9"/>
     </row>
-    <row r="727" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="727" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J727" s="9"/>
     </row>
-    <row r="728" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="728" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J728" s="9"/>
     </row>
-    <row r="729" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="729" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J729" s="9"/>
     </row>
-    <row r="730" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="730" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J730" s="9"/>
     </row>
-    <row r="731" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="731" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J731" s="9"/>
     </row>
-    <row r="732" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="732" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J732" s="9"/>
     </row>
-    <row r="733" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="733" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J733" s="9"/>
     </row>
-    <row r="734" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="734" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J734" s="9"/>
     </row>
-    <row r="735" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="735" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J735" s="9"/>
     </row>
-    <row r="736" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="736" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J736" s="9"/>
     </row>
-    <row r="737" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="737" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J737" s="9"/>
     </row>
-    <row r="738" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="738" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J738" s="9"/>
     </row>
-    <row r="739" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="739" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J739" s="9"/>
     </row>
-    <row r="740" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="740" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J740" s="9"/>
     </row>
-    <row r="741" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="741" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J741" s="9"/>
     </row>
-    <row r="742" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="742" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J742" s="9"/>
     </row>
-    <row r="743" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="743" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J743" s="9"/>
     </row>
-    <row r="744" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="744" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J744" s="9"/>
     </row>
-    <row r="745" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="745" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J745" s="9"/>
     </row>
-    <row r="746" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="746" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J746" s="9"/>
     </row>
-    <row r="747" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="747" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J747" s="9"/>
     </row>
-    <row r="748" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="748" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J748" s="9"/>
     </row>
-    <row r="749" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="749" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J749" s="9"/>
     </row>
-    <row r="750" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="750" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J750" s="9"/>
     </row>
-    <row r="751" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="751" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J751" s="9"/>
     </row>
-    <row r="752" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="752" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J752" s="9"/>
     </row>
-    <row r="753" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="753" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J753" s="9"/>
     </row>
-    <row r="754" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="754" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J754" s="9"/>
     </row>
-    <row r="755" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="755" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J755" s="9"/>
     </row>
-    <row r="756" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="756" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J756" s="9"/>
     </row>
-    <row r="757" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="757" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J757" s="9"/>
     </row>
-    <row r="758" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="758" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J758" s="9"/>
     </row>
-    <row r="759" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="759" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J759" s="9"/>
     </row>
-    <row r="760" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="760" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J760" s="9"/>
     </row>
-    <row r="761" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="761" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J761" s="9"/>
     </row>
-    <row r="762" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="762" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J762" s="9"/>
     </row>
-    <row r="763" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="763" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J763" s="9"/>
     </row>
-    <row r="764" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="764" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J764" s="9"/>
     </row>
-    <row r="765" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="765" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J765" s="9"/>
     </row>
-    <row r="766" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="766" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J766" s="9"/>
     </row>
-    <row r="767" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="767" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J767" s="9"/>
     </row>
-    <row r="768" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="768" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J768" s="9"/>
     </row>
-    <row r="769" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="769" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J769" s="9"/>
     </row>
-    <row r="770" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="770" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J770" s="9"/>
     </row>
-    <row r="771" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="771" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J771" s="9"/>
     </row>
-    <row r="772" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="772" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J772" s="9"/>
     </row>
-    <row r="773" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="773" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J773" s="9"/>
     </row>
-    <row r="774" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="774" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J774" s="9"/>
     </row>
-    <row r="775" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="775" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J775" s="9"/>
     </row>
-    <row r="776" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="776" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J776" s="9"/>
     </row>
-    <row r="777" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="777" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J777" s="9"/>
     </row>
-    <row r="778" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="778" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J778" s="9"/>
     </row>
-    <row r="779" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="779" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J779" s="9"/>
     </row>
-    <row r="780" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="780" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J780" s="9"/>
     </row>
-    <row r="781" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="781" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J781" s="9"/>
     </row>
-    <row r="782" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="782" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J782" s="9"/>
     </row>
-    <row r="783" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="783" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J783" s="9"/>
     </row>
-    <row r="784" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="784" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J784" s="9"/>
     </row>
-    <row r="785" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="785" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J785" s="9"/>
     </row>
-    <row r="786" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="786" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J786" s="9"/>
     </row>
-    <row r="787" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="787" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J787" s="9"/>
     </row>
-    <row r="788" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="788" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J788" s="9"/>
     </row>
-    <row r="789" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="789" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J789" s="9"/>
     </row>
-    <row r="790" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="790" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J790" s="9"/>
     </row>
-    <row r="791" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="791" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J791" s="9"/>
     </row>
-    <row r="792" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="792" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J792" s="9"/>
     </row>
-    <row r="793" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="793" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J793" s="9"/>
     </row>
-    <row r="794" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="794" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J794" s="9"/>
     </row>
-    <row r="795" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="795" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J795" s="9"/>
     </row>
-    <row r="796" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="796" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J796" s="9"/>
     </row>
-    <row r="797" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="797" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J797" s="9"/>
     </row>
-    <row r="798" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="798" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J798" s="9"/>
     </row>
-    <row r="799" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="799" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J799" s="9"/>
     </row>
-    <row r="800" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="800" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J800" s="9"/>
     </row>
-    <row r="801" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="801" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J801" s="9"/>
     </row>
-    <row r="802" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="802" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J802" s="9"/>
     </row>
-    <row r="803" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="803" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J803" s="9"/>
     </row>
-    <row r="804" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="804" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J804" s="9"/>
     </row>
-    <row r="805" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="805" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J805" s="9"/>
     </row>
-    <row r="806" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="806" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J806" s="9"/>
     </row>
-    <row r="807" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="807" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J807" s="9"/>
     </row>
-    <row r="808" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="808" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J808" s="9"/>
     </row>
-    <row r="809" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="809" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J809" s="9"/>
     </row>
-    <row r="810" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="810" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J810" s="9"/>
     </row>
-    <row r="811" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="811" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J811" s="9"/>
     </row>
-    <row r="812" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="812" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J812" s="9"/>
     </row>
-    <row r="813" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="813" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J813" s="9"/>
     </row>
-    <row r="814" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="814" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J814" s="9"/>
     </row>
-    <row r="815" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="815" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J815" s="9"/>
     </row>
-    <row r="816" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="816" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J816" s="9"/>
     </row>
-    <row r="817" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="817" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J817" s="9"/>
     </row>
-    <row r="818" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="818" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J818" s="9"/>
     </row>
-    <row r="819" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="819" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J819" s="9"/>
     </row>
-    <row r="820" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="820" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J820" s="9"/>
     </row>
-    <row r="821" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="821" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J821" s="9"/>
     </row>
-    <row r="822" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="822" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J822" s="9"/>
     </row>
-    <row r="823" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="823" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J823" s="9"/>
     </row>
-    <row r="824" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="824" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J824" s="9"/>
     </row>
-    <row r="825" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="825" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J825" s="9"/>
     </row>
-    <row r="826" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="826" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J826" s="9"/>
     </row>
-    <row r="827" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="827" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J827" s="9"/>
     </row>
-    <row r="828" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="828" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J828" s="9"/>
     </row>
-    <row r="829" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="829" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J829" s="9"/>
     </row>
-    <row r="830" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="830" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J830" s="9"/>
     </row>
-    <row r="831" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="831" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J831" s="9"/>
     </row>
-    <row r="832" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="832" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J832" s="9"/>
     </row>
-    <row r="833" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="833" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J833" s="9"/>
     </row>
-    <row r="834" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="834" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J834" s="9"/>
     </row>
-    <row r="835" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="835" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J835" s="9"/>
     </row>
-    <row r="836" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="836" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J836" s="9"/>
     </row>
-    <row r="837" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="837" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J837" s="9"/>
     </row>
-    <row r="838" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="838" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J838" s="9"/>
     </row>
-    <row r="839" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="839" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J839" s="9"/>
     </row>
-    <row r="840" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="840" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J840" s="9"/>
     </row>
-    <row r="841" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="841" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J841" s="9"/>
     </row>
-    <row r="842" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="842" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J842" s="9"/>
     </row>
-    <row r="843" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="843" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J843" s="9"/>
     </row>
-    <row r="844" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="844" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J844" s="9"/>
     </row>
-    <row r="845" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="845" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J845" s="9"/>
     </row>
-    <row r="846" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="846" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J846" s="9"/>
     </row>
-    <row r="847" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="847" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J847" s="9"/>
     </row>
-    <row r="848" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="848" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J848" s="9"/>
     </row>
-    <row r="849" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="849" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J849" s="9"/>
     </row>
-    <row r="850" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="850" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J850" s="9"/>
     </row>
-    <row r="851" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="851" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J851" s="9"/>
     </row>
-    <row r="852" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="852" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J852" s="9"/>
     </row>
-    <row r="853" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="853" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J853" s="9"/>
     </row>
-    <row r="854" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="854" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J854" s="9"/>
     </row>
-    <row r="855" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="855" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J855" s="9"/>
     </row>
-    <row r="856" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="856" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J856" s="9"/>
     </row>
-    <row r="857" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="857" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J857" s="9"/>
     </row>
-    <row r="858" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="858" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J858" s="9"/>
     </row>
-    <row r="859" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="859" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J859" s="9"/>
     </row>
-    <row r="860" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="860" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J860" s="9"/>
     </row>
-    <row r="861" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="861" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J861" s="9"/>
     </row>
-    <row r="862" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="862" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J862" s="9"/>
     </row>
-    <row r="863" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="863" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J863" s="9"/>
     </row>
-    <row r="864" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="864" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J864" s="9"/>
     </row>
-    <row r="865" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="865" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J865" s="9"/>
     </row>
-    <row r="866" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="866" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J866" s="9"/>
     </row>
-    <row r="867" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="867" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J867" s="9"/>
     </row>
-    <row r="868" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="868" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J868" s="9"/>
     </row>
-    <row r="869" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="869" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J869" s="9"/>
     </row>
-    <row r="870" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="870" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J870" s="9"/>
     </row>
-    <row r="871" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="871" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J871" s="9"/>
     </row>
-    <row r="872" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="872" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J872" s="9"/>
     </row>
-    <row r="873" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="873" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J873" s="9"/>
     </row>
-    <row r="874" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="874" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J874" s="9"/>
     </row>
-    <row r="875" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="875" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J875" s="9"/>
     </row>
-    <row r="876" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="876" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J876" s="9"/>
     </row>
-    <row r="877" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="877" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J877" s="9"/>
     </row>
-    <row r="878" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="878" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J878" s="9"/>
     </row>
-    <row r="879" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="879" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J879" s="9"/>
     </row>
-    <row r="880" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="880" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J880" s="9"/>
     </row>
-    <row r="881" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="881" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J881" s="9"/>
     </row>
-    <row r="882" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="882" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J882" s="9"/>
     </row>
-    <row r="883" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="883" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J883" s="9"/>
     </row>
-    <row r="884" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="884" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J884" s="9"/>
     </row>
-    <row r="885" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="885" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J885" s="9"/>
     </row>
-    <row r="886" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="886" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J886" s="9"/>
     </row>
-    <row r="887" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="887" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J887" s="9"/>
     </row>
-    <row r="888" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="888" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J888" s="9"/>
     </row>
-    <row r="889" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="889" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J889" s="9"/>
     </row>
-    <row r="890" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="890" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J890" s="9"/>
     </row>
-    <row r="891" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="891" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J891" s="9"/>
     </row>
-    <row r="892" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="892" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J892" s="9"/>
     </row>
-    <row r="893" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="893" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J893" s="9"/>
     </row>
-    <row r="894" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="894" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J894" s="9"/>
     </row>
-    <row r="895" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="895" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J895" s="9"/>
     </row>
-    <row r="896" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="896" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J896" s="9"/>
     </row>
-    <row r="897" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="897" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J897" s="9"/>
     </row>
-    <row r="898" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="898" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J898" s="9"/>
     </row>
-    <row r="899" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="899" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J899" s="9"/>
     </row>
-    <row r="900" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="900" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J900" s="9"/>
     </row>
-    <row r="901" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="901" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J901" s="9"/>
     </row>
-    <row r="902" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="902" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J902" s="9"/>
     </row>
-    <row r="903" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="903" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J903" s="9"/>
     </row>
-    <row r="904" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="904" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J904" s="9"/>
     </row>
-    <row r="905" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="905" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J905" s="9"/>
     </row>
-    <row r="906" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="906" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J906" s="9"/>
     </row>
-    <row r="907" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="907" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J907" s="9"/>
     </row>
-    <row r="908" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="908" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J908" s="9"/>
     </row>
-    <row r="909" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="909" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J909" s="9"/>
     </row>
-    <row r="910" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="910" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J910" s="9"/>
     </row>
-    <row r="911" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="911" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J911" s="9"/>
     </row>
-    <row r="912" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="912" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J912" s="9"/>
     </row>
-    <row r="913" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="913" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J913" s="9"/>
     </row>
-    <row r="914" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="914" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J914" s="9"/>
     </row>
-    <row r="915" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="915" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J915" s="9"/>
     </row>
-    <row r="916" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="916" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J916" s="9"/>
     </row>
-    <row r="917" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="917" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J917" s="9"/>
     </row>
-    <row r="918" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="918" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J918" s="9"/>
     </row>
-    <row r="919" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="919" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J919" s="9"/>
     </row>
-    <row r="920" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="920" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J920" s="9"/>
     </row>
-    <row r="921" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="921" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J921" s="9"/>
     </row>
-    <row r="922" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="922" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J922" s="9"/>
     </row>
-    <row r="923" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="923" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J923" s="9"/>
     </row>
-    <row r="924" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="924" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J924" s="9"/>
     </row>
-    <row r="925" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="925" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J925" s="9"/>
     </row>
-    <row r="926" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="926" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J926" s="9"/>
     </row>
-    <row r="927" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="927" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J927" s="9"/>
     </row>
-    <row r="928" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="928" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J928" s="9"/>
     </row>
-    <row r="929" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="929" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J929" s="9"/>
     </row>
-    <row r="930" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="930" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J930" s="9"/>
     </row>
-    <row r="931" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="931" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J931" s="9"/>
     </row>
-    <row r="932" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="932" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J932" s="9"/>
     </row>
-    <row r="933" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="933" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J933" s="9"/>
     </row>
-    <row r="934" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="934" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J934" s="9"/>
     </row>
-    <row r="935" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="935" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J935" s="9"/>
     </row>
-    <row r="936" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="936" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J936" s="9"/>
     </row>
-    <row r="937" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="937" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J937" s="9"/>
     </row>
-    <row r="938" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="938" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J938" s="9"/>
     </row>
-    <row r="939" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="939" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J939" s="9"/>
     </row>
-    <row r="940" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="940" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J940" s="9"/>
     </row>
-    <row r="941" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="941" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J941" s="9"/>
     </row>
-    <row r="942" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="942" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J942" s="9"/>
     </row>
-    <row r="943" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="943" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J943" s="9"/>
     </row>
-    <row r="944" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="944" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J944" s="9"/>
     </row>
-    <row r="945" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="945" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J945" s="9"/>
     </row>
-    <row r="946" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="946" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J946" s="9"/>
     </row>
-    <row r="947" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="947" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J947" s="9"/>
     </row>
-    <row r="948" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="948" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J948" s="9"/>
     </row>
-    <row r="949" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="949" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J949" s="9"/>
     </row>
-    <row r="950" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="950" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J950" s="9"/>
     </row>
-    <row r="951" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="951" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J951" s="9"/>
     </row>
-    <row r="952" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="952" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J952" s="9"/>
     </row>
-    <row r="953" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="953" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J953" s="9"/>
     </row>
-    <row r="954" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="954" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J954" s="9"/>
     </row>
-    <row r="955" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="955" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J955" s="9"/>
     </row>
-    <row r="956" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="956" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J956" s="9"/>
     </row>
-    <row r="957" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="957" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J957" s="9"/>
     </row>
-    <row r="958" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="958" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J958" s="9"/>
     </row>
-    <row r="959" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="959" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J959" s="9"/>
     </row>
-    <row r="960" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="960" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J960" s="9"/>
     </row>
-    <row r="961" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="961" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J961" s="9"/>
     </row>
-    <row r="962" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="962" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J962" s="9"/>
     </row>
-    <row r="963" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="963" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J963" s="9"/>
     </row>
-    <row r="964" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="964" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J964" s="9"/>
     </row>
-    <row r="965" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="965" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J965" s="9"/>
     </row>
-    <row r="966" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="966" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J966" s="9"/>
     </row>
-    <row r="967" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="967" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J967" s="9"/>
     </row>
-    <row r="968" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="968" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J968" s="9"/>
     </row>
-    <row r="969" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="969" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J969" s="9"/>
     </row>
-    <row r="970" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="970" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J970" s="9"/>
     </row>
-    <row r="971" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="971" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J971" s="9"/>
     </row>
-    <row r="972" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="972" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J972" s="9"/>
     </row>
-    <row r="973" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="973" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J973" s="9"/>
     </row>
-    <row r="974" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="974" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J974" s="9"/>
     </row>
-    <row r="975" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="975" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J975" s="9"/>
     </row>
-    <row r="976" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="976" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J976" s="9"/>
     </row>
-    <row r="977" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="977" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J977" s="9"/>
     </row>
-    <row r="978" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="978" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J978" s="9"/>
     </row>
-    <row r="979" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="979" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J979" s="9"/>
     </row>
-    <row r="980" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="980" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J980" s="9"/>
     </row>
-    <row r="981" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="981" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J981" s="9"/>
     </row>
-    <row r="982" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="982" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J982" s="9"/>
     </row>
-    <row r="983" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="983" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J983" s="9"/>
     </row>
-    <row r="984" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="984" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J984" s="9"/>
     </row>
-    <row r="985" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="985" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J985" s="9"/>
     </row>
-    <row r="986" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="986" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J986" s="9"/>
     </row>
-    <row r="987" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="987" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J987" s="9"/>
     </row>
-    <row r="988" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="988" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J988" s="9"/>
     </row>
-    <row r="989" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="989" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J989" s="9"/>
     </row>
-    <row r="990" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="990" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J990" s="9"/>
     </row>
-    <row r="991" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="991" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J991" s="9"/>
     </row>
-    <row r="992" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="992" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J992" s="9"/>
     </row>
-    <row r="993" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="993" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J993" s="9"/>
     </row>
-    <row r="994" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="994" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J994" s="9"/>
     </row>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{D9CDEFDA-B742-4707-B803-BE75C138FC2A}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="P1:P994" xr:uid="{F05FB6E5-6772-4A44-A7A4-03AB4B644E85}"/>
+      <autoFilter ref="P1:P994" xr:uid="{7832FB9B-810C-4563-9B98-889A2154967C}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903B5A93-8202-4044-A142-B3A85507BA31}">
+  <dimension ref="A1:B115"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
+        <v>2</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
+        <v>3</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
+        <v>4</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
+        <v>6</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
+        <v>7</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
+        <v>8</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>11</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
+        <v>12</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
+        <v>13</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
+        <v>14</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
+        <v>15</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
+        <v>16</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
+        <v>18</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>19</v>
+      </c>
+      <c r="B21" s="36" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
+        <v>20</v>
+      </c>
+      <c r="B22" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
+        <v>21</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
+        <v>22</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>23</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>24</v>
+      </c>
+      <c r="B26" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
+        <v>25</v>
+      </c>
+      <c r="B27" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
+        <v>27</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
+        <v>28</v>
+      </c>
+      <c r="B30" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
+        <v>29</v>
+      </c>
+      <c r="B31" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
+        <v>30</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
+        <v>31</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>33</v>
+      </c>
+      <c r="B35" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
+        <v>34</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
+        <v>35</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
+        <v>37</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="2">
+        <v>39</v>
+      </c>
+      <c r="B41" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="2">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="2">
+        <v>41</v>
+      </c>
+      <c r="B43" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44" s="2">
+        <v>42</v>
+      </c>
+      <c r="B44" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="2">
+        <v>43</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="2">
+        <v>44</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="2">
+        <v>45</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="2">
+        <v>46</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="2">
+        <v>47</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="2">
+        <v>48</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A51" s="2">
+        <v>49</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A52" s="2">
+        <v>50</v>
+      </c>
+      <c r="B52" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A53" s="2">
+        <v>51</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A54" s="2">
+        <v>52</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A55" s="2">
+        <v>53</v>
+      </c>
+      <c r="B55" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A56" s="2">
+        <v>54</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A57" s="2">
+        <v>55</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A58" s="2">
+        <v>56</v>
+      </c>
+      <c r="B58" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A59" s="2">
+        <v>57</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A60" s="2">
+        <v>58</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A61" s="2">
+        <v>59</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A62" s="2">
+        <v>60</v>
+      </c>
+      <c r="B62" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A63" s="2">
+        <v>61</v>
+      </c>
+      <c r="B63" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A64" s="2">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A65" s="2">
+        <v>63</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A66" s="2">
+        <v>64</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A67" s="2">
+        <v>65</v>
+      </c>
+      <c r="B67" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A68" s="2">
+        <v>66</v>
+      </c>
+      <c r="B68" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A69" s="2">
+        <v>67</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A70" s="2">
+        <v>68</v>
+      </c>
+      <c r="B70" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A71" s="2">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A72" s="2">
+        <v>70</v>
+      </c>
+      <c r="B72" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A73" s="2">
+        <v>71</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A74" s="2">
+        <v>72</v>
+      </c>
+      <c r="B74" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A75" s="2">
+        <v>73</v>
+      </c>
+      <c r="B75" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A76" s="2">
+        <v>74</v>
+      </c>
+      <c r="B76" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A77" s="2">
+        <v>75</v>
+      </c>
+      <c r="B77" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A78" s="2">
+        <v>76</v>
+      </c>
+      <c r="B78" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A79" s="2">
+        <v>77</v>
+      </c>
+      <c r="B79" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A80" s="2">
+        <v>78</v>
+      </c>
+      <c r="B80" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A81" s="2">
+        <v>79</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A82" s="2">
+        <v>80</v>
+      </c>
+      <c r="B82" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A83" s="2">
+        <v>81</v>
+      </c>
+      <c r="B83" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A84" s="2">
+        <v>82</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A85" s="2">
+        <v>83</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A86" s="2">
+        <v>84</v>
+      </c>
+      <c r="B86" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A87" s="2">
+        <v>85</v>
+      </c>
+      <c r="B87" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A88" s="2">
+        <v>86</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A89" s="2">
+        <v>87</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A90" s="2">
+        <v>88</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A91" s="2">
+        <v>89</v>
+      </c>
+      <c r="B91" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A92" s="2">
+        <v>90</v>
+      </c>
+      <c r="B92" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A93" s="2">
+        <v>91</v>
+      </c>
+      <c r="B93" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A94" s="2">
+        <v>92</v>
+      </c>
+      <c r="B94" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A95" s="2">
+        <v>93</v>
+      </c>
+      <c r="B95" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A96" s="2">
+        <v>94</v>
+      </c>
+      <c r="B96" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A97" s="2">
+        <v>95</v>
+      </c>
+      <c r="B97" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A98" s="2">
+        <v>96</v>
+      </c>
+      <c r="B98" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A99" s="2">
+        <v>97</v>
+      </c>
+      <c r="B99" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A100" s="2">
+        <v>98</v>
+      </c>
+      <c r="B100" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A101" s="2">
+        <v>99</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A102" s="2">
+        <v>100</v>
+      </c>
+      <c r="B102" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A103" s="2">
+        <v>101</v>
+      </c>
+      <c r="B103" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A104" s="2">
+        <v>102</v>
+      </c>
+      <c r="B104" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A105" s="2">
+        <v>103</v>
+      </c>
+      <c r="B105" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A106" s="2">
+        <v>104</v>
+      </c>
+      <c r="B106" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A107" s="2">
+        <v>105</v>
+      </c>
+      <c r="B107" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A108" s="2">
+        <v>106</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A109" s="2">
+        <v>107</v>
+      </c>
+      <c r="B109" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A110" s="2">
+        <v>108</v>
+      </c>
+      <c r="B110" s="36" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A111" s="2">
+        <v>109</v>
+      </c>
+      <c r="B111" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A112" s="2">
+        <v>110</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A113" s="2">
+        <v>111</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A114" s="2">
+        <v>112</v>
+      </c>
+      <c r="B114" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A115" s="2">
+        <v>113</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8700276F-7844-46F1-85C5-DD805B6A2273}">
+  <dimension ref="A1:B50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A3" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A4" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A7" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A8" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A9" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A10" s="18" t="s">
+        <v>65</v>
+      </c>
+      <c r="B10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A11" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A12" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A13" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A14" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A16" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A17" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A18" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A19" s="26" t="s">
+        <v>92</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A20" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A21" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A22" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A23" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A24" s="26" t="s">
+        <v>105</v>
+      </c>
+      <c r="B24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A25" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A26" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B26" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A27" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="B27" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A28" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B28" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A29" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A30" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A31" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A32" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+      <c r="A33" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A34" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A35" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B35" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A36" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A37" s="33" t="s">
+        <v>124</v>
+      </c>
+      <c r="B37" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A38" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B38" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A39" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A40" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A41" s="32" t="s">
+        <v>130</v>
+      </c>
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A42" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A43" s="34" t="s">
+        <v>132</v>
+      </c>
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A44" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B44" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A45" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="B45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A46" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="B46" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A47" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="B47" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A48" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A49" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="B49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+      <c r="A50" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="B50" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/Annotation tracker.xlsx
+++ b/data/Annotation tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10312"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HaroM\Box\Lawrenson Lab\Endometriosis\Rstudio_analysis\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harom/Library/CloudStorage/Box-Box/Lawrenson Lab/Endometriosis/Rstudio_analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61069038-2E24-417C-BD4D-3AC1CB775A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D751777E-F0C1-E849-BE9B-2A1989EC6668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9465" yWindow="1950" windowWidth="28080" windowHeight="13800" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9460" yWindow="1960" windowWidth="28080" windowHeight="13800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clusters" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="822" uniqueCount="153">
   <si>
     <t>Cluster_Number</t>
   </si>
@@ -108,9 +108,6 @@
   </si>
   <si>
     <t>Low</t>
-  </si>
-  <si>
-    <t>Exclude</t>
   </si>
   <si>
     <t>High</t>
@@ -1010,15 +1007,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J115"/>
-  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="1" max="1" width="18.5" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="26.140625" customWidth="1"/>
-    <col min="4" max="5" width="23.42578125" customWidth="1"/>
+    <col min="3" max="3" width="26.1640625" customWidth="1"/>
+    <col min="4" max="5" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1029,7 +1026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1037,7 +1034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1045,7 +1042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1053,7 +1050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1061,7 +1058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1069,7 +1066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1077,7 +1074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1085,7 +1082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1094,7 +1091,7 @@
       </c>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1103,7 +1100,7 @@
       </c>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1112,7 +1109,7 @@
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1121,7 +1118,7 @@
       </c>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1130,7 +1127,7 @@
       </c>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1140,7 +1137,7 @@
       <c r="H14" s="6"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1148,7 +1145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1156,7 +1153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1164,7 +1161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1172,7 +1169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1183,7 +1180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1191,7 +1188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1200,7 +1197,7 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1208,7 +1205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1216,7 +1213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -1224,7 +1221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -1235,7 +1232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -1244,7 +1241,7 @@
       </c>
       <c r="C26" s="7"/>
     </row>
-    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -1252,7 +1249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -1263,7 +1260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -1274,7 +1271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -1282,7 +1279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -1290,7 +1287,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -1298,7 +1295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -1306,7 +1303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -1314,7 +1311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -1322,7 +1319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -1330,7 +1327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -1338,7 +1335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -1346,7 +1343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -1354,7 +1351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -1362,7 +1359,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -1370,7 +1367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -1378,7 +1375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -1386,7 +1383,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -1394,7 +1391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -1405,7 +1402,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -1413,7 +1410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -1424,7 +1421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -1432,7 +1429,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -1440,7 +1437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -1448,7 +1445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -1456,7 +1453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -1464,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -1472,7 +1469,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -1480,7 +1477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -1491,7 +1488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -1499,7 +1496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -1510,7 +1507,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -1518,7 +1515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -1526,7 +1523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -1534,7 +1531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -1545,7 +1542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>60</v>
       </c>
@@ -1553,7 +1550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>61</v>
       </c>
@@ -1561,7 +1558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -1572,7 +1569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -1580,7 +1577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -1591,7 +1588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -1602,7 +1599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -1610,7 +1607,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -1618,7 +1615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>68</v>
       </c>
@@ -1626,7 +1623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>69</v>
       </c>
@@ -1634,7 +1631,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>70</v>
       </c>
@@ -1642,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -1650,7 +1647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>72</v>
       </c>
@@ -1658,7 +1655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>73</v>
       </c>
@@ -1666,7 +1663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>74</v>
       </c>
@@ -1677,7 +1674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -1685,7 +1682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -1693,7 +1690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>77</v>
       </c>
@@ -1701,7 +1698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>78</v>
       </c>
@@ -1709,7 +1706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>79</v>
       </c>
@@ -1720,7 +1717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>80</v>
       </c>
@@ -1728,7 +1725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>81</v>
       </c>
@@ -1736,7 +1733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>82</v>
       </c>
@@ -1744,7 +1741,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>83</v>
       </c>
@@ -1752,7 +1749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>84</v>
       </c>
@@ -1760,7 +1757,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>85</v>
       </c>
@@ -1768,7 +1765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>86</v>
       </c>
@@ -1776,7 +1773,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>87</v>
       </c>
@@ -1784,7 +1781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>88</v>
       </c>
@@ -1795,7 +1792,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>89</v>
       </c>
@@ -1803,7 +1800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>90</v>
       </c>
@@ -1811,7 +1808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>91</v>
       </c>
@@ -1819,7 +1816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>92</v>
       </c>
@@ -1827,7 +1824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>93</v>
       </c>
@@ -1835,7 +1832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>94</v>
       </c>
@@ -1843,7 +1840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>95</v>
       </c>
@@ -1851,7 +1848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>96</v>
       </c>
@@ -1859,7 +1856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>97</v>
       </c>
@@ -1867,7 +1864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>98</v>
       </c>
@@ -1875,7 +1872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>99</v>
       </c>
@@ -1883,7 +1880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>100</v>
       </c>
@@ -1891,7 +1888,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>101</v>
       </c>
@@ -1902,7 +1899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>102</v>
       </c>
@@ -1910,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>103</v>
       </c>
@@ -1921,7 +1918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>104</v>
       </c>
@@ -1929,7 +1926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>105</v>
       </c>
@@ -1937,7 +1934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>106</v>
       </c>
@@ -1945,7 +1942,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>107</v>
       </c>
@@ -1953,7 +1950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>108</v>
       </c>
@@ -1961,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>109</v>
       </c>
@@ -1969,7 +1966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>110</v>
       </c>
@@ -1977,7 +1974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>111</v>
       </c>
@@ -1985,7 +1982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>112</v>
       </c>
@@ -1993,7 +1990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>113</v>
       </c>
@@ -2012,9 +2009,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
@@ -2031,7 +2028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2048,7 +2045,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -2065,7 +2062,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -2082,7 +2079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -2099,7 +2096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -2113,10 +2110,10 @@
         <v>22</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -2133,7 +2130,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -2147,10 +2144,10 @@
         <v>20</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -2158,7 +2155,7 @@
         <v>20</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>22</v>
@@ -2167,7 +2164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -2175,7 +2172,7 @@
         <v>20</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>22</v>
@@ -2184,7 +2181,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -2192,16 +2189,16 @@
         <v>20</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -2215,10 +2212,10 @@
         <v>22</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -2235,7 +2232,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -2252,7 +2249,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -2266,10 +2263,10 @@
         <v>22</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -2286,7 +2283,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -2294,16 +2291,16 @@
         <v>20</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D17" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -2320,7 +2317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -2334,10 +2331,10 @@
         <v>20</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2351,10 +2348,10 @@
         <v>22</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -2362,16 +2359,16 @@
         <v>20</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D21" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -2379,13 +2376,13 @@
         <v>20</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D22" s="7" t="s">
         <v>22</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -2399,48 +2396,48 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P994"/>
-  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="3" max="5" width="24.28515625" customWidth="1"/>
-    <col min="6" max="6" width="19.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
-    <col min="10" max="10" width="26.140625" customWidth="1"/>
+    <col min="3" max="5" width="24.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="10" max="10" width="26.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="J1" s="10" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
@@ -2448,31 +2445,31 @@
         <v>1</v>
       </c>
       <c r="C2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="G2" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H2" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="G2" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>42</v>
-      </c>
-      <c r="I2" s="15" t="s">
-        <v>43</v>
       </c>
       <c r="J2" s="14">
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>23</v>
       </c>
@@ -2480,31 +2477,31 @@
         <v>2</v>
       </c>
       <c r="C3" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="D3" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="E3" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="F3" s="9" t="s">
+      <c r="I3" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="J3" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>23</v>
       </c>
@@ -2512,31 +2509,31 @@
         <v>2</v>
       </c>
       <c r="C4" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="F4" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="I4" s="15" t="s">
         <v>41</v>
-      </c>
-      <c r="G4" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I4" s="15" t="s">
-        <v>42</v>
       </c>
       <c r="J4" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="11" t="s">
         <v>23</v>
       </c>
@@ -2544,32 +2541,32 @@
         <v>3</v>
       </c>
       <c r="C5" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D5" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="E5" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="F5" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="G5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" s="15" t="s">
-        <v>55</v>
-      </c>
       <c r="J5" s="14" t="s">
         <v>23</v>
       </c>
       <c r="P5" s="9"/>
     </row>
-    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
@@ -2577,32 +2574,32 @@
         <v>4</v>
       </c>
       <c r="C6" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="H6" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J6" s="9">
         <v>0</v>
       </c>
       <c r="P6" s="9"/>
     </row>
-    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
         <v>22</v>
       </c>
@@ -2610,32 +2607,32 @@
         <v>4</v>
       </c>
       <c r="C7" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D7" s="19" t="s">
-        <v>61</v>
-      </c>
       <c r="E7" s="19" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F7" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G7" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="14" t="s">
-        <v>59</v>
-      </c>
       <c r="H7" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I7" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J7" s="14">
         <v>0</v>
       </c>
       <c r="P7" s="9"/>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="11" t="s">
         <v>20</v>
       </c>
@@ -2643,32 +2640,32 @@
         <v>5</v>
       </c>
       <c r="C8" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="22" t="s">
-        <v>63</v>
-      </c>
       <c r="E8" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F8" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G8" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G8" s="14" t="s">
-        <v>59</v>
-      </c>
       <c r="H8" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I8" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J8" s="14">
         <v>4</v>
       </c>
       <c r="P8" s="9"/>
     </row>
-    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>23</v>
       </c>
@@ -2676,32 +2673,32 @@
         <v>6</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D9" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="F9" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>55</v>
-      </c>
       <c r="J9" s="9" t="s">
         <v>23</v>
       </c>
       <c r="P9" s="9"/>
     </row>
-    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>23</v>
       </c>
@@ -2709,16 +2706,16 @@
         <v>6</v>
       </c>
       <c r="C10" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="E10" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>23</v>
@@ -2730,40 +2727,40 @@
       </c>
       <c r="P10" s="9"/>
     </row>
-    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="24" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B11" s="25">
         <v>7</v>
       </c>
       <c r="C11" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="E11" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="F11" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J11" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F11" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G11" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="J11" s="9" t="s">
-        <v>72</v>
-      </c>
       <c r="P11" s="9"/>
     </row>
-    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
         <v>20</v>
       </c>
@@ -2771,32 +2768,32 @@
         <v>7</v>
       </c>
       <c r="C12" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="E12" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="22" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G12" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="H12" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J12" s="9">
         <v>12</v>
       </c>
       <c r="P12" s="9"/>
     </row>
-    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
         <v>23</v>
       </c>
@@ -2804,32 +2801,32 @@
         <v>7</v>
       </c>
       <c r="C13" s="26" t="s">
+        <v>74</v>
+      </c>
+      <c r="D13" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>76</v>
-      </c>
       <c r="E13" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F13" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>50</v>
-      </c>
       <c r="I13" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
       </c>
       <c r="P13" s="9"/>
     </row>
-    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
         <v>20</v>
       </c>
@@ -2837,32 +2834,32 @@
         <v>7</v>
       </c>
       <c r="C14" s="26" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" s="22" t="s">
         <v>77</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="E14" s="22" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="F14" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="H14" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="F14" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="H14" s="15" t="s">
+      <c r="I14" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="14" t="s">
-        <v>81</v>
-      </c>
       <c r="P14" s="9"/>
     </row>
-    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>22</v>
       </c>
@@ -2870,32 +2867,32 @@
         <v>8</v>
       </c>
       <c r="C15" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="D15" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G15" s="9" t="s">
-        <v>83</v>
-      </c>
       <c r="H15" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
       </c>
       <c r="P15" s="9"/>
     </row>
-    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
         <v>23</v>
       </c>
@@ -2903,32 +2900,32 @@
         <v>8</v>
       </c>
       <c r="C16" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="D16" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>85</v>
-      </c>
       <c r="E16" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F16" s="9" t="s">
-        <v>41</v>
-      </c>
       <c r="G16" s="9" t="s">
         <v>23</v>
       </c>
       <c r="H16" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
       </c>
       <c r="P16" s="9"/>
     </row>
-    <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
         <v>22</v>
       </c>
@@ -2936,32 +2933,32 @@
         <v>8</v>
       </c>
       <c r="C17" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="E17" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="19" t="s">
-        <v>88</v>
-      </c>
       <c r="F17" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H17" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
       </c>
       <c r="P17" s="9"/>
     </row>
-    <row r="18" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
         <v>22</v>
       </c>
@@ -2969,19 +2966,19 @@
         <v>8</v>
       </c>
       <c r="C18" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="E18" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E18" s="19" t="s">
-        <v>91</v>
-      </c>
       <c r="F18" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H18" s="15"/>
       <c r="I18" s="15"/>
@@ -2990,7 +2987,7 @@
       </c>
       <c r="P18" s="9"/>
     </row>
-    <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>22</v>
       </c>
@@ -2998,32 +2995,32 @@
         <v>9</v>
       </c>
       <c r="C19" s="26" t="s">
+        <v>91</v>
+      </c>
+      <c r="D19" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="D19" s="22" t="s">
-        <v>93</v>
-      </c>
       <c r="E19" s="22" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="H19" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
       </c>
       <c r="P19" s="9"/>
     </row>
-    <row r="20" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="24" t="s">
         <v>22</v>
       </c>
@@ -3031,32 +3028,32 @@
         <v>9</v>
       </c>
       <c r="C20" s="26" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="22" t="s">
-        <v>95</v>
-      </c>
       <c r="E20" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G20" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="H20" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
       </c>
       <c r="P20" s="9"/>
     </row>
-    <row r="21" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="24" t="s">
         <v>22</v>
       </c>
@@ -3064,32 +3061,32 @@
         <v>9</v>
       </c>
       <c r="C21" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D21" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="E21" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="F21" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F21" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="7" t="s">
+      <c r="I21" s="7" t="s">
         <v>99</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>100</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
       </c>
       <c r="P21" s="9"/>
     </row>
-    <row r="22" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="24" t="s">
         <v>23</v>
       </c>
@@ -3097,32 +3094,32 @@
         <v>9</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E22" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="F22" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="F22" s="9" t="s">
+      <c r="I22" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="J22" s="9">
         <v>0</v>
       </c>
       <c r="P22" s="9"/>
     </row>
-    <row r="23" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
         <v>22</v>
       </c>
@@ -3130,26 +3127,26 @@
         <v>9</v>
       </c>
       <c r="C23" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="E23" s="22" t="s">
         <v>103</v>
       </c>
-      <c r="E23" s="22" t="s">
-        <v>104</v>
-      </c>
       <c r="F23" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J23" s="9">
         <v>0</v>
       </c>
       <c r="P23" s="9"/>
     </row>
-    <row r="24" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="27" t="s">
         <v>22</v>
       </c>
@@ -3157,31 +3154,31 @@
         <v>9</v>
       </c>
       <c r="C24" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D24" s="22" t="s">
         <v>105</v>
       </c>
-      <c r="D24" s="22" t="s">
-        <v>106</v>
-      </c>
       <c r="E24" s="22" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F24" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G24" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H24" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J24" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
         <v>23</v>
       </c>
@@ -3189,17 +3186,17 @@
         <v>10</v>
       </c>
       <c r="C25" s="29" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D25" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="F25" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F25" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="G25" s="9" t="s">
         <v>23</v>
       </c>
@@ -3207,7 +3204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>22</v>
       </c>
@@ -3215,25 +3212,25 @@
         <v>10</v>
       </c>
       <c r="C26" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="D26" s="19" t="s">
-        <v>109</v>
-      </c>
       <c r="E26" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J26" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>22</v>
       </c>
@@ -3241,25 +3238,25 @@
         <v>10</v>
       </c>
       <c r="C27" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="19" t="s">
         <v>110</v>
       </c>
-      <c r="D27" s="19" t="s">
-        <v>111</v>
-      </c>
       <c r="E27" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J27" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="20" t="s">
         <v>20</v>
       </c>
@@ -3267,19 +3264,19 @@
         <v>10</v>
       </c>
       <c r="C28" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D28" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="D28" s="19" t="s">
-        <v>113</v>
-      </c>
       <c r="E28" s="19" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F28" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" s="14" t="s">
         <v>58</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>59</v>
       </c>
       <c r="H28" s="15"/>
       <c r="I28" s="15"/>
@@ -3287,7 +3284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="24" t="s">
         <v>20</v>
       </c>
@@ -3295,32 +3292,32 @@
         <v>11</v>
       </c>
       <c r="C29" s="26" t="s">
+        <v>113</v>
+      </c>
+      <c r="D29" s="22" t="s">
         <v>114</v>
       </c>
-      <c r="D29" s="22" t="s">
-        <v>115</v>
-      </c>
       <c r="E29" s="22" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J29" s="9">
         <v>5</v>
       </c>
       <c r="P29" s="9"/>
     </row>
-    <row r="30" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="24" t="s">
         <v>23</v>
       </c>
@@ -3328,32 +3325,32 @@
         <v>11</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D30" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="E30" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="F30" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="F30" s="9" t="s">
+      <c r="G30" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H30" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="I30" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="J30" s="9">
         <v>6</v>
       </c>
       <c r="P30" s="9"/>
     </row>
-    <row r="31" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
         <v>23</v>
       </c>
@@ -3361,16 +3358,16 @@
         <v>11</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D31" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="E31" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="F31" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="F31" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="G31" s="14" t="s">
         <v>23</v>
@@ -3382,7 +3379,7 @@
       </c>
       <c r="P31" s="9"/>
     </row>
-    <row r="32" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="20" t="s">
         <v>23</v>
       </c>
@@ -3390,16 +3387,16 @@
         <v>12</v>
       </c>
       <c r="C32" s="30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D32" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="E32" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="F32" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="F32" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="G32" s="14" t="s">
         <v>23</v>
@@ -3411,7 +3408,7 @@
       </c>
       <c r="P32" s="9"/>
     </row>
-    <row r="33" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
         <v>23</v>
       </c>
@@ -3419,16 +3416,16 @@
         <v>13</v>
       </c>
       <c r="C33" s="31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D33" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="G33" s="14" t="s">
         <v>23</v>
@@ -3440,7 +3437,7 @@
       </c>
       <c r="P33" s="9"/>
     </row>
-    <row r="34" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>22</v>
       </c>
@@ -3448,31 +3445,31 @@
         <v>14</v>
       </c>
       <c r="C34" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="D34" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="19" t="s">
-        <v>120</v>
-      </c>
       <c r="E34" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F34" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G34" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G34" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="H34" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J34" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>23</v>
       </c>
@@ -3480,23 +3477,23 @@
         <v>14</v>
       </c>
       <c r="C35" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="D35" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D35" s="19" t="s">
-        <v>122</v>
-      </c>
       <c r="E35" s="19" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G35" s="9"/>
       <c r="J35" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
         <v>23</v>
       </c>
@@ -3504,16 +3501,16 @@
         <v>14</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D36" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F36" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="G36" s="14" t="s">
         <v>23</v>
@@ -3524,7 +3521,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
         <v>23</v>
       </c>
@@ -3532,16 +3529,16 @@
         <v>15</v>
       </c>
       <c r="C37" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="D37" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="D37" s="22" t="s">
-        <v>125</v>
-      </c>
       <c r="E37" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G37" s="14" t="s">
         <v>23</v>
@@ -3552,7 +3549,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="16" t="s">
         <v>20</v>
       </c>
@@ -3560,31 +3557,31 @@
         <v>16</v>
       </c>
       <c r="C38" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="D38" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D38" s="19" t="s">
-        <v>127</v>
-      </c>
       <c r="E38" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F38" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G38" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G38" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="H38" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J38" s="9">
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="20" t="s">
         <v>23</v>
       </c>
@@ -3592,16 +3589,16 @@
         <v>16</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D39" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E39" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F39" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="E39" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F39" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>23</v>
@@ -3612,7 +3609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="27" t="s">
         <v>23</v>
       </c>
@@ -3620,16 +3617,16 @@
         <v>17</v>
       </c>
       <c r="C40" s="33" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D40" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E40" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="14" t="s">
         <v>53</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="F40" s="14" t="s">
-        <v>54</v>
       </c>
       <c r="G40" s="14" t="s">
         <v>23</v>
@@ -3640,7 +3637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="16" t="s">
         <v>23</v>
       </c>
@@ -3648,28 +3645,28 @@
         <v>18</v>
       </c>
       <c r="C41" s="32" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D41" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E41" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="F41" s="9" t="s">
-        <v>54</v>
-      </c>
       <c r="G41" s="9" t="s">
         <v>23</v>
       </c>
       <c r="H41" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="20" t="s">
         <v>23</v>
       </c>
@@ -3677,16 +3674,16 @@
         <v>18</v>
       </c>
       <c r="C42" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D42" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="E42" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="F42" s="14" t="s">
         <v>66</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>66</v>
-      </c>
-      <c r="F42" s="14" t="s">
-        <v>67</v>
       </c>
       <c r="G42" s="14" t="s">
         <v>23</v>
@@ -3697,7 +3694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="24" t="s">
         <v>23</v>
       </c>
@@ -3705,28 +3702,28 @@
         <v>19</v>
       </c>
       <c r="C43" s="34" t="s">
+        <v>131</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="D43" s="22" t="s">
-        <v>85</v>
-      </c>
-      <c r="E43" s="22" t="s">
-        <v>133</v>
-      </c>
       <c r="F43" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G43" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="7" t="s">
         <v>41</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H43" s="7" t="s">
-        <v>42</v>
       </c>
       <c r="J43" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="27" t="s">
         <v>20</v>
       </c>
@@ -3734,31 +3731,31 @@
         <v>19</v>
       </c>
       <c r="C44" s="34" t="s">
+        <v>133</v>
+      </c>
+      <c r="D44" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="D44" s="22" t="s">
+      <c r="E44" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="E44" s="22" t="s">
-        <v>136</v>
-      </c>
       <c r="F44" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G44" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H44" s="15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I44" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J44" s="14">
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="20" t="s">
         <v>20</v>
       </c>
@@ -3766,31 +3763,31 @@
         <v>20</v>
       </c>
       <c r="C45" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="D45" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D45" s="19" t="s">
-        <v>138</v>
-      </c>
       <c r="E45" s="19" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G45" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H45" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I45" s="15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J45" s="14">
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="24" t="s">
         <v>22</v>
       </c>
@@ -3798,31 +3795,31 @@
         <v>21</v>
       </c>
       <c r="C46" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D46" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="D46" s="22" t="s">
+      <c r="E46" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="E46" s="22" t="s">
-        <v>141</v>
-      </c>
       <c r="F46" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="G46" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G46" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="H46" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J46" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="24" t="s">
         <v>20</v>
       </c>
@@ -3830,31 +3827,31 @@
         <v>21</v>
       </c>
       <c r="C47" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="D47" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="D47" s="22" t="s">
-        <v>143</v>
-      </c>
       <c r="E47" s="22" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F47" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H47" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J47" s="9">
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="24" t="s">
         <v>20</v>
       </c>
@@ -3862,31 +3859,31 @@
         <v>21</v>
       </c>
       <c r="C48" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="D48" s="22" t="s">
-        <v>145</v>
-      </c>
       <c r="E48" s="22" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F48" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G48" s="9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J48" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="24" t="s">
         <v>22</v>
       </c>
@@ -3894,31 +3891,31 @@
         <v>21</v>
       </c>
       <c r="C49" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="D49" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="D49" s="22" t="s">
-        <v>147</v>
-      </c>
       <c r="E49" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="F49" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="F49" s="9" t="s">
+      <c r="G49" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="G49" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="H49" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J49" s="9">
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="27" t="s">
         <v>22</v>
       </c>
@@ -3926,2867 +3923,2867 @@
         <v>21</v>
       </c>
       <c r="C50" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="D50" s="22" t="s">
         <v>148</v>
       </c>
-      <c r="D50" s="22" t="s">
+      <c r="E50" s="22" t="s">
         <v>149</v>
       </c>
-      <c r="E50" s="22" t="s">
-        <v>150</v>
-      </c>
       <c r="F50" s="14" t="s">
+        <v>57</v>
+      </c>
+      <c r="G50" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="G50" s="14" t="s">
-        <v>59</v>
-      </c>
       <c r="H50" s="15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I50" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J50" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J51" s="9"/>
     </row>
-    <row r="52" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J52" s="9"/>
     </row>
-    <row r="53" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J53" s="9"/>
     </row>
-    <row r="54" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J54" s="9"/>
     </row>
-    <row r="55" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J55" s="9"/>
     </row>
-    <row r="56" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J56" s="9"/>
     </row>
-    <row r="57" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J57" s="9"/>
     </row>
-    <row r="58" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J58" s="9"/>
     </row>
-    <row r="59" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J59" s="9"/>
     </row>
-    <row r="60" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J60" s="9"/>
     </row>
-    <row r="61" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J61" s="9"/>
     </row>
-    <row r="62" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J62" s="9"/>
     </row>
-    <row r="63" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J63" s="9"/>
     </row>
-    <row r="64" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J64" s="9"/>
     </row>
-    <row r="65" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="65" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J65" s="9"/>
     </row>
-    <row r="66" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="66" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J66" s="9"/>
     </row>
-    <row r="67" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="67" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J67" s="9"/>
     </row>
-    <row r="68" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="68" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J68" s="9"/>
     </row>
-    <row r="69" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="69" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J69" s="9"/>
     </row>
-    <row r="70" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="70" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J70" s="9"/>
     </row>
-    <row r="71" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="71" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J71" s="9"/>
     </row>
-    <row r="72" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="72" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J72" s="9"/>
     </row>
-    <row r="73" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="73" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J73" s="9"/>
     </row>
-    <row r="74" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="74" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J74" s="9"/>
     </row>
-    <row r="75" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="75" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J75" s="9"/>
     </row>
-    <row r="76" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="76" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J76" s="9"/>
     </row>
-    <row r="77" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="77" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J77" s="9"/>
     </row>
-    <row r="78" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="78" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J78" s="9"/>
     </row>
-    <row r="79" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="79" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J79" s="9"/>
     </row>
-    <row r="80" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="80" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J80" s="9"/>
     </row>
-    <row r="81" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="81" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J81" s="9"/>
     </row>
-    <row r="82" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="82" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J82" s="9"/>
     </row>
-    <row r="83" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="83" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J83" s="9"/>
     </row>
-    <row r="84" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="84" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J84" s="9"/>
     </row>
-    <row r="85" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="85" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J85" s="9"/>
     </row>
-    <row r="86" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="86" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J86" s="9"/>
     </row>
-    <row r="87" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="87" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J87" s="9"/>
     </row>
-    <row r="88" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="88" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J88" s="9"/>
     </row>
-    <row r="89" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="89" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J89" s="9"/>
     </row>
-    <row r="90" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="90" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J90" s="9"/>
     </row>
-    <row r="91" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="91" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J91" s="9"/>
     </row>
-    <row r="92" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="92" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J92" s="9"/>
     </row>
-    <row r="93" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="93" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J93" s="9"/>
     </row>
-    <row r="94" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="94" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J94" s="9"/>
     </row>
-    <row r="95" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="95" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J95" s="9"/>
     </row>
-    <row r="96" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="96" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J96" s="9"/>
     </row>
-    <row r="97" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="97" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J97" s="9"/>
     </row>
-    <row r="98" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="98" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J98" s="9"/>
     </row>
-    <row r="99" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="99" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J99" s="9"/>
     </row>
-    <row r="100" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="100" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J100" s="9"/>
     </row>
-    <row r="101" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="101" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J101" s="9"/>
     </row>
-    <row r="102" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="102" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J102" s="9"/>
     </row>
-    <row r="103" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="103" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J103" s="9"/>
     </row>
-    <row r="104" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="104" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J104" s="9"/>
     </row>
-    <row r="105" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="105" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J105" s="9"/>
     </row>
-    <row r="106" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="106" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J106" s="9"/>
     </row>
-    <row r="107" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="107" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J107" s="9"/>
     </row>
-    <row r="108" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="108" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J108" s="9"/>
     </row>
-    <row r="109" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="109" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J109" s="9"/>
     </row>
-    <row r="110" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="110" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J110" s="9"/>
     </row>
-    <row r="111" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="111" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J111" s="9"/>
     </row>
-    <row r="112" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="112" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J112" s="9"/>
     </row>
-    <row r="113" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="113" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J113" s="9"/>
     </row>
-    <row r="114" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="114" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J114" s="9"/>
     </row>
-    <row r="115" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="115" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J115" s="9"/>
     </row>
-    <row r="116" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="116" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J116" s="9"/>
     </row>
-    <row r="117" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="117" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J117" s="9"/>
     </row>
-    <row r="118" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="118" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J118" s="9"/>
     </row>
-    <row r="119" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="119" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J119" s="9"/>
     </row>
-    <row r="120" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="120" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J120" s="9"/>
     </row>
-    <row r="121" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="121" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J121" s="9"/>
     </row>
-    <row r="122" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="122" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J122" s="9"/>
     </row>
-    <row r="123" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="123" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J123" s="9"/>
     </row>
-    <row r="124" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="124" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J124" s="9"/>
     </row>
-    <row r="125" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="125" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J125" s="9"/>
     </row>
-    <row r="126" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="126" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J126" s="9"/>
     </row>
-    <row r="127" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="127" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J127" s="9"/>
     </row>
-    <row r="128" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="128" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J128" s="9"/>
     </row>
-    <row r="129" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="129" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J129" s="9"/>
     </row>
-    <row r="130" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="130" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J130" s="9"/>
     </row>
-    <row r="131" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="131" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J131" s="9"/>
     </row>
-    <row r="132" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="132" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J132" s="9"/>
     </row>
-    <row r="133" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="133" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J133" s="9"/>
     </row>
-    <row r="134" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="134" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J134" s="9"/>
     </row>
-    <row r="135" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="135" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J135" s="9"/>
     </row>
-    <row r="136" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="136" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J136" s="9"/>
     </row>
-    <row r="137" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="137" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J137" s="9"/>
     </row>
-    <row r="138" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="138" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J138" s="9"/>
     </row>
-    <row r="139" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="139" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J139" s="9"/>
     </row>
-    <row r="140" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="140" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J140" s="9"/>
     </row>
-    <row r="141" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="141" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J141" s="9"/>
     </row>
-    <row r="142" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="142" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J142" s="9"/>
     </row>
-    <row r="143" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="143" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J143" s="9"/>
     </row>
-    <row r="144" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="144" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J144" s="9"/>
     </row>
-    <row r="145" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="145" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J145" s="9"/>
     </row>
-    <row r="146" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="146" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J146" s="9"/>
     </row>
-    <row r="147" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="147" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J147" s="9"/>
     </row>
-    <row r="148" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="148" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J148" s="9"/>
     </row>
-    <row r="149" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="149" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J149" s="9"/>
     </row>
-    <row r="150" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="150" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J150" s="9"/>
     </row>
-    <row r="151" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="151" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J151" s="9"/>
     </row>
-    <row r="152" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="152" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J152" s="9"/>
     </row>
-    <row r="153" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="153" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J153" s="9"/>
     </row>
-    <row r="154" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="154" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J154" s="9"/>
     </row>
-    <row r="155" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="155" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J155" s="9"/>
     </row>
-    <row r="156" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="156" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J156" s="9"/>
     </row>
-    <row r="157" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="157" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J157" s="9"/>
     </row>
-    <row r="158" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="158" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J158" s="9"/>
     </row>
-    <row r="159" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="159" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J159" s="9"/>
     </row>
-    <row r="160" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="160" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J160" s="9"/>
     </row>
-    <row r="161" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="161" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J161" s="9"/>
     </row>
-    <row r="162" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="162" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J162" s="9"/>
     </row>
-    <row r="163" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="163" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J163" s="9"/>
     </row>
-    <row r="164" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="164" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J164" s="9"/>
     </row>
-    <row r="165" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="165" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J165" s="9"/>
     </row>
-    <row r="166" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="166" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J166" s="9"/>
     </row>
-    <row r="167" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="167" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J167" s="9"/>
     </row>
-    <row r="168" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="168" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J168" s="9"/>
     </row>
-    <row r="169" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="169" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J169" s="9"/>
     </row>
-    <row r="170" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="170" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J170" s="9"/>
     </row>
-    <row r="171" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="171" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J171" s="9"/>
     </row>
-    <row r="172" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="172" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J172" s="9"/>
     </row>
-    <row r="173" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="173" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J173" s="9"/>
     </row>
-    <row r="174" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="174" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J174" s="9"/>
     </row>
-    <row r="175" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="175" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J175" s="9"/>
     </row>
-    <row r="176" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="176" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J176" s="9"/>
     </row>
-    <row r="177" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="177" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J177" s="9"/>
     </row>
-    <row r="178" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="178" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J178" s="9"/>
     </row>
-    <row r="179" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="179" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J179" s="9"/>
     </row>
-    <row r="180" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="180" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J180" s="9"/>
     </row>
-    <row r="181" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="181" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J181" s="9"/>
     </row>
-    <row r="182" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="182" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J182" s="9"/>
     </row>
-    <row r="183" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="183" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J183" s="9"/>
     </row>
-    <row r="184" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="184" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J184" s="9"/>
     </row>
-    <row r="185" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="185" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J185" s="9"/>
     </row>
-    <row r="186" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="186" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J186" s="9"/>
     </row>
-    <row r="187" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="187" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J187" s="9"/>
     </row>
-    <row r="188" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="188" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J188" s="9"/>
     </row>
-    <row r="189" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="189" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J189" s="9"/>
     </row>
-    <row r="190" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="190" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J190" s="9"/>
     </row>
-    <row r="191" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="191" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J191" s="9"/>
     </row>
-    <row r="192" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="192" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J192" s="9"/>
     </row>
-    <row r="193" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="193" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J193" s="9"/>
     </row>
-    <row r="194" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="194" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J194" s="9"/>
     </row>
-    <row r="195" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="195" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J195" s="9"/>
     </row>
-    <row r="196" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="196" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J196" s="9"/>
     </row>
-    <row r="197" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="197" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J197" s="9"/>
     </row>
-    <row r="198" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="198" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J198" s="9"/>
     </row>
-    <row r="199" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="199" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J199" s="9"/>
     </row>
-    <row r="200" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="200" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J200" s="9"/>
     </row>
-    <row r="201" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="201" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J201" s="9"/>
     </row>
-    <row r="202" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="202" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J202" s="9"/>
     </row>
-    <row r="203" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="203" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J203" s="9"/>
     </row>
-    <row r="204" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="204" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J204" s="9"/>
     </row>
-    <row r="205" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="205" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J205" s="9"/>
     </row>
-    <row r="206" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="206" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J206" s="9"/>
     </row>
-    <row r="207" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="207" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J207" s="9"/>
     </row>
-    <row r="208" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="208" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J208" s="9"/>
     </row>
-    <row r="209" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="209" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J209" s="9"/>
     </row>
-    <row r="210" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="210" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J210" s="9"/>
     </row>
-    <row r="211" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="211" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J211" s="9"/>
     </row>
-    <row r="212" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="212" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J212" s="9"/>
     </row>
-    <row r="213" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="213" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J213" s="9"/>
     </row>
-    <row r="214" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="214" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J214" s="9"/>
     </row>
-    <row r="215" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="215" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J215" s="9"/>
     </row>
-    <row r="216" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="216" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J216" s="9"/>
     </row>
-    <row r="217" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="217" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J217" s="9"/>
     </row>
-    <row r="218" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="218" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J218" s="9"/>
     </row>
-    <row r="219" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="219" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J219" s="9"/>
     </row>
-    <row r="220" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="220" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J220" s="9"/>
     </row>
-    <row r="221" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="221" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J221" s="9"/>
     </row>
-    <row r="222" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="222" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J222" s="9"/>
     </row>
-    <row r="223" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="223" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J223" s="9"/>
     </row>
-    <row r="224" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="224" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J224" s="9"/>
     </row>
-    <row r="225" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="225" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J225" s="9"/>
     </row>
-    <row r="226" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="226" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J226" s="9"/>
     </row>
-    <row r="227" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="227" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J227" s="9"/>
     </row>
-    <row r="228" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="228" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J228" s="9"/>
     </row>
-    <row r="229" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="229" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J229" s="9"/>
     </row>
-    <row r="230" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="230" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J230" s="9"/>
     </row>
-    <row r="231" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="231" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J231" s="9"/>
     </row>
-    <row r="232" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="232" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J232" s="9"/>
     </row>
-    <row r="233" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="233" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J233" s="9"/>
     </row>
-    <row r="234" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="234" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J234" s="9"/>
     </row>
-    <row r="235" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="235" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J235" s="9"/>
     </row>
-    <row r="236" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="236" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J236" s="9"/>
     </row>
-    <row r="237" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="237" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J237" s="9"/>
     </row>
-    <row r="238" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="238" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J238" s="9"/>
     </row>
-    <row r="239" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="239" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J239" s="9"/>
     </row>
-    <row r="240" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="240" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J240" s="9"/>
     </row>
-    <row r="241" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="241" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J241" s="9"/>
     </row>
-    <row r="242" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="242" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J242" s="9"/>
     </row>
-    <row r="243" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="243" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J243" s="9"/>
     </row>
-    <row r="244" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="244" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J244" s="9"/>
     </row>
-    <row r="245" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="245" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J245" s="9"/>
     </row>
-    <row r="246" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="246" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J246" s="9"/>
     </row>
-    <row r="247" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="247" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J247" s="9"/>
     </row>
-    <row r="248" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="248" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J248" s="9"/>
     </row>
-    <row r="249" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="249" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J249" s="9"/>
     </row>
-    <row r="250" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="250" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J250" s="9"/>
     </row>
-    <row r="251" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="251" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J251" s="9"/>
     </row>
-    <row r="252" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="252" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J252" s="9"/>
     </row>
-    <row r="253" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="253" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J253" s="9"/>
     </row>
-    <row r="254" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="254" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J254" s="9"/>
     </row>
-    <row r="255" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="255" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J255" s="9"/>
     </row>
-    <row r="256" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="256" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J256" s="9"/>
     </row>
-    <row r="257" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="257" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J257" s="9"/>
     </row>
-    <row r="258" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="258" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J258" s="9"/>
     </row>
-    <row r="259" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="259" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J259" s="9"/>
     </row>
-    <row r="260" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="260" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J260" s="9"/>
     </row>
-    <row r="261" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="261" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J261" s="9"/>
     </row>
-    <row r="262" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="262" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J262" s="9"/>
     </row>
-    <row r="263" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="263" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J263" s="9"/>
     </row>
-    <row r="264" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="264" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J264" s="9"/>
     </row>
-    <row r="265" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="265" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J265" s="9"/>
     </row>
-    <row r="266" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="266" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J266" s="9"/>
     </row>
-    <row r="267" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="267" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J267" s="9"/>
     </row>
-    <row r="268" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="268" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J268" s="9"/>
     </row>
-    <row r="269" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="269" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J269" s="9"/>
     </row>
-    <row r="270" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="270" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J270" s="9"/>
     </row>
-    <row r="271" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="271" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J271" s="9"/>
     </row>
-    <row r="272" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="272" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J272" s="9"/>
     </row>
-    <row r="273" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="273" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J273" s="9"/>
     </row>
-    <row r="274" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="274" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J274" s="9"/>
     </row>
-    <row r="275" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="275" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J275" s="9"/>
     </row>
-    <row r="276" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="276" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J276" s="9"/>
     </row>
-    <row r="277" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="277" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J277" s="9"/>
     </row>
-    <row r="278" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="278" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J278" s="9"/>
     </row>
-    <row r="279" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="279" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J279" s="9"/>
     </row>
-    <row r="280" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="280" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J280" s="9"/>
     </row>
-    <row r="281" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="281" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J281" s="9"/>
     </row>
-    <row r="282" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="282" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J282" s="9"/>
     </row>
-    <row r="283" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="283" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J283" s="9"/>
     </row>
-    <row r="284" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="284" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J284" s="9"/>
     </row>
-    <row r="285" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="285" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J285" s="9"/>
     </row>
-    <row r="286" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="286" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J286" s="9"/>
     </row>
-    <row r="287" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="287" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J287" s="9"/>
     </row>
-    <row r="288" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="288" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J288" s="9"/>
     </row>
-    <row r="289" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="289" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J289" s="9"/>
     </row>
-    <row r="290" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="290" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J290" s="9"/>
     </row>
-    <row r="291" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="291" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J291" s="9"/>
     </row>
-    <row r="292" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="292" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J292" s="9"/>
     </row>
-    <row r="293" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="293" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J293" s="9"/>
     </row>
-    <row r="294" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="294" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J294" s="9"/>
     </row>
-    <row r="295" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="295" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J295" s="9"/>
     </row>
-    <row r="296" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="296" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J296" s="9"/>
     </row>
-    <row r="297" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="297" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J297" s="9"/>
     </row>
-    <row r="298" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="298" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J298" s="9"/>
     </row>
-    <row r="299" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="299" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J299" s="9"/>
     </row>
-    <row r="300" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="300" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J300" s="9"/>
     </row>
-    <row r="301" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="301" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J301" s="9"/>
     </row>
-    <row r="302" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="302" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J302" s="9"/>
     </row>
-    <row r="303" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="303" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J303" s="9"/>
     </row>
-    <row r="304" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="304" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J304" s="9"/>
     </row>
-    <row r="305" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="305" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J305" s="9"/>
     </row>
-    <row r="306" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="306" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J306" s="9"/>
     </row>
-    <row r="307" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="307" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J307" s="9"/>
     </row>
-    <row r="308" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="308" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J308" s="9"/>
     </row>
-    <row r="309" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="309" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J309" s="9"/>
     </row>
-    <row r="310" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="310" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J310" s="9"/>
     </row>
-    <row r="311" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="311" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J311" s="9"/>
     </row>
-    <row r="312" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="312" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J312" s="9"/>
     </row>
-    <row r="313" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="313" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J313" s="9"/>
     </row>
-    <row r="314" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="314" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J314" s="9"/>
     </row>
-    <row r="315" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="315" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J315" s="9"/>
     </row>
-    <row r="316" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="316" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J316" s="9"/>
     </row>
-    <row r="317" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="317" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J317" s="9"/>
     </row>
-    <row r="318" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="318" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J318" s="9"/>
     </row>
-    <row r="319" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="319" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J319" s="9"/>
     </row>
-    <row r="320" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="320" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J320" s="9"/>
     </row>
-    <row r="321" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="321" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J321" s="9"/>
     </row>
-    <row r="322" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="322" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J322" s="9"/>
     </row>
-    <row r="323" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="323" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J323" s="9"/>
     </row>
-    <row r="324" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="324" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J324" s="9"/>
     </row>
-    <row r="325" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="325" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J325" s="9"/>
     </row>
-    <row r="326" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="326" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J326" s="9"/>
     </row>
-    <row r="327" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="327" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J327" s="9"/>
     </row>
-    <row r="328" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="328" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J328" s="9"/>
     </row>
-    <row r="329" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="329" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J329" s="9"/>
     </row>
-    <row r="330" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="330" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J330" s="9"/>
     </row>
-    <row r="331" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="331" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J331" s="9"/>
     </row>
-    <row r="332" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="332" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J332" s="9"/>
     </row>
-    <row r="333" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="333" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J333" s="9"/>
     </row>
-    <row r="334" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="334" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J334" s="9"/>
     </row>
-    <row r="335" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="335" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J335" s="9"/>
     </row>
-    <row r="336" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="336" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J336" s="9"/>
     </row>
-    <row r="337" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="337" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J337" s="9"/>
     </row>
-    <row r="338" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="338" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J338" s="9"/>
     </row>
-    <row r="339" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="339" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J339" s="9"/>
     </row>
-    <row r="340" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="340" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J340" s="9"/>
     </row>
-    <row r="341" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="341" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J341" s="9"/>
     </row>
-    <row r="342" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="342" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J342" s="9"/>
     </row>
-    <row r="343" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="343" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J343" s="9"/>
     </row>
-    <row r="344" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="344" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J344" s="9"/>
     </row>
-    <row r="345" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="345" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J345" s="9"/>
     </row>
-    <row r="346" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="346" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J346" s="9"/>
     </row>
-    <row r="347" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="347" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J347" s="9"/>
     </row>
-    <row r="348" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="348" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J348" s="9"/>
     </row>
-    <row r="349" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="349" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J349" s="9"/>
     </row>
-    <row r="350" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="350" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J350" s="9"/>
     </row>
-    <row r="351" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="351" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J351" s="9"/>
     </row>
-    <row r="352" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="352" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J352" s="9"/>
     </row>
-    <row r="353" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="353" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J353" s="9"/>
     </row>
-    <row r="354" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="354" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J354" s="9"/>
     </row>
-    <row r="355" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="355" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J355" s="9"/>
     </row>
-    <row r="356" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="356" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J356" s="9"/>
     </row>
-    <row r="357" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="357" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J357" s="9"/>
     </row>
-    <row r="358" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="358" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J358" s="9"/>
     </row>
-    <row r="359" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="359" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J359" s="9"/>
     </row>
-    <row r="360" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="360" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J360" s="9"/>
     </row>
-    <row r="361" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="361" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J361" s="9"/>
     </row>
-    <row r="362" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="362" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J362" s="9"/>
     </row>
-    <row r="363" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="363" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J363" s="9"/>
     </row>
-    <row r="364" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="364" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J364" s="9"/>
     </row>
-    <row r="365" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="365" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J365" s="9"/>
     </row>
-    <row r="366" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="366" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J366" s="9"/>
     </row>
-    <row r="367" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="367" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J367" s="9"/>
     </row>
-    <row r="368" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="368" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J368" s="9"/>
     </row>
-    <row r="369" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="369" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J369" s="9"/>
     </row>
-    <row r="370" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="370" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J370" s="9"/>
     </row>
-    <row r="371" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="371" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J371" s="9"/>
     </row>
-    <row r="372" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="372" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J372" s="9"/>
     </row>
-    <row r="373" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="373" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J373" s="9"/>
     </row>
-    <row r="374" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="374" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J374" s="9"/>
     </row>
-    <row r="375" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="375" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J375" s="9"/>
     </row>
-    <row r="376" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="376" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J376" s="9"/>
     </row>
-    <row r="377" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="377" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J377" s="9"/>
     </row>
-    <row r="378" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="378" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J378" s="9"/>
     </row>
-    <row r="379" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="379" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J379" s="9"/>
     </row>
-    <row r="380" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="380" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J380" s="9"/>
     </row>
-    <row r="381" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="381" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J381" s="9"/>
     </row>
-    <row r="382" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="382" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J382" s="9"/>
     </row>
-    <row r="383" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="383" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J383" s="9"/>
     </row>
-    <row r="384" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="384" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J384" s="9"/>
     </row>
-    <row r="385" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="385" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J385" s="9"/>
     </row>
-    <row r="386" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="386" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J386" s="9"/>
     </row>
-    <row r="387" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="387" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J387" s="9"/>
     </row>
-    <row r="388" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="388" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J388" s="9"/>
     </row>
-    <row r="389" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="389" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J389" s="9"/>
     </row>
-    <row r="390" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="390" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J390" s="9"/>
     </row>
-    <row r="391" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="391" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J391" s="9"/>
     </row>
-    <row r="392" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="392" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J392" s="9"/>
     </row>
-    <row r="393" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="393" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J393" s="9"/>
     </row>
-    <row r="394" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="394" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J394" s="9"/>
     </row>
-    <row r="395" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="395" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J395" s="9"/>
     </row>
-    <row r="396" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="396" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J396" s="9"/>
     </row>
-    <row r="397" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="397" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J397" s="9"/>
     </row>
-    <row r="398" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="398" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J398" s="9"/>
     </row>
-    <row r="399" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="399" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J399" s="9"/>
     </row>
-    <row r="400" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="400" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J400" s="9"/>
     </row>
-    <row r="401" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="401" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J401" s="9"/>
     </row>
-    <row r="402" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="402" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J402" s="9"/>
     </row>
-    <row r="403" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="403" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J403" s="9"/>
     </row>
-    <row r="404" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="404" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J404" s="9"/>
     </row>
-    <row r="405" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="405" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J405" s="9"/>
     </row>
-    <row r="406" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="406" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J406" s="9"/>
     </row>
-    <row r="407" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="407" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J407" s="9"/>
     </row>
-    <row r="408" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="408" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J408" s="9"/>
     </row>
-    <row r="409" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="409" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J409" s="9"/>
     </row>
-    <row r="410" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="410" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J410" s="9"/>
     </row>
-    <row r="411" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="411" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J411" s="9"/>
     </row>
-    <row r="412" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="412" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J412" s="9"/>
     </row>
-    <row r="413" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="413" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J413" s="9"/>
     </row>
-    <row r="414" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="414" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J414" s="9"/>
     </row>
-    <row r="415" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="415" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J415" s="9"/>
     </row>
-    <row r="416" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="416" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J416" s="9"/>
     </row>
-    <row r="417" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="417" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J417" s="9"/>
     </row>
-    <row r="418" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="418" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J418" s="9"/>
     </row>
-    <row r="419" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="419" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J419" s="9"/>
     </row>
-    <row r="420" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="420" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J420" s="9"/>
     </row>
-    <row r="421" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="421" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J421" s="9"/>
     </row>
-    <row r="422" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="422" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J422" s="9"/>
     </row>
-    <row r="423" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="423" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J423" s="9"/>
     </row>
-    <row r="424" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="424" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J424" s="9"/>
     </row>
-    <row r="425" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="425" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J425" s="9"/>
     </row>
-    <row r="426" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="426" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J426" s="9"/>
     </row>
-    <row r="427" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="427" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J427" s="9"/>
     </row>
-    <row r="428" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="428" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J428" s="9"/>
     </row>
-    <row r="429" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="429" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J429" s="9"/>
     </row>
-    <row r="430" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="430" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J430" s="9"/>
     </row>
-    <row r="431" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="431" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J431" s="9"/>
     </row>
-    <row r="432" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="432" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J432" s="9"/>
     </row>
-    <row r="433" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="433" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J433" s="9"/>
     </row>
-    <row r="434" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="434" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J434" s="9"/>
     </row>
-    <row r="435" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="435" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J435" s="9"/>
     </row>
-    <row r="436" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="436" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J436" s="9"/>
     </row>
-    <row r="437" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="437" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J437" s="9"/>
     </row>
-    <row r="438" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="438" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J438" s="9"/>
     </row>
-    <row r="439" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="439" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J439" s="9"/>
     </row>
-    <row r="440" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="440" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J440" s="9"/>
     </row>
-    <row r="441" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="441" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J441" s="9"/>
     </row>
-    <row r="442" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="442" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J442" s="9"/>
     </row>
-    <row r="443" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="443" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J443" s="9"/>
     </row>
-    <row r="444" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="444" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J444" s="9"/>
     </row>
-    <row r="445" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="445" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J445" s="9"/>
     </row>
-    <row r="446" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="446" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J446" s="9"/>
     </row>
-    <row r="447" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="447" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J447" s="9"/>
     </row>
-    <row r="448" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="448" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J448" s="9"/>
     </row>
-    <row r="449" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="449" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J449" s="9"/>
     </row>
-    <row r="450" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="450" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J450" s="9"/>
     </row>
-    <row r="451" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="451" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J451" s="9"/>
     </row>
-    <row r="452" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="452" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J452" s="9"/>
     </row>
-    <row r="453" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="453" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J453" s="9"/>
     </row>
-    <row r="454" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="454" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J454" s="9"/>
     </row>
-    <row r="455" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="455" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J455" s="9"/>
     </row>
-    <row r="456" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="456" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J456" s="9"/>
     </row>
-    <row r="457" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="457" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J457" s="9"/>
     </row>
-    <row r="458" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="458" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J458" s="9"/>
     </row>
-    <row r="459" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="459" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J459" s="9"/>
     </row>
-    <row r="460" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="460" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J460" s="9"/>
     </row>
-    <row r="461" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="461" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J461" s="9"/>
     </row>
-    <row r="462" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="462" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J462" s="9"/>
     </row>
-    <row r="463" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="463" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J463" s="9"/>
     </row>
-    <row r="464" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="464" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J464" s="9"/>
     </row>
-    <row r="465" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="465" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J465" s="9"/>
     </row>
-    <row r="466" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="466" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J466" s="9"/>
     </row>
-    <row r="467" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="467" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J467" s="9"/>
     </row>
-    <row r="468" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="468" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J468" s="9"/>
     </row>
-    <row r="469" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="469" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J469" s="9"/>
     </row>
-    <row r="470" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="470" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J470" s="9"/>
     </row>
-    <row r="471" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="471" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J471" s="9"/>
     </row>
-    <row r="472" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="472" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J472" s="9"/>
     </row>
-    <row r="473" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="473" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J473" s="9"/>
     </row>
-    <row r="474" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="474" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J474" s="9"/>
     </row>
-    <row r="475" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="475" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J475" s="9"/>
     </row>
-    <row r="476" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="476" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J476" s="9"/>
     </row>
-    <row r="477" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="477" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J477" s="9"/>
     </row>
-    <row r="478" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="478" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J478" s="9"/>
     </row>
-    <row r="479" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="479" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J479" s="9"/>
     </row>
-    <row r="480" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="480" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J480" s="9"/>
     </row>
-    <row r="481" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="481" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J481" s="9"/>
     </row>
-    <row r="482" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="482" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J482" s="9"/>
     </row>
-    <row r="483" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="483" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J483" s="9"/>
     </row>
-    <row r="484" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="484" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J484" s="9"/>
     </row>
-    <row r="485" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="485" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J485" s="9"/>
     </row>
-    <row r="486" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="486" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J486" s="9"/>
     </row>
-    <row r="487" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="487" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J487" s="9"/>
     </row>
-    <row r="488" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="488" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J488" s="9"/>
     </row>
-    <row r="489" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="489" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J489" s="9"/>
     </row>
-    <row r="490" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="490" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J490" s="9"/>
     </row>
-    <row r="491" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="491" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J491" s="9"/>
     </row>
-    <row r="492" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="492" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J492" s="9"/>
     </row>
-    <row r="493" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="493" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J493" s="9"/>
     </row>
-    <row r="494" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="494" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J494" s="9"/>
     </row>
-    <row r="495" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="495" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J495" s="9"/>
     </row>
-    <row r="496" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="496" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J496" s="9"/>
     </row>
-    <row r="497" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="497" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J497" s="9"/>
     </row>
-    <row r="498" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="498" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J498" s="9"/>
     </row>
-    <row r="499" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="499" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J499" s="9"/>
     </row>
-    <row r="500" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="500" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J500" s="9"/>
     </row>
-    <row r="501" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="501" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J501" s="9"/>
     </row>
-    <row r="502" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="502" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J502" s="9"/>
     </row>
-    <row r="503" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="503" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J503" s="9"/>
     </row>
-    <row r="504" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="504" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J504" s="9"/>
     </row>
-    <row r="505" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="505" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J505" s="9"/>
     </row>
-    <row r="506" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="506" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J506" s="9"/>
     </row>
-    <row r="507" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="507" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J507" s="9"/>
     </row>
-    <row r="508" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="508" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J508" s="9"/>
     </row>
-    <row r="509" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="509" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J509" s="9"/>
     </row>
-    <row r="510" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="510" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J510" s="9"/>
     </row>
-    <row r="511" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="511" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J511" s="9"/>
     </row>
-    <row r="512" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="512" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J512" s="9"/>
     </row>
-    <row r="513" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="513" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J513" s="9"/>
     </row>
-    <row r="514" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="514" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J514" s="9"/>
     </row>
-    <row r="515" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="515" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J515" s="9"/>
     </row>
-    <row r="516" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="516" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J516" s="9"/>
     </row>
-    <row r="517" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="517" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J517" s="9"/>
     </row>
-    <row r="518" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="518" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J518" s="9"/>
     </row>
-    <row r="519" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="519" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J519" s="9"/>
     </row>
-    <row r="520" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="520" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J520" s="9"/>
     </row>
-    <row r="521" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="521" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J521" s="9"/>
     </row>
-    <row r="522" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="522" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J522" s="9"/>
     </row>
-    <row r="523" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="523" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J523" s="9"/>
     </row>
-    <row r="524" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="524" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J524" s="9"/>
     </row>
-    <row r="525" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="525" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J525" s="9"/>
     </row>
-    <row r="526" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="526" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J526" s="9"/>
     </row>
-    <row r="527" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="527" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J527" s="9"/>
     </row>
-    <row r="528" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="528" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J528" s="9"/>
     </row>
-    <row r="529" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="529" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J529" s="9"/>
     </row>
-    <row r="530" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="530" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J530" s="9"/>
     </row>
-    <row r="531" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="531" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J531" s="9"/>
     </row>
-    <row r="532" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="532" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J532" s="9"/>
     </row>
-    <row r="533" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="533" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J533" s="9"/>
     </row>
-    <row r="534" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="534" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J534" s="9"/>
     </row>
-    <row r="535" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="535" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J535" s="9"/>
     </row>
-    <row r="536" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="536" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J536" s="9"/>
     </row>
-    <row r="537" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="537" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J537" s="9"/>
     </row>
-    <row r="538" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="538" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J538" s="9"/>
     </row>
-    <row r="539" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="539" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J539" s="9"/>
     </row>
-    <row r="540" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="540" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J540" s="9"/>
     </row>
-    <row r="541" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="541" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J541" s="9"/>
     </row>
-    <row r="542" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="542" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J542" s="9"/>
     </row>
-    <row r="543" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="543" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J543" s="9"/>
     </row>
-    <row r="544" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="544" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J544" s="9"/>
     </row>
-    <row r="545" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="545" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J545" s="9"/>
     </row>
-    <row r="546" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="546" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J546" s="9"/>
     </row>
-    <row r="547" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="547" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J547" s="9"/>
     </row>
-    <row r="548" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="548" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J548" s="9"/>
     </row>
-    <row r="549" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="549" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J549" s="9"/>
     </row>
-    <row r="550" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="550" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J550" s="9"/>
     </row>
-    <row r="551" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="551" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J551" s="9"/>
     </row>
-    <row r="552" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="552" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J552" s="9"/>
     </row>
-    <row r="553" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="553" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J553" s="9"/>
     </row>
-    <row r="554" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="554" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J554" s="9"/>
     </row>
-    <row r="555" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="555" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J555" s="9"/>
     </row>
-    <row r="556" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="556" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J556" s="9"/>
     </row>
-    <row r="557" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="557" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J557" s="9"/>
     </row>
-    <row r="558" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="558" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J558" s="9"/>
     </row>
-    <row r="559" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="559" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J559" s="9"/>
     </row>
-    <row r="560" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="560" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J560" s="9"/>
     </row>
-    <row r="561" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="561" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J561" s="9"/>
     </row>
-    <row r="562" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="562" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J562" s="9"/>
     </row>
-    <row r="563" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="563" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J563" s="9"/>
     </row>
-    <row r="564" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="564" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J564" s="9"/>
     </row>
-    <row r="565" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="565" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J565" s="9"/>
     </row>
-    <row r="566" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="566" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J566" s="9"/>
     </row>
-    <row r="567" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="567" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J567" s="9"/>
     </row>
-    <row r="568" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="568" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J568" s="9"/>
     </row>
-    <row r="569" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="569" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J569" s="9"/>
     </row>
-    <row r="570" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="570" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J570" s="9"/>
     </row>
-    <row r="571" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="571" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J571" s="9"/>
     </row>
-    <row r="572" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="572" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J572" s="9"/>
     </row>
-    <row r="573" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="573" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J573" s="9"/>
     </row>
-    <row r="574" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="574" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J574" s="9"/>
     </row>
-    <row r="575" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="575" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J575" s="9"/>
     </row>
-    <row r="576" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="576" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J576" s="9"/>
     </row>
-    <row r="577" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="577" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J577" s="9"/>
     </row>
-    <row r="578" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="578" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J578" s="9"/>
     </row>
-    <row r="579" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="579" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J579" s="9"/>
     </row>
-    <row r="580" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="580" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J580" s="9"/>
     </row>
-    <row r="581" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="581" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J581" s="9"/>
     </row>
-    <row r="582" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="582" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J582" s="9"/>
     </row>
-    <row r="583" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="583" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J583" s="9"/>
     </row>
-    <row r="584" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="584" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J584" s="9"/>
     </row>
-    <row r="585" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="585" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J585" s="9"/>
     </row>
-    <row r="586" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="586" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J586" s="9"/>
     </row>
-    <row r="587" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="587" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J587" s="9"/>
     </row>
-    <row r="588" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="588" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J588" s="9"/>
     </row>
-    <row r="589" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="589" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J589" s="9"/>
     </row>
-    <row r="590" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="590" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J590" s="9"/>
     </row>
-    <row r="591" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="591" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J591" s="9"/>
     </row>
-    <row r="592" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="592" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J592" s="9"/>
     </row>
-    <row r="593" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="593" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J593" s="9"/>
     </row>
-    <row r="594" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="594" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J594" s="9"/>
     </row>
-    <row r="595" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="595" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J595" s="9"/>
     </row>
-    <row r="596" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="596" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J596" s="9"/>
     </row>
-    <row r="597" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="597" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J597" s="9"/>
     </row>
-    <row r="598" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="598" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J598" s="9"/>
     </row>
-    <row r="599" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="599" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J599" s="9"/>
     </row>
-    <row r="600" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="600" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J600" s="9"/>
     </row>
-    <row r="601" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="601" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J601" s="9"/>
     </row>
-    <row r="602" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="602" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J602" s="9"/>
     </row>
-    <row r="603" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="603" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J603" s="9"/>
     </row>
-    <row r="604" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="604" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J604" s="9"/>
     </row>
-    <row r="605" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="605" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J605" s="9"/>
     </row>
-    <row r="606" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="606" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J606" s="9"/>
     </row>
-    <row r="607" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="607" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J607" s="9"/>
     </row>
-    <row r="608" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="608" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J608" s="9"/>
     </row>
-    <row r="609" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="609" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J609" s="9"/>
     </row>
-    <row r="610" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="610" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J610" s="9"/>
     </row>
-    <row r="611" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="611" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J611" s="9"/>
     </row>
-    <row r="612" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="612" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J612" s="9"/>
     </row>
-    <row r="613" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="613" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J613" s="9"/>
     </row>
-    <row r="614" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="614" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J614" s="9"/>
     </row>
-    <row r="615" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="615" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J615" s="9"/>
     </row>
-    <row r="616" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="616" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J616" s="9"/>
     </row>
-    <row r="617" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="617" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J617" s="9"/>
     </row>
-    <row r="618" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="618" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J618" s="9"/>
     </row>
-    <row r="619" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="619" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J619" s="9"/>
     </row>
-    <row r="620" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="620" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J620" s="9"/>
     </row>
-    <row r="621" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="621" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J621" s="9"/>
     </row>
-    <row r="622" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="622" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J622" s="9"/>
     </row>
-    <row r="623" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="623" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J623" s="9"/>
     </row>
-    <row r="624" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="624" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J624" s="9"/>
     </row>
-    <row r="625" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="625" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J625" s="9"/>
     </row>
-    <row r="626" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="626" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J626" s="9"/>
     </row>
-    <row r="627" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="627" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J627" s="9"/>
     </row>
-    <row r="628" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="628" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J628" s="9"/>
     </row>
-    <row r="629" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="629" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J629" s="9"/>
     </row>
-    <row r="630" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="630" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J630" s="9"/>
     </row>
-    <row r="631" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="631" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J631" s="9"/>
     </row>
-    <row r="632" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="632" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J632" s="9"/>
     </row>
-    <row r="633" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="633" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J633" s="9"/>
     </row>
-    <row r="634" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="634" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J634" s="9"/>
     </row>
-    <row r="635" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="635" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J635" s="9"/>
     </row>
-    <row r="636" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="636" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J636" s="9"/>
     </row>
-    <row r="637" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="637" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J637" s="9"/>
     </row>
-    <row r="638" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="638" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J638" s="9"/>
     </row>
-    <row r="639" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="639" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J639" s="9"/>
     </row>
-    <row r="640" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="640" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J640" s="9"/>
     </row>
-    <row r="641" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="641" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J641" s="9"/>
     </row>
-    <row r="642" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="642" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J642" s="9"/>
     </row>
-    <row r="643" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="643" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J643" s="9"/>
     </row>
-    <row r="644" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="644" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J644" s="9"/>
     </row>
-    <row r="645" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="645" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J645" s="9"/>
     </row>
-    <row r="646" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="646" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J646" s="9"/>
     </row>
-    <row r="647" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="647" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J647" s="9"/>
     </row>
-    <row r="648" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="648" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J648" s="9"/>
     </row>
-    <row r="649" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="649" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J649" s="9"/>
     </row>
-    <row r="650" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="650" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J650" s="9"/>
     </row>
-    <row r="651" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="651" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J651" s="9"/>
     </row>
-    <row r="652" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="652" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J652" s="9"/>
     </row>
-    <row r="653" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="653" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J653" s="9"/>
     </row>
-    <row r="654" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="654" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J654" s="9"/>
     </row>
-    <row r="655" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="655" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J655" s="9"/>
     </row>
-    <row r="656" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="656" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J656" s="9"/>
     </row>
-    <row r="657" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="657" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J657" s="9"/>
     </row>
-    <row r="658" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="658" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J658" s="9"/>
     </row>
-    <row r="659" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="659" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J659" s="9"/>
     </row>
-    <row r="660" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="660" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J660" s="9"/>
     </row>
-    <row r="661" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="661" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J661" s="9"/>
     </row>
-    <row r="662" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="662" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J662" s="9"/>
     </row>
-    <row r="663" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="663" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J663" s="9"/>
     </row>
-    <row r="664" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="664" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J664" s="9"/>
     </row>
-    <row r="665" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="665" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J665" s="9"/>
     </row>
-    <row r="666" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="666" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J666" s="9"/>
     </row>
-    <row r="667" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="667" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J667" s="9"/>
     </row>
-    <row r="668" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="668" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J668" s="9"/>
     </row>
-    <row r="669" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="669" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J669" s="9"/>
     </row>
-    <row r="670" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="670" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J670" s="9"/>
     </row>
-    <row r="671" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="671" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J671" s="9"/>
     </row>
-    <row r="672" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="672" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J672" s="9"/>
     </row>
-    <row r="673" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="673" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J673" s="9"/>
     </row>
-    <row r="674" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="674" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J674" s="9"/>
     </row>
-    <row r="675" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="675" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J675" s="9"/>
     </row>
-    <row r="676" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="676" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J676" s="9"/>
     </row>
-    <row r="677" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="677" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J677" s="9"/>
     </row>
-    <row r="678" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="678" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J678" s="9"/>
     </row>
-    <row r="679" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="679" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J679" s="9"/>
     </row>
-    <row r="680" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="680" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J680" s="9"/>
     </row>
-    <row r="681" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="681" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J681" s="9"/>
     </row>
-    <row r="682" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="682" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J682" s="9"/>
     </row>
-    <row r="683" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="683" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J683" s="9"/>
     </row>
-    <row r="684" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="684" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J684" s="9"/>
     </row>
-    <row r="685" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="685" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J685" s="9"/>
     </row>
-    <row r="686" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="686" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J686" s="9"/>
     </row>
-    <row r="687" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="687" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J687" s="9"/>
     </row>
-    <row r="688" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="688" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J688" s="9"/>
     </row>
-    <row r="689" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="689" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J689" s="9"/>
     </row>
-    <row r="690" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="690" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J690" s="9"/>
     </row>
-    <row r="691" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="691" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J691" s="9"/>
     </row>
-    <row r="692" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="692" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J692" s="9"/>
     </row>
-    <row r="693" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="693" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J693" s="9"/>
     </row>
-    <row r="694" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="694" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J694" s="9"/>
     </row>
-    <row r="695" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="695" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J695" s="9"/>
     </row>
-    <row r="696" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="696" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J696" s="9"/>
     </row>
-    <row r="697" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="697" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J697" s="9"/>
     </row>
-    <row r="698" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="698" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J698" s="9"/>
     </row>
-    <row r="699" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="699" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J699" s="9"/>
     </row>
-    <row r="700" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="700" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J700" s="9"/>
     </row>
-    <row r="701" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="701" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J701" s="9"/>
     </row>
-    <row r="702" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="702" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J702" s="9"/>
     </row>
-    <row r="703" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="703" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J703" s="9"/>
     </row>
-    <row r="704" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="704" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J704" s="9"/>
     </row>
-    <row r="705" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="705" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J705" s="9"/>
     </row>
-    <row r="706" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="706" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J706" s="9"/>
     </row>
-    <row r="707" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="707" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J707" s="9"/>
     </row>
-    <row r="708" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="708" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J708" s="9"/>
     </row>
-    <row r="709" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="709" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J709" s="9"/>
     </row>
-    <row r="710" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="710" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J710" s="9"/>
     </row>
-    <row r="711" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="711" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J711" s="9"/>
     </row>
-    <row r="712" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="712" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J712" s="9"/>
     </row>
-    <row r="713" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="713" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J713" s="9"/>
     </row>
-    <row r="714" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="714" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J714" s="9"/>
     </row>
-    <row r="715" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="715" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J715" s="9"/>
     </row>
-    <row r="716" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="716" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J716" s="9"/>
     </row>
-    <row r="717" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="717" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J717" s="9"/>
     </row>
-    <row r="718" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="718" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J718" s="9"/>
     </row>
-    <row r="719" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="719" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J719" s="9"/>
     </row>
-    <row r="720" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="720" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J720" s="9"/>
     </row>
-    <row r="721" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="721" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J721" s="9"/>
     </row>
-    <row r="722" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="722" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J722" s="9"/>
     </row>
-    <row r="723" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="723" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J723" s="9"/>
     </row>
-    <row r="724" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="724" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J724" s="9"/>
     </row>
-    <row r="725" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="725" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J725" s="9"/>
     </row>
-    <row r="726" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="726" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J726" s="9"/>
     </row>
-    <row r="727" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="727" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J727" s="9"/>
     </row>
-    <row r="728" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="728" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J728" s="9"/>
     </row>
-    <row r="729" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="729" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J729" s="9"/>
     </row>
-    <row r="730" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="730" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J730" s="9"/>
     </row>
-    <row r="731" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="731" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J731" s="9"/>
     </row>
-    <row r="732" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="732" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J732" s="9"/>
     </row>
-    <row r="733" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="733" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J733" s="9"/>
     </row>
-    <row r="734" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="734" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J734" s="9"/>
     </row>
-    <row r="735" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="735" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J735" s="9"/>
     </row>
-    <row r="736" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="736" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J736" s="9"/>
     </row>
-    <row r="737" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="737" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J737" s="9"/>
     </row>
-    <row r="738" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="738" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J738" s="9"/>
     </row>
-    <row r="739" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="739" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J739" s="9"/>
     </row>
-    <row r="740" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="740" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J740" s="9"/>
     </row>
-    <row r="741" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="741" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J741" s="9"/>
     </row>
-    <row r="742" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="742" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J742" s="9"/>
     </row>
-    <row r="743" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="743" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J743" s="9"/>
     </row>
-    <row r="744" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="744" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J744" s="9"/>
     </row>
-    <row r="745" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="745" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J745" s="9"/>
     </row>
-    <row r="746" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="746" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J746" s="9"/>
     </row>
-    <row r="747" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="747" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J747" s="9"/>
     </row>
-    <row r="748" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="748" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J748" s="9"/>
     </row>
-    <row r="749" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="749" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J749" s="9"/>
     </row>
-    <row r="750" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="750" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J750" s="9"/>
     </row>
-    <row r="751" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="751" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J751" s="9"/>
     </row>
-    <row r="752" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="752" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J752" s="9"/>
     </row>
-    <row r="753" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="753" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J753" s="9"/>
     </row>
-    <row r="754" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="754" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J754" s="9"/>
     </row>
-    <row r="755" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="755" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J755" s="9"/>
     </row>
-    <row r="756" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="756" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J756" s="9"/>
     </row>
-    <row r="757" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="757" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J757" s="9"/>
     </row>
-    <row r="758" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="758" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J758" s="9"/>
     </row>
-    <row r="759" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="759" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J759" s="9"/>
     </row>
-    <row r="760" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="760" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J760" s="9"/>
     </row>
-    <row r="761" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="761" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J761" s="9"/>
     </row>
-    <row r="762" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="762" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J762" s="9"/>
     </row>
-    <row r="763" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="763" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J763" s="9"/>
     </row>
-    <row r="764" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="764" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J764" s="9"/>
     </row>
-    <row r="765" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="765" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J765" s="9"/>
     </row>
-    <row r="766" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="766" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J766" s="9"/>
     </row>
-    <row r="767" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="767" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J767" s="9"/>
     </row>
-    <row r="768" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="768" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J768" s="9"/>
     </row>
-    <row r="769" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="769" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J769" s="9"/>
     </row>
-    <row r="770" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="770" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J770" s="9"/>
     </row>
-    <row r="771" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="771" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J771" s="9"/>
     </row>
-    <row r="772" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="772" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J772" s="9"/>
     </row>
-    <row r="773" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="773" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J773" s="9"/>
     </row>
-    <row r="774" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="774" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J774" s="9"/>
     </row>
-    <row r="775" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="775" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J775" s="9"/>
     </row>
-    <row r="776" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="776" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J776" s="9"/>
     </row>
-    <row r="777" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="777" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J777" s="9"/>
     </row>
-    <row r="778" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="778" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J778" s="9"/>
     </row>
-    <row r="779" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="779" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J779" s="9"/>
     </row>
-    <row r="780" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="780" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J780" s="9"/>
     </row>
-    <row r="781" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="781" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J781" s="9"/>
     </row>
-    <row r="782" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="782" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J782" s="9"/>
     </row>
-    <row r="783" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="783" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J783" s="9"/>
     </row>
-    <row r="784" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="784" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J784" s="9"/>
     </row>
-    <row r="785" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="785" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J785" s="9"/>
     </row>
-    <row r="786" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="786" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J786" s="9"/>
     </row>
-    <row r="787" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="787" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J787" s="9"/>
     </row>
-    <row r="788" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="788" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J788" s="9"/>
     </row>
-    <row r="789" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="789" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J789" s="9"/>
     </row>
-    <row r="790" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="790" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J790" s="9"/>
     </row>
-    <row r="791" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="791" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J791" s="9"/>
     </row>
-    <row r="792" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="792" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J792" s="9"/>
     </row>
-    <row r="793" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="793" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J793" s="9"/>
     </row>
-    <row r="794" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="794" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J794" s="9"/>
     </row>
-    <row r="795" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="795" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J795" s="9"/>
     </row>
-    <row r="796" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="796" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J796" s="9"/>
     </row>
-    <row r="797" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="797" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J797" s="9"/>
     </row>
-    <row r="798" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="798" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J798" s="9"/>
     </row>
-    <row r="799" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="799" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J799" s="9"/>
     </row>
-    <row r="800" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="800" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J800" s="9"/>
     </row>
-    <row r="801" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="801" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J801" s="9"/>
     </row>
-    <row r="802" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="802" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J802" s="9"/>
     </row>
-    <row r="803" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="803" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J803" s="9"/>
     </row>
-    <row r="804" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="804" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J804" s="9"/>
     </row>
-    <row r="805" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="805" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J805" s="9"/>
     </row>
-    <row r="806" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="806" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J806" s="9"/>
     </row>
-    <row r="807" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="807" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J807" s="9"/>
     </row>
-    <row r="808" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="808" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J808" s="9"/>
     </row>
-    <row r="809" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="809" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J809" s="9"/>
     </row>
-    <row r="810" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="810" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J810" s="9"/>
     </row>
-    <row r="811" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="811" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J811" s="9"/>
     </row>
-    <row r="812" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="812" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J812" s="9"/>
     </row>
-    <row r="813" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="813" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J813" s="9"/>
     </row>
-    <row r="814" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="814" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J814" s="9"/>
     </row>
-    <row r="815" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="815" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J815" s="9"/>
     </row>
-    <row r="816" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="816" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J816" s="9"/>
     </row>
-    <row r="817" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="817" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J817" s="9"/>
     </row>
-    <row r="818" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="818" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J818" s="9"/>
     </row>
-    <row r="819" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="819" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J819" s="9"/>
     </row>
-    <row r="820" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="820" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J820" s="9"/>
     </row>
-    <row r="821" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="821" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J821" s="9"/>
     </row>
-    <row r="822" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="822" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J822" s="9"/>
     </row>
-    <row r="823" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="823" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J823" s="9"/>
     </row>
-    <row r="824" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="824" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J824" s="9"/>
     </row>
-    <row r="825" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="825" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J825" s="9"/>
     </row>
-    <row r="826" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="826" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J826" s="9"/>
     </row>
-    <row r="827" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="827" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J827" s="9"/>
     </row>
-    <row r="828" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="828" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J828" s="9"/>
     </row>
-    <row r="829" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="829" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J829" s="9"/>
     </row>
-    <row r="830" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="830" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J830" s="9"/>
     </row>
-    <row r="831" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="831" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J831" s="9"/>
     </row>
-    <row r="832" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="832" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J832" s="9"/>
     </row>
-    <row r="833" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="833" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J833" s="9"/>
     </row>
-    <row r="834" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="834" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J834" s="9"/>
     </row>
-    <row r="835" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="835" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J835" s="9"/>
     </row>
-    <row r="836" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="836" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J836" s="9"/>
     </row>
-    <row r="837" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="837" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J837" s="9"/>
     </row>
-    <row r="838" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="838" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J838" s="9"/>
     </row>
-    <row r="839" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="839" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J839" s="9"/>
     </row>
-    <row r="840" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="840" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J840" s="9"/>
     </row>
-    <row r="841" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="841" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J841" s="9"/>
     </row>
-    <row r="842" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="842" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J842" s="9"/>
     </row>
-    <row r="843" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="843" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J843" s="9"/>
     </row>
-    <row r="844" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="844" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J844" s="9"/>
     </row>
-    <row r="845" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="845" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J845" s="9"/>
     </row>
-    <row r="846" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="846" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J846" s="9"/>
     </row>
-    <row r="847" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="847" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J847" s="9"/>
     </row>
-    <row r="848" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="848" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J848" s="9"/>
     </row>
-    <row r="849" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="849" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J849" s="9"/>
     </row>
-    <row r="850" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="850" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J850" s="9"/>
     </row>
-    <row r="851" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="851" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J851" s="9"/>
     </row>
-    <row r="852" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="852" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J852" s="9"/>
     </row>
-    <row r="853" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="853" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J853" s="9"/>
     </row>
-    <row r="854" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="854" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J854" s="9"/>
     </row>
-    <row r="855" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="855" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J855" s="9"/>
     </row>
-    <row r="856" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="856" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J856" s="9"/>
     </row>
-    <row r="857" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="857" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J857" s="9"/>
     </row>
-    <row r="858" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="858" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J858" s="9"/>
     </row>
-    <row r="859" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="859" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J859" s="9"/>
     </row>
-    <row r="860" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="860" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J860" s="9"/>
     </row>
-    <row r="861" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="861" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J861" s="9"/>
     </row>
-    <row r="862" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="862" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J862" s="9"/>
     </row>
-    <row r="863" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="863" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J863" s="9"/>
     </row>
-    <row r="864" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="864" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J864" s="9"/>
     </row>
-    <row r="865" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="865" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J865" s="9"/>
     </row>
-    <row r="866" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="866" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J866" s="9"/>
     </row>
-    <row r="867" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="867" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J867" s="9"/>
     </row>
-    <row r="868" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="868" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J868" s="9"/>
     </row>
-    <row r="869" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="869" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J869" s="9"/>
     </row>
-    <row r="870" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="870" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J870" s="9"/>
     </row>
-    <row r="871" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="871" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J871" s="9"/>
     </row>
-    <row r="872" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="872" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J872" s="9"/>
     </row>
-    <row r="873" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="873" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J873" s="9"/>
     </row>
-    <row r="874" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="874" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J874" s="9"/>
     </row>
-    <row r="875" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="875" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J875" s="9"/>
     </row>
-    <row r="876" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="876" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J876" s="9"/>
     </row>
-    <row r="877" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="877" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J877" s="9"/>
     </row>
-    <row r="878" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="878" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J878" s="9"/>
     </row>
-    <row r="879" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="879" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J879" s="9"/>
     </row>
-    <row r="880" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="880" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J880" s="9"/>
     </row>
-    <row r="881" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="881" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J881" s="9"/>
     </row>
-    <row r="882" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="882" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J882" s="9"/>
     </row>
-    <row r="883" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="883" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J883" s="9"/>
     </row>
-    <row r="884" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="884" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J884" s="9"/>
     </row>
-    <row r="885" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="885" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J885" s="9"/>
     </row>
-    <row r="886" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="886" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J886" s="9"/>
     </row>
-    <row r="887" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="887" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J887" s="9"/>
     </row>
-    <row r="888" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="888" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J888" s="9"/>
     </row>
-    <row r="889" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="889" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J889" s="9"/>
     </row>
-    <row r="890" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="890" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J890" s="9"/>
     </row>
-    <row r="891" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="891" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J891" s="9"/>
     </row>
-    <row r="892" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="892" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J892" s="9"/>
     </row>
-    <row r="893" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="893" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J893" s="9"/>
     </row>
-    <row r="894" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="894" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J894" s="9"/>
     </row>
-    <row r="895" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="895" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J895" s="9"/>
     </row>
-    <row r="896" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="896" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J896" s="9"/>
     </row>
-    <row r="897" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="897" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J897" s="9"/>
     </row>
-    <row r="898" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="898" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J898" s="9"/>
     </row>
-    <row r="899" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="899" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J899" s="9"/>
     </row>
-    <row r="900" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="900" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J900" s="9"/>
     </row>
-    <row r="901" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="901" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J901" s="9"/>
     </row>
-    <row r="902" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="902" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J902" s="9"/>
     </row>
-    <row r="903" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="903" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J903" s="9"/>
     </row>
-    <row r="904" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="904" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J904" s="9"/>
     </row>
-    <row r="905" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="905" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J905" s="9"/>
     </row>
-    <row r="906" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="906" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J906" s="9"/>
     </row>
-    <row r="907" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="907" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J907" s="9"/>
     </row>
-    <row r="908" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="908" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J908" s="9"/>
     </row>
-    <row r="909" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="909" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J909" s="9"/>
     </row>
-    <row r="910" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="910" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J910" s="9"/>
     </row>
-    <row r="911" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="911" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J911" s="9"/>
     </row>
-    <row r="912" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="912" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J912" s="9"/>
     </row>
-    <row r="913" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="913" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J913" s="9"/>
     </row>
-    <row r="914" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="914" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J914" s="9"/>
     </row>
-    <row r="915" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="915" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J915" s="9"/>
     </row>
-    <row r="916" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="916" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J916" s="9"/>
     </row>
-    <row r="917" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="917" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J917" s="9"/>
     </row>
-    <row r="918" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="918" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J918" s="9"/>
     </row>
-    <row r="919" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="919" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J919" s="9"/>
     </row>
-    <row r="920" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="920" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J920" s="9"/>
     </row>
-    <row r="921" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="921" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J921" s="9"/>
     </row>
-    <row r="922" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="922" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J922" s="9"/>
     </row>
-    <row r="923" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="923" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J923" s="9"/>
     </row>
-    <row r="924" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="924" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J924" s="9"/>
     </row>
-    <row r="925" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="925" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J925" s="9"/>
     </row>
-    <row r="926" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="926" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J926" s="9"/>
     </row>
-    <row r="927" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="927" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J927" s="9"/>
     </row>
-    <row r="928" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="928" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J928" s="9"/>
     </row>
-    <row r="929" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="929" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J929" s="9"/>
     </row>
-    <row r="930" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="930" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J930" s="9"/>
     </row>
-    <row r="931" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="931" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J931" s="9"/>
     </row>
-    <row r="932" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="932" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J932" s="9"/>
     </row>
-    <row r="933" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="933" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J933" s="9"/>
     </row>
-    <row r="934" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="934" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J934" s="9"/>
     </row>
-    <row r="935" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="935" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J935" s="9"/>
     </row>
-    <row r="936" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="936" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J936" s="9"/>
     </row>
-    <row r="937" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="937" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J937" s="9"/>
     </row>
-    <row r="938" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="938" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J938" s="9"/>
     </row>
-    <row r="939" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="939" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J939" s="9"/>
     </row>
-    <row r="940" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="940" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J940" s="9"/>
     </row>
-    <row r="941" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="941" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J941" s="9"/>
     </row>
-    <row r="942" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="942" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J942" s="9"/>
     </row>
-    <row r="943" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="943" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J943" s="9"/>
     </row>
-    <row r="944" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="944" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J944" s="9"/>
     </row>
-    <row r="945" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="945" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J945" s="9"/>
     </row>
-    <row r="946" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="946" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J946" s="9"/>
     </row>
-    <row r="947" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="947" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J947" s="9"/>
     </row>
-    <row r="948" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="948" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J948" s="9"/>
     </row>
-    <row r="949" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="949" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J949" s="9"/>
     </row>
-    <row r="950" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="950" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J950" s="9"/>
     </row>
-    <row r="951" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="951" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J951" s="9"/>
     </row>
-    <row r="952" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="952" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J952" s="9"/>
     </row>
-    <row r="953" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="953" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J953" s="9"/>
     </row>
-    <row r="954" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="954" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J954" s="9"/>
     </row>
-    <row r="955" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="955" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J955" s="9"/>
     </row>
-    <row r="956" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="956" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J956" s="9"/>
     </row>
-    <row r="957" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="957" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J957" s="9"/>
     </row>
-    <row r="958" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="958" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J958" s="9"/>
     </row>
-    <row r="959" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="959" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J959" s="9"/>
     </row>
-    <row r="960" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="960" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J960" s="9"/>
     </row>
-    <row r="961" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="961" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J961" s="9"/>
     </row>
-    <row r="962" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="962" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J962" s="9"/>
     </row>
-    <row r="963" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="963" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J963" s="9"/>
     </row>
-    <row r="964" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="964" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J964" s="9"/>
     </row>
-    <row r="965" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="965" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J965" s="9"/>
     </row>
-    <row r="966" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="966" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J966" s="9"/>
     </row>
-    <row r="967" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="967" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J967" s="9"/>
     </row>
-    <row r="968" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="968" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J968" s="9"/>
     </row>
-    <row r="969" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="969" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J969" s="9"/>
     </row>
-    <row r="970" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="970" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J970" s="9"/>
     </row>
-    <row r="971" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="971" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J971" s="9"/>
     </row>
-    <row r="972" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="972" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J972" s="9"/>
     </row>
-    <row r="973" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="973" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J973" s="9"/>
     </row>
-    <row r="974" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="974" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J974" s="9"/>
     </row>
-    <row r="975" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="975" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J975" s="9"/>
     </row>
-    <row r="976" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="976" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J976" s="9"/>
     </row>
-    <row r="977" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="977" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J977" s="9"/>
     </row>
-    <row r="978" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="978" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J978" s="9"/>
     </row>
-    <row r="979" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="979" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J979" s="9"/>
     </row>
-    <row r="980" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="980" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J980" s="9"/>
     </row>
-    <row r="981" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="981" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J981" s="9"/>
     </row>
-    <row r="982" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="982" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J982" s="9"/>
     </row>
-    <row r="983" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="983" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J983" s="9"/>
     </row>
-    <row r="984" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="984" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J984" s="9"/>
     </row>
-    <row r="985" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="985" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J985" s="9"/>
     </row>
-    <row r="986" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="986" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J986" s="9"/>
     </row>
-    <row r="987" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="987" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J987" s="9"/>
     </row>
-    <row r="988" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="988" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J988" s="9"/>
     </row>
-    <row r="989" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="989" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J989" s="9"/>
     </row>
-    <row r="990" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="990" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J990" s="9"/>
     </row>
-    <row r="991" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="991" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J991" s="9"/>
     </row>
-    <row r="992" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="992" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J992" s="9"/>
     </row>
-    <row r="993" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="993" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J993" s="9"/>
     </row>
-    <row r="994" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="994" spans="10:10" ht="13" x14ac:dyDescent="0.15">
       <c r="J994" s="9"/>
     </row>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{D9CDEFDA-B742-4707-B803-BE75C138FC2A}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="P1:P994" xr:uid="{7832FB9B-810C-4563-9B98-889A2154967C}"/>
+      <autoFilter ref="P1:P994" xr:uid="{19CEDF4C-346D-2C4B-B662-BD273CC2A6CD}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6796,21 +6793,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903B5A93-8202-4044-A142-B3A85507BA31}">
   <dimension ref="A1:B115"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="21.140625" customWidth="1"/>
-    <col min="2" max="2" width="29.85546875" customWidth="1"/>
+    <col min="1" max="1" width="21.1640625" customWidth="1"/>
+    <col min="2" max="2" width="29.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -6818,7 +6815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -6826,7 +6823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -6834,23 +6831,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>4</v>
       </c>
       <c r="B6" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -6858,7 +6855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -6866,15 +6863,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -6882,7 +6879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -6890,7 +6887,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -6898,15 +6895,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -6914,7 +6911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -6922,23 +6919,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>14</v>
       </c>
       <c r="B16" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>15</v>
       </c>
       <c r="B17" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -6946,7 +6943,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -6954,15 +6951,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>18</v>
       </c>
       <c r="B20" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -6970,15 +6967,15 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20</v>
       </c>
       <c r="B22" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -6986,39 +6983,39 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>22</v>
       </c>
       <c r="B24" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>23</v>
       </c>
       <c r="B25" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>24</v>
       </c>
       <c r="B26" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>25</v>
       </c>
       <c r="B27" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -7026,7 +7023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -7034,23 +7031,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>28</v>
       </c>
       <c r="B30" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>29</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -7058,7 +7055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -7066,23 +7063,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>32</v>
       </c>
       <c r="B34" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>33</v>
       </c>
       <c r="B35" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -7090,7 +7087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -7098,7 +7095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -7106,15 +7103,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>37</v>
       </c>
       <c r="B39" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -7122,15 +7119,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>39</v>
       </c>
       <c r="B41" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -7138,23 +7135,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>41</v>
       </c>
       <c r="B43" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>42</v>
       </c>
       <c r="B44" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -7162,7 +7159,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -7170,7 +7167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -7178,7 +7175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -7186,7 +7183,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -7194,7 +7191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -7202,7 +7199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -7210,15 +7207,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>50</v>
       </c>
       <c r="B52" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -7226,7 +7223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -7234,15 +7231,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>53</v>
       </c>
       <c r="B55" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -7250,7 +7247,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -7258,15 +7255,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>56</v>
       </c>
       <c r="B58" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -7274,7 +7271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -7282,7 +7279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -7290,23 +7287,23 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>60</v>
       </c>
       <c r="B62" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>61</v>
       </c>
       <c r="B63" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -7314,7 +7311,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -7322,7 +7319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -7330,7 +7327,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -7338,7 +7335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -7346,7 +7343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -7354,15 +7351,15 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>68</v>
       </c>
       <c r="B70" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>69</v>
       </c>
@@ -7370,15 +7367,15 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>70</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -7386,31 +7383,31 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>72</v>
       </c>
       <c r="B74" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>73</v>
       </c>
       <c r="B75" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>74</v>
       </c>
       <c r="B76" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -7418,7 +7415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -7426,23 +7423,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>77</v>
       </c>
       <c r="B79" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>78</v>
       </c>
       <c r="B80" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>79</v>
       </c>
@@ -7450,23 +7447,23 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>80</v>
       </c>
       <c r="B82" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>81</v>
       </c>
       <c r="B83" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>82</v>
       </c>
@@ -7474,7 +7471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>83</v>
       </c>
@@ -7482,23 +7479,23 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>84</v>
       </c>
       <c r="B86" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>85</v>
       </c>
       <c r="B87" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>86</v>
       </c>
@@ -7506,7 +7503,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>87</v>
       </c>
@@ -7514,7 +7511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>88</v>
       </c>
@@ -7522,15 +7519,15 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>89</v>
       </c>
       <c r="B91" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>90</v>
       </c>
@@ -7538,39 +7535,39 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>91</v>
       </c>
       <c r="B93" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>92</v>
       </c>
       <c r="B94" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>93</v>
       </c>
       <c r="B95" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>94</v>
       </c>
       <c r="B96" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>95</v>
       </c>
@@ -7578,15 +7575,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>96</v>
       </c>
       <c r="B98" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>97</v>
       </c>
@@ -7594,7 +7591,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>98</v>
       </c>
@@ -7602,7 +7599,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>99</v>
       </c>
@@ -7610,7 +7607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>100</v>
       </c>
@@ -7618,47 +7615,47 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>101</v>
       </c>
       <c r="B103" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>102</v>
       </c>
       <c r="B104" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>103</v>
       </c>
       <c r="B105" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>104</v>
       </c>
       <c r="B106" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>105</v>
       </c>
       <c r="B107" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>106</v>
       </c>
@@ -7666,23 +7663,23 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>107</v>
       </c>
       <c r="B109" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>108</v>
       </c>
       <c r="B110" s="36" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>109</v>
       </c>
@@ -7690,7 +7687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>110</v>
       </c>
@@ -7698,7 +7695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>111</v>
       </c>
@@ -7706,7 +7703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>112</v>
       </c>
@@ -7714,7 +7711,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>113</v>
       </c>
@@ -7730,409 +7727,409 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8700276F-7844-46F1-85C5-DD805B6A2273}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
       <c r="A1" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B1" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A2" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A4" s="18" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A6" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" s="18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A8" s="23" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" s="18" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A10" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
-        <v>65</v>
-      </c>
       <c r="B10" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A11" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A12" s="26" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A13" s="26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A14" s="26" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A15" s="18" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B15" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A16" s="18" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A17" s="18" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B17" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A18" s="18" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A19" s="26" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B19" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A20" s="26" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B20" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A21" s="26" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A22" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="B22" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A23" s="26" t="s">
         <v>101</v>
-      </c>
-      <c r="B22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A23" s="26" t="s">
-        <v>102</v>
       </c>
       <c r="B23" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A24" s="26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B24" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A25" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A26" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B25" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A26" s="18" t="s">
-        <v>108</v>
-      </c>
       <c r="B26" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A27" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A28" s="18" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A29" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A30" s="26" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" ht="14" x14ac:dyDescent="0.15">
       <c r="A31" s="26" t="s">
+        <v>115</v>
+      </c>
+      <c r="B31" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A32" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="B31" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A32" s="30" t="s">
+      <c r="B32" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+      <c r="A33" s="31" t="s">
         <v>117</v>
       </c>
-      <c r="B32" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A33" s="31" t="s">
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="B33" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="32" t="s">
-        <v>119</v>
-      </c>
       <c r="B34" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" s="32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="B36" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37" s="33" t="s">
-        <v>124</v>
-      </c>
       <c r="B37" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" s="32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="B39" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="33" t="s">
+      <c r="B40" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="B40" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41" s="32" t="s">
+      <c r="B41" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="B41" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A42" s="32" t="s">
+      <c r="B42" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="B42" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A43" s="34" t="s">
-        <v>132</v>
-      </c>
       <c r="B43" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="34" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.15">
       <c r="A45" s="35" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="34" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="34" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A48" s="34" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A50" s="34" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/data/Annotation tracker.xlsx
+++ b/data/Annotation tracker.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10312"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25601"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/harom/Library/CloudStorage/Box-Box/Lawrenson Lab/Endometriosis/Rstudio_analysis/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HaroM\Box\Lawrenson Lab\Endometriosis\Rstudio_analysis\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D751777E-F0C1-E849-BE9B-2A1989EC6668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C28081B6-36E9-4CFA-80AF-CC240C536857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9460" yWindow="1960" windowWidth="28080" windowHeight="13800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14235" yWindow="3975" windowWidth="27990" windowHeight="13590" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Clusters" sheetId="1" r:id="rId1"/>
@@ -1007,15 +1007,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:J115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.5" customWidth="1"/>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="26.1640625" customWidth="1"/>
-    <col min="4" max="5" width="23.5" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" customWidth="1"/>
+    <col min="4" max="5" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1026,7 +1026,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -1058,7 +1058,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1066,7 +1066,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1074,7 +1074,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1082,7 +1082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="J9" s="4"/>
     </row>
-    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="J10" s="4"/>
     </row>
-    <row r="11" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1109,7 +1109,7 @@
       </c>
       <c r="J11" s="5"/>
     </row>
-    <row r="12" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="J12" s="5"/>
     </row>
-    <row r="13" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="J13" s="5"/>
     </row>
-    <row r="14" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1137,7 +1137,7 @@
       <c r="H14" s="6"/>
       <c r="J14" s="5"/>
     </row>
-    <row r="15" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1145,7 +1145,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1161,7 +1161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1180,7 +1180,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1188,7 +1188,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1205,7 +1205,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1213,7 +1213,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="C26" s="7"/>
     </row>
-    <row r="27" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -1249,7 +1249,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -1260,7 +1260,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -1271,7 +1271,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -1279,7 +1279,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -1287,7 +1287,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -1303,7 +1303,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -1311,7 +1311,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -1327,7 +1327,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -1343,7 +1343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -1359,7 +1359,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -1367,7 +1367,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -1383,7 +1383,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -1421,7 +1421,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -1437,7 +1437,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -1445,7 +1445,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -1453,7 +1453,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -1461,7 +1461,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -1477,7 +1477,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -1488,7 +1488,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -1496,7 +1496,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -1507,7 +1507,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -1523,7 +1523,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -1531,7 +1531,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>60</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>61</v>
       </c>
@@ -1558,7 +1558,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -1569,7 +1569,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -1577,7 +1577,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -1588,7 +1588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -1599,7 +1599,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>68</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>69</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>70</v>
       </c>
@@ -1639,7 +1639,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>72</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>73</v>
       </c>
@@ -1663,7 +1663,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>74</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>77</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>78</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>79</v>
       </c>
@@ -1717,7 +1717,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>80</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>81</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>82</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>83</v>
       </c>
@@ -1749,7 +1749,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>84</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>85</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>86</v>
       </c>
@@ -1773,7 +1773,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>87</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>88</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>89</v>
       </c>
@@ -1800,7 +1800,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>90</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>91</v>
       </c>
@@ -1816,7 +1816,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>92</v>
       </c>
@@ -1824,7 +1824,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>93</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>94</v>
       </c>
@@ -1840,7 +1840,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>95</v>
       </c>
@@ -1848,7 +1848,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>96</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>97</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>98</v>
       </c>
@@ -1872,7 +1872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>99</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>100</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>101</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>102</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>103</v>
       </c>
@@ -1918,7 +1918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>104</v>
       </c>
@@ -1926,7 +1926,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>105</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>106</v>
       </c>
@@ -1942,7 +1942,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>107</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>108</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>109</v>
       </c>
@@ -1966,7 +1966,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>110</v>
       </c>
@@ -1974,7 +1974,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>111</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>112</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>113</v>
       </c>
@@ -2009,9 +2009,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:E22"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>15</v>
       </c>
@@ -2028,7 +2028,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>1</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -2062,7 +2062,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -2079,7 +2079,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>4</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>5</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>6</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>7</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -2181,7 +2181,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -2215,7 +2215,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -2232,7 +2232,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -2249,7 +2249,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -2283,7 +2283,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -2300,7 +2300,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -2317,7 +2317,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -2334,7 +2334,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2351,7 +2351,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>20</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>21</v>
       </c>
@@ -2396,16 +2396,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:P994"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="12.42578125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="3" max="5" width="24.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.5" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
-    <col min="10" max="10" width="26.1640625" customWidth="1"/>
+    <col min="3" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="10" max="10" width="26.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>28</v>
       </c>
@@ -2437,7 +2437,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
         <v>23</v>
       </c>
@@ -2469,7 +2469,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="16" t="s">
         <v>23</v>
       </c>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>23</v>
       </c>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="11" t="s">
         <v>23</v>
       </c>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="P5" s="9"/>
     </row>
-    <row r="6" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="16" t="s">
         <v>22</v>
       </c>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="P6" s="9"/>
     </row>
-    <row r="7" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
         <v>22</v>
       </c>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="P7" s="9"/>
     </row>
-    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="11" t="s">
         <v>20</v>
       </c>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="P8" s="9"/>
     </row>
-    <row r="9" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="16" t="s">
         <v>23</v>
       </c>
@@ -2698,7 +2698,7 @@
       </c>
       <c r="P9" s="9"/>
     </row>
-    <row r="10" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>23</v>
       </c>
@@ -2727,7 +2727,7 @@
       </c>
       <c r="P10" s="9"/>
     </row>
-    <row r="11" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="24" t="s">
         <v>67</v>
       </c>
@@ -2760,7 +2760,7 @@
       </c>
       <c r="P11" s="9"/>
     </row>
-    <row r="12" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
         <v>20</v>
       </c>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="P12" s="9"/>
     </row>
-    <row r="13" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
         <v>23</v>
       </c>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="P13" s="9"/>
     </row>
-    <row r="14" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="27" t="s">
         <v>20</v>
       </c>
@@ -2859,7 +2859,7 @@
       </c>
       <c r="P14" s="9"/>
     </row>
-    <row r="15" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="16" t="s">
         <v>22</v>
       </c>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="P15" s="9"/>
     </row>
-    <row r="16" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="16" t="s">
         <v>23</v>
       </c>
@@ -2925,7 +2925,7 @@
       </c>
       <c r="P16" s="9"/>
     </row>
-    <row r="17" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="16" t="s">
         <v>22</v>
       </c>
@@ -2958,7 +2958,7 @@
       </c>
       <c r="P17" s="9"/>
     </row>
-    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="20" t="s">
         <v>22</v>
       </c>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="P18" s="9"/>
     </row>
-    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>22</v>
       </c>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="P19" s="9"/>
     </row>
-    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="24" t="s">
         <v>22</v>
       </c>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="P20" s="9"/>
     </row>
-    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="24" t="s">
         <v>22</v>
       </c>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="P21" s="9"/>
     </row>
-    <row r="22" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="24" t="s">
         <v>23</v>
       </c>
@@ -3119,7 +3119,7 @@
       </c>
       <c r="P22" s="9"/>
     </row>
-    <row r="23" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
         <v>22</v>
       </c>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="P23" s="9"/>
     </row>
-    <row r="24" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="27" t="s">
         <v>22</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="16" t="s">
         <v>23</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="16" t="s">
         <v>22</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="16" t="s">
         <v>22</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="20" t="s">
         <v>20</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="24" t="s">
         <v>20</v>
       </c>
@@ -3317,7 +3317,7 @@
       </c>
       <c r="P29" s="9"/>
     </row>
-    <row r="30" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="24" t="s">
         <v>23</v>
       </c>
@@ -3350,7 +3350,7 @@
       </c>
       <c r="P30" s="9"/>
     </row>
-    <row r="31" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="27" t="s">
         <v>23</v>
       </c>
@@ -3379,7 +3379,7 @@
       </c>
       <c r="P31" s="9"/>
     </row>
-    <row r="32" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="20" t="s">
         <v>23</v>
       </c>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="P32" s="9"/>
     </row>
-    <row r="33" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="27" t="s">
         <v>23</v>
       </c>
@@ -3437,7 +3437,7 @@
       </c>
       <c r="P33" s="9"/>
     </row>
-    <row r="34" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="16" t="s">
         <v>22</v>
       </c>
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="16" t="s">
         <v>23</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="20" t="s">
         <v>23</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="27" t="s">
         <v>23</v>
       </c>
@@ -3549,7 +3549,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="16" t="s">
         <v>20</v>
       </c>
@@ -3581,7 +3581,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="20" t="s">
         <v>23</v>
       </c>
@@ -3609,7 +3609,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="27" t="s">
         <v>23</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="16" t="s">
         <v>23</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="20" t="s">
         <v>23</v>
       </c>
@@ -3694,7 +3694,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="24" t="s">
         <v>23</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="27" t="s">
         <v>20</v>
       </c>
@@ -3755,7 +3755,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="20" t="s">
         <v>20</v>
       </c>
@@ -3787,7 +3787,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="24" t="s">
         <v>22</v>
       </c>
@@ -3819,7 +3819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="24" t="s">
         <v>20</v>
       </c>
@@ -3851,7 +3851,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:16" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="24" t="s">
         <v>20</v>
       </c>
@@ -3883,7 +3883,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="24" t="s">
         <v>22</v>
       </c>
@@ -3915,7 +3915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="27" t="s">
         <v>22</v>
       </c>
@@ -3947,2843 +3947,2843 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J51" s="9"/>
     </row>
-    <row r="52" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J52" s="9"/>
     </row>
-    <row r="53" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J53" s="9"/>
     </row>
-    <row r="54" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J54" s="9"/>
     </row>
-    <row r="55" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J55" s="9"/>
     </row>
-    <row r="56" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J56" s="9"/>
     </row>
-    <row r="57" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J57" s="9"/>
     </row>
-    <row r="58" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J58" s="9"/>
     </row>
-    <row r="59" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J59" s="9"/>
     </row>
-    <row r="60" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J60" s="9"/>
     </row>
-    <row r="61" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J61" s="9"/>
     </row>
-    <row r="62" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J62" s="9"/>
     </row>
-    <row r="63" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J63" s="9"/>
     </row>
-    <row r="64" spans="1:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J64" s="9"/>
     </row>
-    <row r="65" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="65" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J65" s="9"/>
     </row>
-    <row r="66" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="66" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J66" s="9"/>
     </row>
-    <row r="67" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="67" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J67" s="9"/>
     </row>
-    <row r="68" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="68" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J68" s="9"/>
     </row>
-    <row r="69" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="69" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J69" s="9"/>
     </row>
-    <row r="70" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="70" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J70" s="9"/>
     </row>
-    <row r="71" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="71" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J71" s="9"/>
     </row>
-    <row r="72" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="72" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J72" s="9"/>
     </row>
-    <row r="73" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="73" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J73" s="9"/>
     </row>
-    <row r="74" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="74" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J74" s="9"/>
     </row>
-    <row r="75" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="75" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J75" s="9"/>
     </row>
-    <row r="76" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="76" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J76" s="9"/>
     </row>
-    <row r="77" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="77" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J77" s="9"/>
     </row>
-    <row r="78" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="78" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J78" s="9"/>
     </row>
-    <row r="79" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="79" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J79" s="9"/>
     </row>
-    <row r="80" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="80" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J80" s="9"/>
     </row>
-    <row r="81" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="81" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J81" s="9"/>
     </row>
-    <row r="82" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="82" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J82" s="9"/>
     </row>
-    <row r="83" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="83" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J83" s="9"/>
     </row>
-    <row r="84" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="84" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J84" s="9"/>
     </row>
-    <row r="85" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="85" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J85" s="9"/>
     </row>
-    <row r="86" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="86" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J86" s="9"/>
     </row>
-    <row r="87" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="87" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J87" s="9"/>
     </row>
-    <row r="88" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="88" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J88" s="9"/>
     </row>
-    <row r="89" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="89" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J89" s="9"/>
     </row>
-    <row r="90" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="90" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J90" s="9"/>
     </row>
-    <row r="91" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="91" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J91" s="9"/>
     </row>
-    <row r="92" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="92" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J92" s="9"/>
     </row>
-    <row r="93" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="93" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J93" s="9"/>
     </row>
-    <row r="94" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="94" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J94" s="9"/>
     </row>
-    <row r="95" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="95" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J95" s="9"/>
     </row>
-    <row r="96" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="96" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J96" s="9"/>
     </row>
-    <row r="97" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="97" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J97" s="9"/>
     </row>
-    <row r="98" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="98" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J98" s="9"/>
     </row>
-    <row r="99" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="99" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J99" s="9"/>
     </row>
-    <row r="100" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="100" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J100" s="9"/>
     </row>
-    <row r="101" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="101" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J101" s="9"/>
     </row>
-    <row r="102" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="102" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J102" s="9"/>
     </row>
-    <row r="103" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="103" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J103" s="9"/>
     </row>
-    <row r="104" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="104" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J104" s="9"/>
     </row>
-    <row r="105" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="105" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J105" s="9"/>
     </row>
-    <row r="106" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="106" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J106" s="9"/>
     </row>
-    <row r="107" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="107" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J107" s="9"/>
     </row>
-    <row r="108" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="108" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J108" s="9"/>
     </row>
-    <row r="109" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="109" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J109" s="9"/>
     </row>
-    <row r="110" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="110" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J110" s="9"/>
     </row>
-    <row r="111" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="111" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J111" s="9"/>
     </row>
-    <row r="112" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="112" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J112" s="9"/>
     </row>
-    <row r="113" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="113" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J113" s="9"/>
     </row>
-    <row r="114" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="114" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J114" s="9"/>
     </row>
-    <row r="115" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="115" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J115" s="9"/>
     </row>
-    <row r="116" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="116" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J116" s="9"/>
     </row>
-    <row r="117" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="117" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J117" s="9"/>
     </row>
-    <row r="118" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="118" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J118" s="9"/>
     </row>
-    <row r="119" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="119" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J119" s="9"/>
     </row>
-    <row r="120" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="120" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J120" s="9"/>
     </row>
-    <row r="121" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="121" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J121" s="9"/>
     </row>
-    <row r="122" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="122" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J122" s="9"/>
     </row>
-    <row r="123" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="123" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J123" s="9"/>
     </row>
-    <row r="124" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="124" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J124" s="9"/>
     </row>
-    <row r="125" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="125" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J125" s="9"/>
     </row>
-    <row r="126" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="126" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J126" s="9"/>
     </row>
-    <row r="127" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="127" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J127" s="9"/>
     </row>
-    <row r="128" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="128" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J128" s="9"/>
     </row>
-    <row r="129" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="129" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J129" s="9"/>
     </row>
-    <row r="130" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="130" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J130" s="9"/>
     </row>
-    <row r="131" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="131" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J131" s="9"/>
     </row>
-    <row r="132" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="132" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J132" s="9"/>
     </row>
-    <row r="133" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="133" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J133" s="9"/>
     </row>
-    <row r="134" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="134" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J134" s="9"/>
     </row>
-    <row r="135" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="135" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J135" s="9"/>
     </row>
-    <row r="136" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="136" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J136" s="9"/>
     </row>
-    <row r="137" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="137" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J137" s="9"/>
     </row>
-    <row r="138" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="138" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J138" s="9"/>
     </row>
-    <row r="139" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="139" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J139" s="9"/>
     </row>
-    <row r="140" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="140" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J140" s="9"/>
     </row>
-    <row r="141" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="141" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J141" s="9"/>
     </row>
-    <row r="142" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="142" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J142" s="9"/>
     </row>
-    <row r="143" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="143" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J143" s="9"/>
     </row>
-    <row r="144" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="144" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J144" s="9"/>
     </row>
-    <row r="145" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="145" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J145" s="9"/>
     </row>
-    <row r="146" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="146" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J146" s="9"/>
     </row>
-    <row r="147" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="147" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J147" s="9"/>
     </row>
-    <row r="148" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="148" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J148" s="9"/>
     </row>
-    <row r="149" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="149" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J149" s="9"/>
     </row>
-    <row r="150" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="150" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J150" s="9"/>
     </row>
-    <row r="151" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="151" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J151" s="9"/>
     </row>
-    <row r="152" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="152" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J152" s="9"/>
     </row>
-    <row r="153" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="153" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J153" s="9"/>
     </row>
-    <row r="154" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="154" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J154" s="9"/>
     </row>
-    <row r="155" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="155" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J155" s="9"/>
     </row>
-    <row r="156" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="156" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J156" s="9"/>
     </row>
-    <row r="157" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="157" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J157" s="9"/>
     </row>
-    <row r="158" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="158" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J158" s="9"/>
     </row>
-    <row r="159" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="159" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J159" s="9"/>
     </row>
-    <row r="160" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="160" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J160" s="9"/>
     </row>
-    <row r="161" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="161" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J161" s="9"/>
     </row>
-    <row r="162" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="162" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J162" s="9"/>
     </row>
-    <row r="163" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="163" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J163" s="9"/>
     </row>
-    <row r="164" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="164" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J164" s="9"/>
     </row>
-    <row r="165" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="165" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J165" s="9"/>
     </row>
-    <row r="166" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="166" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J166" s="9"/>
     </row>
-    <row r="167" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="167" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J167" s="9"/>
     </row>
-    <row r="168" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="168" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J168" s="9"/>
     </row>
-    <row r="169" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="169" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J169" s="9"/>
     </row>
-    <row r="170" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="170" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J170" s="9"/>
     </row>
-    <row r="171" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="171" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J171" s="9"/>
     </row>
-    <row r="172" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="172" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J172" s="9"/>
     </row>
-    <row r="173" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="173" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J173" s="9"/>
     </row>
-    <row r="174" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="174" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J174" s="9"/>
     </row>
-    <row r="175" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="175" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J175" s="9"/>
     </row>
-    <row r="176" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="176" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J176" s="9"/>
     </row>
-    <row r="177" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="177" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J177" s="9"/>
     </row>
-    <row r="178" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="178" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J178" s="9"/>
     </row>
-    <row r="179" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="179" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J179" s="9"/>
     </row>
-    <row r="180" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="180" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J180" s="9"/>
     </row>
-    <row r="181" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="181" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J181" s="9"/>
     </row>
-    <row r="182" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="182" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J182" s="9"/>
     </row>
-    <row r="183" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="183" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J183" s="9"/>
     </row>
-    <row r="184" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="184" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J184" s="9"/>
     </row>
-    <row r="185" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="185" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J185" s="9"/>
     </row>
-    <row r="186" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="186" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J186" s="9"/>
     </row>
-    <row r="187" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="187" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J187" s="9"/>
     </row>
-    <row r="188" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="188" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J188" s="9"/>
     </row>
-    <row r="189" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="189" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J189" s="9"/>
     </row>
-    <row r="190" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="190" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J190" s="9"/>
     </row>
-    <row r="191" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="191" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J191" s="9"/>
     </row>
-    <row r="192" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="192" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J192" s="9"/>
     </row>
-    <row r="193" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="193" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J193" s="9"/>
     </row>
-    <row r="194" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="194" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J194" s="9"/>
     </row>
-    <row r="195" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="195" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J195" s="9"/>
     </row>
-    <row r="196" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="196" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J196" s="9"/>
     </row>
-    <row r="197" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="197" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J197" s="9"/>
     </row>
-    <row r="198" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="198" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J198" s="9"/>
     </row>
-    <row r="199" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="199" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J199" s="9"/>
     </row>
-    <row r="200" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="200" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J200" s="9"/>
     </row>
-    <row r="201" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="201" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J201" s="9"/>
     </row>
-    <row r="202" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="202" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J202" s="9"/>
     </row>
-    <row r="203" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="203" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J203" s="9"/>
     </row>
-    <row r="204" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="204" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J204" s="9"/>
     </row>
-    <row r="205" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="205" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J205" s="9"/>
     </row>
-    <row r="206" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="206" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J206" s="9"/>
     </row>
-    <row r="207" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="207" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J207" s="9"/>
     </row>
-    <row r="208" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="208" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J208" s="9"/>
     </row>
-    <row r="209" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="209" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J209" s="9"/>
     </row>
-    <row r="210" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="210" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J210" s="9"/>
     </row>
-    <row r="211" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="211" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J211" s="9"/>
     </row>
-    <row r="212" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="212" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J212" s="9"/>
     </row>
-    <row r="213" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="213" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J213" s="9"/>
     </row>
-    <row r="214" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="214" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J214" s="9"/>
     </row>
-    <row r="215" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="215" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J215" s="9"/>
     </row>
-    <row r="216" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="216" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J216" s="9"/>
     </row>
-    <row r="217" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="217" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J217" s="9"/>
     </row>
-    <row r="218" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="218" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J218" s="9"/>
     </row>
-    <row r="219" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="219" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J219" s="9"/>
     </row>
-    <row r="220" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="220" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J220" s="9"/>
     </row>
-    <row r="221" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="221" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J221" s="9"/>
     </row>
-    <row r="222" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="222" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J222" s="9"/>
     </row>
-    <row r="223" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="223" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J223" s="9"/>
     </row>
-    <row r="224" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="224" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J224" s="9"/>
     </row>
-    <row r="225" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="225" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J225" s="9"/>
     </row>
-    <row r="226" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="226" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J226" s="9"/>
     </row>
-    <row r="227" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="227" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J227" s="9"/>
     </row>
-    <row r="228" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="228" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J228" s="9"/>
     </row>
-    <row r="229" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="229" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J229" s="9"/>
     </row>
-    <row r="230" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="230" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J230" s="9"/>
     </row>
-    <row r="231" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="231" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J231" s="9"/>
     </row>
-    <row r="232" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="232" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J232" s="9"/>
     </row>
-    <row r="233" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="233" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J233" s="9"/>
     </row>
-    <row r="234" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="234" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J234" s="9"/>
     </row>
-    <row r="235" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="235" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J235" s="9"/>
     </row>
-    <row r="236" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="236" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J236" s="9"/>
     </row>
-    <row r="237" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="237" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J237" s="9"/>
     </row>
-    <row r="238" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="238" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J238" s="9"/>
     </row>
-    <row r="239" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="239" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J239" s="9"/>
     </row>
-    <row r="240" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="240" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J240" s="9"/>
     </row>
-    <row r="241" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="241" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J241" s="9"/>
     </row>
-    <row r="242" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="242" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J242" s="9"/>
     </row>
-    <row r="243" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="243" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J243" s="9"/>
     </row>
-    <row r="244" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="244" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J244" s="9"/>
     </row>
-    <row r="245" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="245" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J245" s="9"/>
     </row>
-    <row r="246" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="246" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J246" s="9"/>
     </row>
-    <row r="247" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="247" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J247" s="9"/>
     </row>
-    <row r="248" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="248" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J248" s="9"/>
     </row>
-    <row r="249" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="249" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J249" s="9"/>
     </row>
-    <row r="250" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="250" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J250" s="9"/>
     </row>
-    <row r="251" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="251" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J251" s="9"/>
     </row>
-    <row r="252" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="252" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J252" s="9"/>
     </row>
-    <row r="253" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="253" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J253" s="9"/>
     </row>
-    <row r="254" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="254" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J254" s="9"/>
     </row>
-    <row r="255" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="255" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J255" s="9"/>
     </row>
-    <row r="256" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="256" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J256" s="9"/>
     </row>
-    <row r="257" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="257" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J257" s="9"/>
     </row>
-    <row r="258" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="258" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J258" s="9"/>
     </row>
-    <row r="259" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="259" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J259" s="9"/>
     </row>
-    <row r="260" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="260" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J260" s="9"/>
     </row>
-    <row r="261" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="261" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J261" s="9"/>
     </row>
-    <row r="262" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="262" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J262" s="9"/>
     </row>
-    <row r="263" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="263" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J263" s="9"/>
     </row>
-    <row r="264" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="264" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J264" s="9"/>
     </row>
-    <row r="265" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="265" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J265" s="9"/>
     </row>
-    <row r="266" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="266" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J266" s="9"/>
     </row>
-    <row r="267" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="267" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J267" s="9"/>
     </row>
-    <row r="268" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="268" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J268" s="9"/>
     </row>
-    <row r="269" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="269" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J269" s="9"/>
     </row>
-    <row r="270" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="270" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J270" s="9"/>
     </row>
-    <row r="271" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="271" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J271" s="9"/>
     </row>
-    <row r="272" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="272" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J272" s="9"/>
     </row>
-    <row r="273" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="273" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J273" s="9"/>
     </row>
-    <row r="274" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="274" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J274" s="9"/>
     </row>
-    <row r="275" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="275" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J275" s="9"/>
     </row>
-    <row r="276" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="276" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J276" s="9"/>
     </row>
-    <row r="277" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="277" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J277" s="9"/>
     </row>
-    <row r="278" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="278" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J278" s="9"/>
     </row>
-    <row r="279" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="279" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J279" s="9"/>
     </row>
-    <row r="280" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="280" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J280" s="9"/>
     </row>
-    <row r="281" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="281" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J281" s="9"/>
     </row>
-    <row r="282" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="282" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J282" s="9"/>
     </row>
-    <row r="283" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="283" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J283" s="9"/>
     </row>
-    <row r="284" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="284" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J284" s="9"/>
     </row>
-    <row r="285" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="285" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J285" s="9"/>
     </row>
-    <row r="286" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="286" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J286" s="9"/>
     </row>
-    <row r="287" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="287" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J287" s="9"/>
     </row>
-    <row r="288" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="288" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J288" s="9"/>
     </row>
-    <row r="289" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="289" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J289" s="9"/>
     </row>
-    <row r="290" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="290" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J290" s="9"/>
     </row>
-    <row r="291" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="291" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J291" s="9"/>
     </row>
-    <row r="292" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="292" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J292" s="9"/>
     </row>
-    <row r="293" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="293" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J293" s="9"/>
     </row>
-    <row r="294" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="294" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J294" s="9"/>
     </row>
-    <row r="295" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="295" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J295" s="9"/>
     </row>
-    <row r="296" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="296" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J296" s="9"/>
     </row>
-    <row r="297" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="297" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J297" s="9"/>
     </row>
-    <row r="298" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="298" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J298" s="9"/>
     </row>
-    <row r="299" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="299" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J299" s="9"/>
     </row>
-    <row r="300" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="300" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J300" s="9"/>
     </row>
-    <row r="301" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="301" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J301" s="9"/>
     </row>
-    <row r="302" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="302" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J302" s="9"/>
     </row>
-    <row r="303" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="303" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J303" s="9"/>
     </row>
-    <row r="304" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="304" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J304" s="9"/>
     </row>
-    <row r="305" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="305" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J305" s="9"/>
     </row>
-    <row r="306" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="306" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J306" s="9"/>
     </row>
-    <row r="307" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="307" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J307" s="9"/>
     </row>
-    <row r="308" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="308" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J308" s="9"/>
     </row>
-    <row r="309" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="309" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J309" s="9"/>
     </row>
-    <row r="310" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="310" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J310" s="9"/>
     </row>
-    <row r="311" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="311" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J311" s="9"/>
     </row>
-    <row r="312" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="312" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J312" s="9"/>
     </row>
-    <row r="313" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="313" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J313" s="9"/>
     </row>
-    <row r="314" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="314" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J314" s="9"/>
     </row>
-    <row r="315" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="315" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J315" s="9"/>
     </row>
-    <row r="316" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="316" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J316" s="9"/>
     </row>
-    <row r="317" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="317" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J317" s="9"/>
     </row>
-    <row r="318" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="318" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J318" s="9"/>
     </row>
-    <row r="319" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="319" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J319" s="9"/>
     </row>
-    <row r="320" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="320" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J320" s="9"/>
     </row>
-    <row r="321" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="321" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J321" s="9"/>
     </row>
-    <row r="322" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="322" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J322" s="9"/>
     </row>
-    <row r="323" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="323" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J323" s="9"/>
     </row>
-    <row r="324" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="324" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J324" s="9"/>
     </row>
-    <row r="325" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="325" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J325" s="9"/>
     </row>
-    <row r="326" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="326" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J326" s="9"/>
     </row>
-    <row r="327" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="327" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J327" s="9"/>
     </row>
-    <row r="328" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="328" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J328" s="9"/>
     </row>
-    <row r="329" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="329" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J329" s="9"/>
     </row>
-    <row r="330" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="330" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J330" s="9"/>
     </row>
-    <row r="331" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="331" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J331" s="9"/>
     </row>
-    <row r="332" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="332" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J332" s="9"/>
     </row>
-    <row r="333" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="333" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J333" s="9"/>
     </row>
-    <row r="334" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="334" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J334" s="9"/>
     </row>
-    <row r="335" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="335" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J335" s="9"/>
     </row>
-    <row r="336" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="336" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J336" s="9"/>
     </row>
-    <row r="337" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="337" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J337" s="9"/>
     </row>
-    <row r="338" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="338" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J338" s="9"/>
     </row>
-    <row r="339" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="339" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J339" s="9"/>
     </row>
-    <row r="340" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="340" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J340" s="9"/>
     </row>
-    <row r="341" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="341" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J341" s="9"/>
     </row>
-    <row r="342" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="342" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J342" s="9"/>
     </row>
-    <row r="343" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="343" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J343" s="9"/>
     </row>
-    <row r="344" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="344" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J344" s="9"/>
     </row>
-    <row r="345" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="345" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J345" s="9"/>
     </row>
-    <row r="346" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="346" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J346" s="9"/>
     </row>
-    <row r="347" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="347" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J347" s="9"/>
     </row>
-    <row r="348" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="348" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J348" s="9"/>
     </row>
-    <row r="349" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="349" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J349" s="9"/>
     </row>
-    <row r="350" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="350" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J350" s="9"/>
     </row>
-    <row r="351" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="351" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J351" s="9"/>
     </row>
-    <row r="352" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="352" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J352" s="9"/>
     </row>
-    <row r="353" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="353" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J353" s="9"/>
     </row>
-    <row r="354" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="354" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J354" s="9"/>
     </row>
-    <row r="355" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="355" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J355" s="9"/>
     </row>
-    <row r="356" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="356" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J356" s="9"/>
     </row>
-    <row r="357" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="357" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J357" s="9"/>
     </row>
-    <row r="358" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="358" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J358" s="9"/>
     </row>
-    <row r="359" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="359" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J359" s="9"/>
     </row>
-    <row r="360" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="360" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J360" s="9"/>
     </row>
-    <row r="361" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="361" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J361" s="9"/>
     </row>
-    <row r="362" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="362" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J362" s="9"/>
     </row>
-    <row r="363" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="363" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J363" s="9"/>
     </row>
-    <row r="364" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="364" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J364" s="9"/>
     </row>
-    <row r="365" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="365" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J365" s="9"/>
     </row>
-    <row r="366" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="366" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J366" s="9"/>
     </row>
-    <row r="367" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="367" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J367" s="9"/>
     </row>
-    <row r="368" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="368" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J368" s="9"/>
     </row>
-    <row r="369" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="369" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J369" s="9"/>
     </row>
-    <row r="370" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="370" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J370" s="9"/>
     </row>
-    <row r="371" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="371" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J371" s="9"/>
     </row>
-    <row r="372" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="372" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J372" s="9"/>
     </row>
-    <row r="373" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="373" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J373" s="9"/>
     </row>
-    <row r="374" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="374" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J374" s="9"/>
     </row>
-    <row r="375" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="375" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J375" s="9"/>
     </row>
-    <row r="376" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="376" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J376" s="9"/>
     </row>
-    <row r="377" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="377" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J377" s="9"/>
     </row>
-    <row r="378" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="378" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J378" s="9"/>
     </row>
-    <row r="379" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="379" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J379" s="9"/>
     </row>
-    <row r="380" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="380" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J380" s="9"/>
     </row>
-    <row r="381" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="381" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J381" s="9"/>
     </row>
-    <row r="382" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="382" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J382" s="9"/>
     </row>
-    <row r="383" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="383" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J383" s="9"/>
     </row>
-    <row r="384" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="384" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J384" s="9"/>
     </row>
-    <row r="385" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="385" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J385" s="9"/>
     </row>
-    <row r="386" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="386" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J386" s="9"/>
     </row>
-    <row r="387" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="387" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J387" s="9"/>
     </row>
-    <row r="388" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="388" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J388" s="9"/>
     </row>
-    <row r="389" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="389" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J389" s="9"/>
     </row>
-    <row r="390" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="390" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J390" s="9"/>
     </row>
-    <row r="391" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="391" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J391" s="9"/>
     </row>
-    <row r="392" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="392" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J392" s="9"/>
     </row>
-    <row r="393" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="393" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J393" s="9"/>
     </row>
-    <row r="394" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="394" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J394" s="9"/>
     </row>
-    <row r="395" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="395" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J395" s="9"/>
     </row>
-    <row r="396" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="396" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J396" s="9"/>
     </row>
-    <row r="397" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="397" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J397" s="9"/>
     </row>
-    <row r="398" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="398" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J398" s="9"/>
     </row>
-    <row r="399" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="399" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J399" s="9"/>
     </row>
-    <row r="400" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="400" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J400" s="9"/>
     </row>
-    <row r="401" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="401" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J401" s="9"/>
     </row>
-    <row r="402" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="402" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J402" s="9"/>
     </row>
-    <row r="403" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="403" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J403" s="9"/>
     </row>
-    <row r="404" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="404" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J404" s="9"/>
     </row>
-    <row r="405" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="405" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J405" s="9"/>
     </row>
-    <row r="406" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="406" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J406" s="9"/>
     </row>
-    <row r="407" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="407" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J407" s="9"/>
     </row>
-    <row r="408" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="408" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J408" s="9"/>
     </row>
-    <row r="409" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="409" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J409" s="9"/>
     </row>
-    <row r="410" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="410" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J410" s="9"/>
     </row>
-    <row r="411" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="411" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J411" s="9"/>
     </row>
-    <row r="412" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="412" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J412" s="9"/>
     </row>
-    <row r="413" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="413" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J413" s="9"/>
     </row>
-    <row r="414" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="414" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J414" s="9"/>
     </row>
-    <row r="415" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="415" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J415" s="9"/>
     </row>
-    <row r="416" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="416" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J416" s="9"/>
     </row>
-    <row r="417" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="417" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J417" s="9"/>
     </row>
-    <row r="418" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="418" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J418" s="9"/>
     </row>
-    <row r="419" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="419" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J419" s="9"/>
     </row>
-    <row r="420" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="420" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J420" s="9"/>
     </row>
-    <row r="421" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="421" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J421" s="9"/>
     </row>
-    <row r="422" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="422" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J422" s="9"/>
     </row>
-    <row r="423" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="423" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J423" s="9"/>
     </row>
-    <row r="424" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="424" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J424" s="9"/>
     </row>
-    <row r="425" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="425" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J425" s="9"/>
     </row>
-    <row r="426" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="426" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J426" s="9"/>
     </row>
-    <row r="427" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="427" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J427" s="9"/>
     </row>
-    <row r="428" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="428" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J428" s="9"/>
     </row>
-    <row r="429" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="429" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J429" s="9"/>
     </row>
-    <row r="430" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="430" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J430" s="9"/>
     </row>
-    <row r="431" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="431" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J431" s="9"/>
     </row>
-    <row r="432" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="432" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J432" s="9"/>
     </row>
-    <row r="433" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="433" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J433" s="9"/>
     </row>
-    <row r="434" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="434" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J434" s="9"/>
     </row>
-    <row r="435" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="435" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J435" s="9"/>
     </row>
-    <row r="436" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="436" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J436" s="9"/>
     </row>
-    <row r="437" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="437" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J437" s="9"/>
     </row>
-    <row r="438" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="438" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J438" s="9"/>
     </row>
-    <row r="439" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="439" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J439" s="9"/>
     </row>
-    <row r="440" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="440" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J440" s="9"/>
     </row>
-    <row r="441" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="441" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J441" s="9"/>
     </row>
-    <row r="442" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="442" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J442" s="9"/>
     </row>
-    <row r="443" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="443" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J443" s="9"/>
     </row>
-    <row r="444" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="444" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J444" s="9"/>
     </row>
-    <row r="445" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="445" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J445" s="9"/>
     </row>
-    <row r="446" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="446" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J446" s="9"/>
     </row>
-    <row r="447" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="447" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J447" s="9"/>
     </row>
-    <row r="448" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="448" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J448" s="9"/>
     </row>
-    <row r="449" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="449" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J449" s="9"/>
     </row>
-    <row r="450" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="450" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J450" s="9"/>
     </row>
-    <row r="451" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="451" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J451" s="9"/>
     </row>
-    <row r="452" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="452" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J452" s="9"/>
     </row>
-    <row r="453" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="453" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J453" s="9"/>
     </row>
-    <row r="454" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="454" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J454" s="9"/>
     </row>
-    <row r="455" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="455" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J455" s="9"/>
     </row>
-    <row r="456" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="456" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J456" s="9"/>
     </row>
-    <row r="457" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="457" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J457" s="9"/>
     </row>
-    <row r="458" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="458" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J458" s="9"/>
     </row>
-    <row r="459" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="459" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J459" s="9"/>
     </row>
-    <row r="460" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="460" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J460" s="9"/>
     </row>
-    <row r="461" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="461" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J461" s="9"/>
     </row>
-    <row r="462" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="462" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J462" s="9"/>
     </row>
-    <row r="463" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="463" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J463" s="9"/>
     </row>
-    <row r="464" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="464" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J464" s="9"/>
     </row>
-    <row r="465" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="465" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J465" s="9"/>
     </row>
-    <row r="466" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="466" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J466" s="9"/>
     </row>
-    <row r="467" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="467" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J467" s="9"/>
     </row>
-    <row r="468" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="468" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J468" s="9"/>
     </row>
-    <row r="469" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="469" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J469" s="9"/>
     </row>
-    <row r="470" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="470" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J470" s="9"/>
     </row>
-    <row r="471" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="471" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J471" s="9"/>
     </row>
-    <row r="472" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="472" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J472" s="9"/>
     </row>
-    <row r="473" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="473" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J473" s="9"/>
     </row>
-    <row r="474" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="474" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J474" s="9"/>
     </row>
-    <row r="475" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="475" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J475" s="9"/>
     </row>
-    <row r="476" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="476" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J476" s="9"/>
     </row>
-    <row r="477" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="477" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J477" s="9"/>
     </row>
-    <row r="478" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="478" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J478" s="9"/>
     </row>
-    <row r="479" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="479" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J479" s="9"/>
     </row>
-    <row r="480" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="480" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J480" s="9"/>
     </row>
-    <row r="481" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="481" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J481" s="9"/>
     </row>
-    <row r="482" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="482" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J482" s="9"/>
     </row>
-    <row r="483" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="483" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J483" s="9"/>
     </row>
-    <row r="484" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="484" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J484" s="9"/>
     </row>
-    <row r="485" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="485" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J485" s="9"/>
     </row>
-    <row r="486" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="486" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J486" s="9"/>
     </row>
-    <row r="487" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="487" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J487" s="9"/>
     </row>
-    <row r="488" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="488" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J488" s="9"/>
     </row>
-    <row r="489" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="489" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J489" s="9"/>
     </row>
-    <row r="490" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="490" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J490" s="9"/>
     </row>
-    <row r="491" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="491" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J491" s="9"/>
     </row>
-    <row r="492" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="492" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J492" s="9"/>
     </row>
-    <row r="493" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="493" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J493" s="9"/>
     </row>
-    <row r="494" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="494" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J494" s="9"/>
     </row>
-    <row r="495" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="495" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J495" s="9"/>
     </row>
-    <row r="496" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="496" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J496" s="9"/>
     </row>
-    <row r="497" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="497" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J497" s="9"/>
     </row>
-    <row r="498" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="498" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J498" s="9"/>
     </row>
-    <row r="499" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="499" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J499" s="9"/>
     </row>
-    <row r="500" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="500" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J500" s="9"/>
     </row>
-    <row r="501" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="501" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J501" s="9"/>
     </row>
-    <row r="502" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="502" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J502" s="9"/>
     </row>
-    <row r="503" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="503" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J503" s="9"/>
     </row>
-    <row r="504" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="504" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J504" s="9"/>
     </row>
-    <row r="505" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="505" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J505" s="9"/>
     </row>
-    <row r="506" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="506" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J506" s="9"/>
     </row>
-    <row r="507" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="507" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J507" s="9"/>
     </row>
-    <row r="508" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="508" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J508" s="9"/>
     </row>
-    <row r="509" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="509" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J509" s="9"/>
     </row>
-    <row r="510" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="510" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J510" s="9"/>
     </row>
-    <row r="511" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="511" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J511" s="9"/>
     </row>
-    <row r="512" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="512" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J512" s="9"/>
     </row>
-    <row r="513" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="513" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J513" s="9"/>
     </row>
-    <row r="514" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="514" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J514" s="9"/>
     </row>
-    <row r="515" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="515" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J515" s="9"/>
     </row>
-    <row r="516" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="516" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J516" s="9"/>
     </row>
-    <row r="517" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="517" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J517" s="9"/>
     </row>
-    <row r="518" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="518" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J518" s="9"/>
     </row>
-    <row r="519" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="519" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J519" s="9"/>
     </row>
-    <row r="520" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="520" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J520" s="9"/>
     </row>
-    <row r="521" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="521" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J521" s="9"/>
     </row>
-    <row r="522" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="522" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J522" s="9"/>
     </row>
-    <row r="523" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="523" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J523" s="9"/>
     </row>
-    <row r="524" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="524" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J524" s="9"/>
     </row>
-    <row r="525" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="525" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J525" s="9"/>
     </row>
-    <row r="526" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="526" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J526" s="9"/>
     </row>
-    <row r="527" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="527" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J527" s="9"/>
     </row>
-    <row r="528" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="528" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J528" s="9"/>
     </row>
-    <row r="529" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="529" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J529" s="9"/>
     </row>
-    <row r="530" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="530" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J530" s="9"/>
     </row>
-    <row r="531" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="531" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J531" s="9"/>
     </row>
-    <row r="532" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="532" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J532" s="9"/>
     </row>
-    <row r="533" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="533" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J533" s="9"/>
     </row>
-    <row r="534" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="534" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J534" s="9"/>
     </row>
-    <row r="535" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="535" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J535" s="9"/>
     </row>
-    <row r="536" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="536" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J536" s="9"/>
     </row>
-    <row r="537" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="537" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J537" s="9"/>
     </row>
-    <row r="538" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="538" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J538" s="9"/>
     </row>
-    <row r="539" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="539" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J539" s="9"/>
     </row>
-    <row r="540" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="540" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J540" s="9"/>
     </row>
-    <row r="541" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="541" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J541" s="9"/>
     </row>
-    <row r="542" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="542" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J542" s="9"/>
     </row>
-    <row r="543" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="543" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J543" s="9"/>
     </row>
-    <row r="544" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="544" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J544" s="9"/>
     </row>
-    <row r="545" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="545" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J545" s="9"/>
     </row>
-    <row r="546" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="546" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J546" s="9"/>
     </row>
-    <row r="547" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="547" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J547" s="9"/>
     </row>
-    <row r="548" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="548" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J548" s="9"/>
     </row>
-    <row r="549" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="549" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J549" s="9"/>
     </row>
-    <row r="550" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="550" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J550" s="9"/>
     </row>
-    <row r="551" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="551" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J551" s="9"/>
     </row>
-    <row r="552" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="552" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J552" s="9"/>
     </row>
-    <row r="553" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="553" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J553" s="9"/>
     </row>
-    <row r="554" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="554" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J554" s="9"/>
     </row>
-    <row r="555" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="555" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J555" s="9"/>
     </row>
-    <row r="556" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="556" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J556" s="9"/>
     </row>
-    <row r="557" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="557" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J557" s="9"/>
     </row>
-    <row r="558" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="558" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J558" s="9"/>
     </row>
-    <row r="559" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="559" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J559" s="9"/>
     </row>
-    <row r="560" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="560" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J560" s="9"/>
     </row>
-    <row r="561" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="561" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J561" s="9"/>
     </row>
-    <row r="562" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="562" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J562" s="9"/>
     </row>
-    <row r="563" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="563" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J563" s="9"/>
     </row>
-    <row r="564" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="564" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J564" s="9"/>
     </row>
-    <row r="565" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="565" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J565" s="9"/>
     </row>
-    <row r="566" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="566" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J566" s="9"/>
     </row>
-    <row r="567" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="567" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J567" s="9"/>
     </row>
-    <row r="568" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="568" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J568" s="9"/>
     </row>
-    <row r="569" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="569" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J569" s="9"/>
     </row>
-    <row r="570" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="570" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J570" s="9"/>
     </row>
-    <row r="571" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="571" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J571" s="9"/>
     </row>
-    <row r="572" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="572" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J572" s="9"/>
     </row>
-    <row r="573" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="573" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J573" s="9"/>
     </row>
-    <row r="574" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="574" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J574" s="9"/>
     </row>
-    <row r="575" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="575" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J575" s="9"/>
     </row>
-    <row r="576" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="576" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J576" s="9"/>
     </row>
-    <row r="577" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="577" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J577" s="9"/>
     </row>
-    <row r="578" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="578" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J578" s="9"/>
     </row>
-    <row r="579" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="579" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J579" s="9"/>
     </row>
-    <row r="580" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="580" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J580" s="9"/>
     </row>
-    <row r="581" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="581" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J581" s="9"/>
     </row>
-    <row r="582" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="582" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J582" s="9"/>
     </row>
-    <row r="583" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="583" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J583" s="9"/>
     </row>
-    <row r="584" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="584" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J584" s="9"/>
     </row>
-    <row r="585" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="585" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J585" s="9"/>
     </row>
-    <row r="586" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="586" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J586" s="9"/>
     </row>
-    <row r="587" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="587" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J587" s="9"/>
     </row>
-    <row r="588" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="588" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J588" s="9"/>
     </row>
-    <row r="589" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="589" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J589" s="9"/>
     </row>
-    <row r="590" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="590" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J590" s="9"/>
     </row>
-    <row r="591" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="591" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J591" s="9"/>
     </row>
-    <row r="592" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="592" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J592" s="9"/>
     </row>
-    <row r="593" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="593" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J593" s="9"/>
     </row>
-    <row r="594" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="594" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J594" s="9"/>
     </row>
-    <row r="595" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="595" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J595" s="9"/>
     </row>
-    <row r="596" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="596" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J596" s="9"/>
     </row>
-    <row r="597" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="597" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J597" s="9"/>
     </row>
-    <row r="598" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="598" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J598" s="9"/>
     </row>
-    <row r="599" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="599" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J599" s="9"/>
     </row>
-    <row r="600" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="600" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J600" s="9"/>
     </row>
-    <row r="601" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="601" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J601" s="9"/>
     </row>
-    <row r="602" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="602" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J602" s="9"/>
     </row>
-    <row r="603" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="603" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J603" s="9"/>
     </row>
-    <row r="604" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="604" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J604" s="9"/>
     </row>
-    <row r="605" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="605" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J605" s="9"/>
     </row>
-    <row r="606" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="606" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J606" s="9"/>
     </row>
-    <row r="607" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="607" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J607" s="9"/>
     </row>
-    <row r="608" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="608" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J608" s="9"/>
     </row>
-    <row r="609" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="609" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J609" s="9"/>
     </row>
-    <row r="610" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="610" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J610" s="9"/>
     </row>
-    <row r="611" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="611" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J611" s="9"/>
     </row>
-    <row r="612" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="612" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J612" s="9"/>
     </row>
-    <row r="613" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="613" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J613" s="9"/>
     </row>
-    <row r="614" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="614" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J614" s="9"/>
     </row>
-    <row r="615" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="615" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J615" s="9"/>
     </row>
-    <row r="616" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="616" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J616" s="9"/>
     </row>
-    <row r="617" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="617" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J617" s="9"/>
     </row>
-    <row r="618" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="618" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J618" s="9"/>
     </row>
-    <row r="619" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="619" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J619" s="9"/>
     </row>
-    <row r="620" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="620" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J620" s="9"/>
     </row>
-    <row r="621" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="621" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J621" s="9"/>
     </row>
-    <row r="622" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="622" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J622" s="9"/>
     </row>
-    <row r="623" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="623" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J623" s="9"/>
     </row>
-    <row r="624" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="624" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J624" s="9"/>
     </row>
-    <row r="625" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="625" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J625" s="9"/>
     </row>
-    <row r="626" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="626" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J626" s="9"/>
     </row>
-    <row r="627" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="627" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J627" s="9"/>
     </row>
-    <row r="628" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="628" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J628" s="9"/>
     </row>
-    <row r="629" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="629" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J629" s="9"/>
     </row>
-    <row r="630" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="630" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J630" s="9"/>
     </row>
-    <row r="631" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="631" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J631" s="9"/>
     </row>
-    <row r="632" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="632" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J632" s="9"/>
     </row>
-    <row r="633" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="633" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J633" s="9"/>
     </row>
-    <row r="634" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="634" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J634" s="9"/>
     </row>
-    <row r="635" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="635" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J635" s="9"/>
     </row>
-    <row r="636" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="636" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J636" s="9"/>
     </row>
-    <row r="637" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="637" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J637" s="9"/>
     </row>
-    <row r="638" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="638" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J638" s="9"/>
     </row>
-    <row r="639" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="639" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J639" s="9"/>
     </row>
-    <row r="640" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="640" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J640" s="9"/>
     </row>
-    <row r="641" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="641" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J641" s="9"/>
     </row>
-    <row r="642" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="642" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J642" s="9"/>
     </row>
-    <row r="643" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="643" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J643" s="9"/>
     </row>
-    <row r="644" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="644" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J644" s="9"/>
     </row>
-    <row r="645" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="645" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J645" s="9"/>
     </row>
-    <row r="646" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="646" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J646" s="9"/>
     </row>
-    <row r="647" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="647" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J647" s="9"/>
     </row>
-    <row r="648" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="648" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J648" s="9"/>
     </row>
-    <row r="649" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="649" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J649" s="9"/>
     </row>
-    <row r="650" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="650" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J650" s="9"/>
     </row>
-    <row r="651" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="651" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J651" s="9"/>
     </row>
-    <row r="652" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="652" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J652" s="9"/>
     </row>
-    <row r="653" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="653" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J653" s="9"/>
     </row>
-    <row r="654" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="654" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J654" s="9"/>
     </row>
-    <row r="655" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="655" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J655" s="9"/>
     </row>
-    <row r="656" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="656" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J656" s="9"/>
     </row>
-    <row r="657" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="657" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J657" s="9"/>
     </row>
-    <row r="658" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="658" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J658" s="9"/>
     </row>
-    <row r="659" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="659" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J659" s="9"/>
     </row>
-    <row r="660" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="660" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J660" s="9"/>
     </row>
-    <row r="661" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="661" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J661" s="9"/>
     </row>
-    <row r="662" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="662" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J662" s="9"/>
     </row>
-    <row r="663" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="663" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J663" s="9"/>
     </row>
-    <row r="664" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="664" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J664" s="9"/>
     </row>
-    <row r="665" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="665" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J665" s="9"/>
     </row>
-    <row r="666" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="666" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J666" s="9"/>
     </row>
-    <row r="667" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="667" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J667" s="9"/>
     </row>
-    <row r="668" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="668" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J668" s="9"/>
     </row>
-    <row r="669" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="669" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J669" s="9"/>
     </row>
-    <row r="670" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="670" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J670" s="9"/>
     </row>
-    <row r="671" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="671" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J671" s="9"/>
     </row>
-    <row r="672" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="672" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J672" s="9"/>
     </row>
-    <row r="673" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="673" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J673" s="9"/>
     </row>
-    <row r="674" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="674" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J674" s="9"/>
     </row>
-    <row r="675" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="675" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J675" s="9"/>
     </row>
-    <row r="676" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="676" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J676" s="9"/>
     </row>
-    <row r="677" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="677" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J677" s="9"/>
     </row>
-    <row r="678" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="678" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J678" s="9"/>
     </row>
-    <row r="679" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="679" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J679" s="9"/>
     </row>
-    <row r="680" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="680" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J680" s="9"/>
     </row>
-    <row r="681" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="681" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J681" s="9"/>
     </row>
-    <row r="682" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="682" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J682" s="9"/>
     </row>
-    <row r="683" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="683" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J683" s="9"/>
     </row>
-    <row r="684" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="684" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J684" s="9"/>
     </row>
-    <row r="685" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="685" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J685" s="9"/>
     </row>
-    <row r="686" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="686" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J686" s="9"/>
     </row>
-    <row r="687" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="687" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J687" s="9"/>
     </row>
-    <row r="688" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="688" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J688" s="9"/>
     </row>
-    <row r="689" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="689" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J689" s="9"/>
     </row>
-    <row r="690" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="690" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J690" s="9"/>
     </row>
-    <row r="691" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="691" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J691" s="9"/>
     </row>
-    <row r="692" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="692" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J692" s="9"/>
     </row>
-    <row r="693" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="693" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J693" s="9"/>
     </row>
-    <row r="694" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="694" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J694" s="9"/>
     </row>
-    <row r="695" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="695" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J695" s="9"/>
     </row>
-    <row r="696" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="696" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J696" s="9"/>
     </row>
-    <row r="697" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="697" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J697" s="9"/>
     </row>
-    <row r="698" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="698" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J698" s="9"/>
     </row>
-    <row r="699" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="699" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J699" s="9"/>
     </row>
-    <row r="700" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="700" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J700" s="9"/>
     </row>
-    <row r="701" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="701" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J701" s="9"/>
     </row>
-    <row r="702" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="702" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J702" s="9"/>
     </row>
-    <row r="703" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="703" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J703" s="9"/>
     </row>
-    <row r="704" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="704" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J704" s="9"/>
     </row>
-    <row r="705" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="705" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J705" s="9"/>
     </row>
-    <row r="706" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="706" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J706" s="9"/>
     </row>
-    <row r="707" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="707" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J707" s="9"/>
     </row>
-    <row r="708" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="708" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J708" s="9"/>
     </row>
-    <row r="709" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="709" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J709" s="9"/>
     </row>
-    <row r="710" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="710" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J710" s="9"/>
     </row>
-    <row r="711" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="711" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J711" s="9"/>
     </row>
-    <row r="712" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="712" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J712" s="9"/>
     </row>
-    <row r="713" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="713" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J713" s="9"/>
     </row>
-    <row r="714" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="714" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J714" s="9"/>
     </row>
-    <row r="715" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="715" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J715" s="9"/>
     </row>
-    <row r="716" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="716" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J716" s="9"/>
     </row>
-    <row r="717" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="717" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J717" s="9"/>
     </row>
-    <row r="718" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="718" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J718" s="9"/>
     </row>
-    <row r="719" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="719" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J719" s="9"/>
     </row>
-    <row r="720" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="720" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J720" s="9"/>
     </row>
-    <row r="721" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="721" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J721" s="9"/>
     </row>
-    <row r="722" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="722" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J722" s="9"/>
     </row>
-    <row r="723" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="723" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J723" s="9"/>
     </row>
-    <row r="724" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="724" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J724" s="9"/>
     </row>
-    <row r="725" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="725" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J725" s="9"/>
     </row>
-    <row r="726" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="726" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J726" s="9"/>
     </row>
-    <row r="727" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="727" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J727" s="9"/>
     </row>
-    <row r="728" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="728" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J728" s="9"/>
     </row>
-    <row r="729" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="729" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J729" s="9"/>
     </row>
-    <row r="730" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="730" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J730" s="9"/>
     </row>
-    <row r="731" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="731" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J731" s="9"/>
     </row>
-    <row r="732" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="732" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J732" s="9"/>
     </row>
-    <row r="733" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="733" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J733" s="9"/>
     </row>
-    <row r="734" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="734" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J734" s="9"/>
     </row>
-    <row r="735" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="735" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J735" s="9"/>
     </row>
-    <row r="736" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="736" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J736" s="9"/>
     </row>
-    <row r="737" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="737" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J737" s="9"/>
     </row>
-    <row r="738" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="738" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J738" s="9"/>
     </row>
-    <row r="739" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="739" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J739" s="9"/>
     </row>
-    <row r="740" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="740" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J740" s="9"/>
     </row>
-    <row r="741" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="741" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J741" s="9"/>
     </row>
-    <row r="742" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="742" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J742" s="9"/>
     </row>
-    <row r="743" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="743" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J743" s="9"/>
     </row>
-    <row r="744" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="744" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J744" s="9"/>
     </row>
-    <row r="745" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="745" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J745" s="9"/>
     </row>
-    <row r="746" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="746" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J746" s="9"/>
     </row>
-    <row r="747" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="747" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J747" s="9"/>
     </row>
-    <row r="748" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="748" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J748" s="9"/>
     </row>
-    <row r="749" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="749" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J749" s="9"/>
     </row>
-    <row r="750" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="750" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J750" s="9"/>
     </row>
-    <row r="751" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="751" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J751" s="9"/>
     </row>
-    <row r="752" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="752" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J752" s="9"/>
     </row>
-    <row r="753" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="753" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J753" s="9"/>
     </row>
-    <row r="754" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="754" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J754" s="9"/>
     </row>
-    <row r="755" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="755" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J755" s="9"/>
     </row>
-    <row r="756" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="756" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J756" s="9"/>
     </row>
-    <row r="757" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="757" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J757" s="9"/>
     </row>
-    <row r="758" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="758" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J758" s="9"/>
     </row>
-    <row r="759" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="759" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J759" s="9"/>
     </row>
-    <row r="760" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="760" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J760" s="9"/>
     </row>
-    <row r="761" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="761" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J761" s="9"/>
     </row>
-    <row r="762" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="762" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J762" s="9"/>
     </row>
-    <row r="763" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="763" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J763" s="9"/>
     </row>
-    <row r="764" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="764" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J764" s="9"/>
     </row>
-    <row r="765" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="765" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J765" s="9"/>
     </row>
-    <row r="766" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="766" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J766" s="9"/>
     </row>
-    <row r="767" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="767" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J767" s="9"/>
     </row>
-    <row r="768" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="768" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J768" s="9"/>
     </row>
-    <row r="769" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="769" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J769" s="9"/>
     </row>
-    <row r="770" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="770" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J770" s="9"/>
     </row>
-    <row r="771" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="771" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J771" s="9"/>
     </row>
-    <row r="772" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="772" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J772" s="9"/>
     </row>
-    <row r="773" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="773" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J773" s="9"/>
     </row>
-    <row r="774" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="774" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J774" s="9"/>
     </row>
-    <row r="775" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="775" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J775" s="9"/>
     </row>
-    <row r="776" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="776" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J776" s="9"/>
     </row>
-    <row r="777" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="777" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J777" s="9"/>
     </row>
-    <row r="778" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="778" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J778" s="9"/>
     </row>
-    <row r="779" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="779" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J779" s="9"/>
     </row>
-    <row r="780" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="780" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J780" s="9"/>
     </row>
-    <row r="781" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="781" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J781" s="9"/>
     </row>
-    <row r="782" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="782" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J782" s="9"/>
     </row>
-    <row r="783" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="783" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J783" s="9"/>
     </row>
-    <row r="784" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="784" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J784" s="9"/>
     </row>
-    <row r="785" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="785" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J785" s="9"/>
     </row>
-    <row r="786" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="786" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J786" s="9"/>
     </row>
-    <row r="787" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="787" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J787" s="9"/>
     </row>
-    <row r="788" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="788" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J788" s="9"/>
     </row>
-    <row r="789" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="789" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J789" s="9"/>
     </row>
-    <row r="790" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="790" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J790" s="9"/>
     </row>
-    <row r="791" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="791" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J791" s="9"/>
     </row>
-    <row r="792" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="792" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J792" s="9"/>
     </row>
-    <row r="793" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="793" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J793" s="9"/>
     </row>
-    <row r="794" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="794" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J794" s="9"/>
     </row>
-    <row r="795" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="795" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J795" s="9"/>
     </row>
-    <row r="796" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="796" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J796" s="9"/>
     </row>
-    <row r="797" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="797" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J797" s="9"/>
     </row>
-    <row r="798" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="798" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J798" s="9"/>
     </row>
-    <row r="799" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="799" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J799" s="9"/>
     </row>
-    <row r="800" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="800" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J800" s="9"/>
     </row>
-    <row r="801" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="801" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J801" s="9"/>
     </row>
-    <row r="802" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="802" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J802" s="9"/>
     </row>
-    <row r="803" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="803" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J803" s="9"/>
     </row>
-    <row r="804" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="804" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J804" s="9"/>
     </row>
-    <row r="805" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="805" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J805" s="9"/>
     </row>
-    <row r="806" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="806" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J806" s="9"/>
     </row>
-    <row r="807" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="807" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J807" s="9"/>
     </row>
-    <row r="808" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="808" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J808" s="9"/>
     </row>
-    <row r="809" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="809" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J809" s="9"/>
     </row>
-    <row r="810" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="810" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J810" s="9"/>
     </row>
-    <row r="811" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="811" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J811" s="9"/>
     </row>
-    <row r="812" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="812" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J812" s="9"/>
     </row>
-    <row r="813" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="813" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J813" s="9"/>
     </row>
-    <row r="814" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="814" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J814" s="9"/>
     </row>
-    <row r="815" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="815" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J815" s="9"/>
     </row>
-    <row r="816" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="816" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J816" s="9"/>
     </row>
-    <row r="817" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="817" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J817" s="9"/>
     </row>
-    <row r="818" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="818" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J818" s="9"/>
     </row>
-    <row r="819" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="819" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J819" s="9"/>
     </row>
-    <row r="820" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="820" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J820" s="9"/>
     </row>
-    <row r="821" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="821" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J821" s="9"/>
     </row>
-    <row r="822" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="822" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J822" s="9"/>
     </row>
-    <row r="823" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="823" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J823" s="9"/>
     </row>
-    <row r="824" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="824" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J824" s="9"/>
     </row>
-    <row r="825" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="825" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J825" s="9"/>
     </row>
-    <row r="826" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="826" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J826" s="9"/>
     </row>
-    <row r="827" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="827" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J827" s="9"/>
     </row>
-    <row r="828" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="828" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J828" s="9"/>
     </row>
-    <row r="829" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="829" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J829" s="9"/>
     </row>
-    <row r="830" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="830" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J830" s="9"/>
     </row>
-    <row r="831" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="831" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J831" s="9"/>
     </row>
-    <row r="832" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="832" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J832" s="9"/>
     </row>
-    <row r="833" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="833" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J833" s="9"/>
     </row>
-    <row r="834" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="834" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J834" s="9"/>
     </row>
-    <row r="835" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="835" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J835" s="9"/>
     </row>
-    <row r="836" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="836" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J836" s="9"/>
     </row>
-    <row r="837" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="837" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J837" s="9"/>
     </row>
-    <row r="838" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="838" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J838" s="9"/>
     </row>
-    <row r="839" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="839" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J839" s="9"/>
     </row>
-    <row r="840" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="840" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J840" s="9"/>
     </row>
-    <row r="841" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="841" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J841" s="9"/>
     </row>
-    <row r="842" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="842" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J842" s="9"/>
     </row>
-    <row r="843" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="843" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J843" s="9"/>
     </row>
-    <row r="844" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="844" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J844" s="9"/>
     </row>
-    <row r="845" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="845" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J845" s="9"/>
     </row>
-    <row r="846" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="846" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J846" s="9"/>
     </row>
-    <row r="847" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="847" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J847" s="9"/>
     </row>
-    <row r="848" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="848" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J848" s="9"/>
     </row>
-    <row r="849" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="849" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J849" s="9"/>
     </row>
-    <row r="850" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="850" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J850" s="9"/>
     </row>
-    <row r="851" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="851" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J851" s="9"/>
     </row>
-    <row r="852" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="852" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J852" s="9"/>
     </row>
-    <row r="853" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="853" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J853" s="9"/>
     </row>
-    <row r="854" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="854" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J854" s="9"/>
     </row>
-    <row r="855" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="855" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J855" s="9"/>
     </row>
-    <row r="856" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="856" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J856" s="9"/>
     </row>
-    <row r="857" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="857" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J857" s="9"/>
     </row>
-    <row r="858" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="858" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J858" s="9"/>
     </row>
-    <row r="859" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="859" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J859" s="9"/>
     </row>
-    <row r="860" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="860" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J860" s="9"/>
     </row>
-    <row r="861" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="861" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J861" s="9"/>
     </row>
-    <row r="862" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="862" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J862" s="9"/>
     </row>
-    <row r="863" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="863" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J863" s="9"/>
     </row>
-    <row r="864" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="864" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J864" s="9"/>
     </row>
-    <row r="865" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="865" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J865" s="9"/>
     </row>
-    <row r="866" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="866" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J866" s="9"/>
     </row>
-    <row r="867" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="867" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J867" s="9"/>
     </row>
-    <row r="868" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="868" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J868" s="9"/>
     </row>
-    <row r="869" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="869" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J869" s="9"/>
     </row>
-    <row r="870" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="870" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J870" s="9"/>
     </row>
-    <row r="871" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="871" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J871" s="9"/>
     </row>
-    <row r="872" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="872" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J872" s="9"/>
     </row>
-    <row r="873" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="873" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J873" s="9"/>
     </row>
-    <row r="874" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="874" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J874" s="9"/>
     </row>
-    <row r="875" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="875" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J875" s="9"/>
     </row>
-    <row r="876" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="876" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J876" s="9"/>
     </row>
-    <row r="877" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="877" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J877" s="9"/>
     </row>
-    <row r="878" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="878" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J878" s="9"/>
     </row>
-    <row r="879" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="879" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J879" s="9"/>
     </row>
-    <row r="880" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="880" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J880" s="9"/>
     </row>
-    <row r="881" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="881" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J881" s="9"/>
     </row>
-    <row r="882" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="882" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J882" s="9"/>
     </row>
-    <row r="883" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="883" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J883" s="9"/>
     </row>
-    <row r="884" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="884" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J884" s="9"/>
     </row>
-    <row r="885" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="885" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J885" s="9"/>
     </row>
-    <row r="886" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="886" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J886" s="9"/>
     </row>
-    <row r="887" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="887" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J887" s="9"/>
     </row>
-    <row r="888" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="888" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J888" s="9"/>
     </row>
-    <row r="889" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="889" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J889" s="9"/>
     </row>
-    <row r="890" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="890" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J890" s="9"/>
     </row>
-    <row r="891" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="891" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J891" s="9"/>
     </row>
-    <row r="892" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="892" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J892" s="9"/>
     </row>
-    <row r="893" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="893" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J893" s="9"/>
     </row>
-    <row r="894" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="894" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J894" s="9"/>
     </row>
-    <row r="895" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="895" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J895" s="9"/>
     </row>
-    <row r="896" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="896" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J896" s="9"/>
     </row>
-    <row r="897" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="897" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J897" s="9"/>
     </row>
-    <row r="898" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="898" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J898" s="9"/>
     </row>
-    <row r="899" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="899" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J899" s="9"/>
     </row>
-    <row r="900" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="900" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J900" s="9"/>
     </row>
-    <row r="901" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="901" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J901" s="9"/>
     </row>
-    <row r="902" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="902" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J902" s="9"/>
     </row>
-    <row r="903" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="903" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J903" s="9"/>
     </row>
-    <row r="904" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="904" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J904" s="9"/>
     </row>
-    <row r="905" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="905" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J905" s="9"/>
     </row>
-    <row r="906" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="906" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J906" s="9"/>
     </row>
-    <row r="907" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="907" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J907" s="9"/>
     </row>
-    <row r="908" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="908" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J908" s="9"/>
     </row>
-    <row r="909" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="909" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J909" s="9"/>
     </row>
-    <row r="910" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="910" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J910" s="9"/>
     </row>
-    <row r="911" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="911" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J911" s="9"/>
     </row>
-    <row r="912" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="912" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J912" s="9"/>
     </row>
-    <row r="913" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="913" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J913" s="9"/>
     </row>
-    <row r="914" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="914" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J914" s="9"/>
     </row>
-    <row r="915" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="915" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J915" s="9"/>
     </row>
-    <row r="916" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="916" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J916" s="9"/>
     </row>
-    <row r="917" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="917" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J917" s="9"/>
     </row>
-    <row r="918" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="918" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J918" s="9"/>
     </row>
-    <row r="919" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="919" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J919" s="9"/>
     </row>
-    <row r="920" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="920" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J920" s="9"/>
     </row>
-    <row r="921" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="921" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J921" s="9"/>
     </row>
-    <row r="922" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="922" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J922" s="9"/>
     </row>
-    <row r="923" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="923" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J923" s="9"/>
     </row>
-    <row r="924" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="924" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J924" s="9"/>
     </row>
-    <row r="925" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="925" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J925" s="9"/>
     </row>
-    <row r="926" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="926" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J926" s="9"/>
     </row>
-    <row r="927" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="927" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J927" s="9"/>
     </row>
-    <row r="928" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="928" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J928" s="9"/>
     </row>
-    <row r="929" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="929" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J929" s="9"/>
     </row>
-    <row r="930" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="930" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J930" s="9"/>
     </row>
-    <row r="931" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="931" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J931" s="9"/>
     </row>
-    <row r="932" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="932" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J932" s="9"/>
     </row>
-    <row r="933" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="933" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J933" s="9"/>
     </row>
-    <row r="934" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="934" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J934" s="9"/>
     </row>
-    <row r="935" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="935" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J935" s="9"/>
     </row>
-    <row r="936" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="936" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J936" s="9"/>
     </row>
-    <row r="937" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="937" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J937" s="9"/>
     </row>
-    <row r="938" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="938" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J938" s="9"/>
     </row>
-    <row r="939" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="939" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J939" s="9"/>
     </row>
-    <row r="940" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="940" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J940" s="9"/>
     </row>
-    <row r="941" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="941" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J941" s="9"/>
     </row>
-    <row r="942" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="942" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J942" s="9"/>
     </row>
-    <row r="943" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="943" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J943" s="9"/>
     </row>
-    <row r="944" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="944" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J944" s="9"/>
     </row>
-    <row r="945" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="945" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J945" s="9"/>
     </row>
-    <row r="946" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="946" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J946" s="9"/>
     </row>
-    <row r="947" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="947" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J947" s="9"/>
     </row>
-    <row r="948" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="948" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J948" s="9"/>
     </row>
-    <row r="949" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="949" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J949" s="9"/>
     </row>
-    <row r="950" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="950" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J950" s="9"/>
     </row>
-    <row r="951" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="951" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J951" s="9"/>
     </row>
-    <row r="952" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="952" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J952" s="9"/>
     </row>
-    <row r="953" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="953" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J953" s="9"/>
     </row>
-    <row r="954" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="954" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J954" s="9"/>
     </row>
-    <row r="955" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="955" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J955" s="9"/>
     </row>
-    <row r="956" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="956" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J956" s="9"/>
     </row>
-    <row r="957" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="957" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J957" s="9"/>
     </row>
-    <row r="958" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="958" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J958" s="9"/>
     </row>
-    <row r="959" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="959" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J959" s="9"/>
     </row>
-    <row r="960" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="960" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J960" s="9"/>
     </row>
-    <row r="961" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="961" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J961" s="9"/>
     </row>
-    <row r="962" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="962" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J962" s="9"/>
     </row>
-    <row r="963" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="963" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J963" s="9"/>
     </row>
-    <row r="964" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="964" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J964" s="9"/>
     </row>
-    <row r="965" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="965" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J965" s="9"/>
     </row>
-    <row r="966" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="966" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J966" s="9"/>
     </row>
-    <row r="967" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="967" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J967" s="9"/>
     </row>
-    <row r="968" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="968" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J968" s="9"/>
     </row>
-    <row r="969" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="969" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J969" s="9"/>
     </row>
-    <row r="970" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="970" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J970" s="9"/>
     </row>
-    <row r="971" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="971" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J971" s="9"/>
     </row>
-    <row r="972" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="972" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J972" s="9"/>
     </row>
-    <row r="973" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="973" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J973" s="9"/>
     </row>
-    <row r="974" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="974" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J974" s="9"/>
     </row>
-    <row r="975" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="975" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J975" s="9"/>
     </row>
-    <row r="976" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="976" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J976" s="9"/>
     </row>
-    <row r="977" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="977" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J977" s="9"/>
     </row>
-    <row r="978" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="978" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J978" s="9"/>
     </row>
-    <row r="979" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="979" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J979" s="9"/>
     </row>
-    <row r="980" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="980" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J980" s="9"/>
     </row>
-    <row r="981" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="981" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J981" s="9"/>
     </row>
-    <row r="982" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="982" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J982" s="9"/>
     </row>
-    <row r="983" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="983" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J983" s="9"/>
     </row>
-    <row r="984" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="984" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J984" s="9"/>
     </row>
-    <row r="985" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="985" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J985" s="9"/>
     </row>
-    <row r="986" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="986" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J986" s="9"/>
     </row>
-    <row r="987" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="987" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J987" s="9"/>
     </row>
-    <row r="988" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="988" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J988" s="9"/>
     </row>
-    <row r="989" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="989" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J989" s="9"/>
     </row>
-    <row r="990" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="990" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J990" s="9"/>
     </row>
-    <row r="991" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="991" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J991" s="9"/>
     </row>
-    <row r="992" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="992" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J992" s="9"/>
     </row>
-    <row r="993" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="993" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J993" s="9"/>
     </row>
-    <row r="994" spans="10:10" ht="13" x14ac:dyDescent="0.15">
+    <row r="994" spans="10:10" ht="12.75" x14ac:dyDescent="0.2">
       <c r="J994" s="9"/>
     </row>
   </sheetData>
   <customSheetViews>
     <customSheetView guid="{D9CDEFDA-B742-4707-B803-BE75C138FC2A}" filter="1" showAutoFilter="1">
       <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-      <autoFilter ref="P1:P994" xr:uid="{19CEDF4C-346D-2C4B-B662-BD273CC2A6CD}"/>
+      <autoFilter ref="P1:P994" xr:uid="{7BC3390D-7D4C-46D5-BAD5-25340C7B951F}"/>
     </customSheetView>
   </customSheetViews>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6793,13 +6793,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{903B5A93-8202-4044-A142-B3A85507BA31}">
   <dimension ref="A1:B115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="21.1640625" customWidth="1"/>
-    <col min="2" max="2" width="29.83203125" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -6815,7 +6815,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -6823,7 +6823,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -6831,7 +6831,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -6839,7 +6839,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -6847,7 +6847,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -6855,7 +6855,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -6863,7 +6863,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -6879,7 +6879,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -6887,7 +6887,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -6903,7 +6903,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -6911,7 +6911,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -6919,7 +6919,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -6927,7 +6927,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -6935,7 +6935,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -6951,7 +6951,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -6959,7 +6959,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -6967,7 +6967,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -6975,7 +6975,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -6983,7 +6983,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -6999,7 +6999,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -7007,7 +7007,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>25</v>
       </c>
@@ -7015,7 +7015,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>26</v>
       </c>
@@ -7023,7 +7023,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>27</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>28</v>
       </c>
@@ -7039,7 +7039,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>29</v>
       </c>
@@ -7047,7 +7047,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>30</v>
       </c>
@@ -7055,7 +7055,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>31</v>
       </c>
@@ -7063,7 +7063,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>32</v>
       </c>
@@ -7071,7 +7071,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>33</v>
       </c>
@@ -7079,7 +7079,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>34</v>
       </c>
@@ -7087,7 +7087,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>35</v>
       </c>
@@ -7095,7 +7095,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>36</v>
       </c>
@@ -7103,7 +7103,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>37</v>
       </c>
@@ -7111,7 +7111,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>38</v>
       </c>
@@ -7119,7 +7119,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>39</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>40</v>
       </c>
@@ -7135,7 +7135,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>41</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>42</v>
       </c>
@@ -7151,7 +7151,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>43</v>
       </c>
@@ -7159,7 +7159,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>44</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>45</v>
       </c>
@@ -7175,7 +7175,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>46</v>
       </c>
@@ -7183,7 +7183,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>47</v>
       </c>
@@ -7191,7 +7191,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="2">
         <v>48</v>
       </c>
@@ -7199,7 +7199,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>49</v>
       </c>
@@ -7207,7 +7207,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>50</v>
       </c>
@@ -7215,7 +7215,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>51</v>
       </c>
@@ -7223,7 +7223,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>52</v>
       </c>
@@ -7231,7 +7231,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>53</v>
       </c>
@@ -7239,7 +7239,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>54</v>
       </c>
@@ -7247,7 +7247,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>55</v>
       </c>
@@ -7255,7 +7255,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>56</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>57</v>
       </c>
@@ -7271,7 +7271,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>58</v>
       </c>
@@ -7279,7 +7279,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>59</v>
       </c>
@@ -7287,7 +7287,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>60</v>
       </c>
@@ -7295,7 +7295,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>61</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>62</v>
       </c>
@@ -7311,7 +7311,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>63</v>
       </c>
@@ -7319,7 +7319,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>64</v>
       </c>
@@ -7327,7 +7327,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>65</v>
       </c>
@@ -7335,7 +7335,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>66</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>67</v>
       </c>
@@ -7351,7 +7351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>68</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>69</v>
       </c>
@@ -7367,7 +7367,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>70</v>
       </c>
@@ -7375,7 +7375,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>71</v>
       </c>
@@ -7383,7 +7383,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>72</v>
       </c>
@@ -7391,7 +7391,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>73</v>
       </c>
@@ -7399,7 +7399,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>74</v>
       </c>
@@ -7407,7 +7407,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>75</v>
       </c>
@@ -7415,7 +7415,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>76</v>
       </c>
@@ -7423,7 +7423,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>77</v>
       </c>
@@ -7431,7 +7431,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>78</v>
       </c>
@@ -7439,7 +7439,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>79</v>
       </c>
@@ -7447,7 +7447,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>80</v>
       </c>
@@ -7455,7 +7455,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>81</v>
       </c>
@@ -7463,7 +7463,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>82</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>83</v>
       </c>
@@ -7479,7 +7479,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>84</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>85</v>
       </c>
@@ -7495,7 +7495,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>86</v>
       </c>
@@ -7503,7 +7503,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>87</v>
       </c>
@@ -7511,7 +7511,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>88</v>
       </c>
@@ -7519,7 +7519,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>89</v>
       </c>
@@ -7527,7 +7527,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>90</v>
       </c>
@@ -7535,7 +7535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>91</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>92</v>
       </c>
@@ -7551,7 +7551,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>93</v>
       </c>
@@ -7559,7 +7559,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>94</v>
       </c>
@@ -7567,7 +7567,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>95</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>96</v>
       </c>
@@ -7583,7 +7583,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>97</v>
       </c>
@@ -7591,7 +7591,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>98</v>
       </c>
@@ -7599,7 +7599,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>99</v>
       </c>
@@ -7607,7 +7607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>100</v>
       </c>
@@ -7615,7 +7615,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>101</v>
       </c>
@@ -7623,7 +7623,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>102</v>
       </c>
@@ -7631,7 +7631,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>103</v>
       </c>
@@ -7639,7 +7639,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>104</v>
       </c>
@@ -7647,7 +7647,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A107" s="2">
         <v>105</v>
       </c>
@@ -7655,7 +7655,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>106</v>
       </c>
@@ -7663,7 +7663,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>107</v>
       </c>
@@ -7671,7 +7671,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>108</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>109</v>
       </c>
@@ -7687,7 +7687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>110</v>
       </c>
@@ -7695,7 +7695,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>111</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>112</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>113</v>
       </c>
@@ -7727,12 +7727,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8700276F-7844-46F1-85C5-DD805B6A2273}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="9" t="s">
         <v>29</v>
       </c>
@@ -7740,7 +7740,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
         <v>37</v>
       </c>
@@ -7748,7 +7748,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
         <v>43</v>
       </c>
@@ -7756,7 +7756,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
         <v>46</v>
       </c>
@@ -7764,7 +7764,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A5" s="13" t="s">
         <v>50</v>
       </c>
@@ -7772,7 +7772,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
         <v>55</v>
       </c>
@@ -7780,7 +7780,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
         <v>59</v>
       </c>
@@ -7788,7 +7788,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A8" s="23" t="s">
         <v>61</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A9" s="18" t="s">
         <v>63</v>
       </c>
@@ -7804,7 +7804,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
         <v>64</v>
       </c>
@@ -7812,7 +7812,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A11" s="26" t="s">
         <v>68</v>
       </c>
@@ -7820,7 +7820,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A12" s="26" t="s">
         <v>72</v>
       </c>
@@ -7828,7 +7828,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A13" s="26" t="s">
         <v>74</v>
       </c>
@@ -7836,7 +7836,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A14" s="26" t="s">
         <v>76</v>
       </c>
@@ -7844,7 +7844,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
         <v>81</v>
       </c>
@@ -7852,7 +7852,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
         <v>83</v>
       </c>
@@ -7860,7 +7860,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
         <v>85</v>
       </c>
@@ -7868,7 +7868,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
         <v>88</v>
       </c>
@@ -7876,7 +7876,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A19" s="26" t="s">
         <v>91</v>
       </c>
@@ -7884,7 +7884,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="26" t="s">
         <v>93</v>
       </c>
@@ -7892,7 +7892,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A21" s="26" t="s">
         <v>95</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="26" t="s">
         <v>100</v>
       </c>
@@ -7908,7 +7908,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A23" s="26" t="s">
         <v>101</v>
       </c>
@@ -7916,7 +7916,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="26" t="s">
         <v>104</v>
       </c>
@@ -7924,7 +7924,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="37" t="s">
         <v>106</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="18" t="s">
         <v>107</v>
       </c>
@@ -7940,7 +7940,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="18" t="s">
         <v>109</v>
       </c>
@@ -7948,7 +7948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A28" s="18" t="s">
         <v>111</v>
       </c>
@@ -7956,7 +7956,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A29" s="26" t="s">
         <v>113</v>
       </c>
@@ -7964,7 +7964,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A30" s="26" t="s">
         <v>42</v>
       </c>
@@ -7972,7 +7972,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A31" s="26" t="s">
         <v>115</v>
       </c>
@@ -7980,7 +7980,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A32" s="30" t="s">
         <v>116</v>
       </c>
@@ -7988,7 +7988,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="14" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:2" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A33" s="31" t="s">
         <v>117</v>
       </c>
@@ -7996,7 +7996,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="32" t="s">
         <v>118</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="32" t="s">
         <v>120</v>
       </c>
@@ -8012,7 +8012,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="32" t="s">
         <v>122</v>
       </c>
@@ -8020,7 +8020,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="33" t="s">
         <v>123</v>
       </c>
@@ -8028,7 +8028,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="32" t="s">
         <v>125</v>
       </c>
@@ -8036,7 +8036,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="32" t="s">
         <v>127</v>
       </c>
@@ -8044,7 +8044,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="33" t="s">
         <v>128</v>
       </c>
@@ -8052,7 +8052,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="32" t="s">
         <v>129</v>
       </c>
@@ -8060,7 +8060,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="32" t="s">
         <v>130</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="34" t="s">
         <v>131</v>
       </c>
@@ -8076,7 +8076,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="34" t="s">
         <v>133</v>
       </c>
@@ -8084,7 +8084,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="16" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="35" t="s">
         <v>136</v>
       </c>
@@ -8092,7 +8092,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="34" t="s">
         <v>138</v>
       </c>
@@ -8100,7 +8100,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="34" t="s">
         <v>141</v>
       </c>
@@ -8108,7 +8108,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="34" t="s">
         <v>143</v>
       </c>
@@ -8116,7 +8116,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="34" t="s">
         <v>145</v>
       </c>
@@ -8124,7 +8124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="16" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="34" t="s">
         <v>147</v>
       </c>
